--- a/basic-forms/forms/app/android_app_launcher.xlsx
+++ b/basic-forms/forms/app/android_app_launcher.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -49,6 +49,27 @@
 </t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>-7</xdr:colOff>
+                <xdr:row>16</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
@@ -61,6 +82,27 @@
           <t xml:space="preserve">Variable name. It may not contain spaces and must start with a letter or underscore. You should use a short, descriptive name and can use underscores to separate words. For example: date_of_birth.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>-241</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
@@ -74,6 +116,27 @@
 Can be translated.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>-241</xdr:colOff>
+                <xdr:row>15</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
@@ -87,6 +150,27 @@
 Can be translated.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>-9</xdr:colOff>
+                <xdr:row>7</xdr:row>
+                <xdr:rowOff>8</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
@@ -100,6 +184,27 @@
 These can be specific to the field type.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>-123</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="F1" authorId="0">
       <text>
@@ -113,6 +218,27 @@
 https://docs.getodk.org/form-logic/#setting-default-responses</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>38</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="G1" authorId="0">
       <text>
@@ -128,6 +254,27 @@
 https://docs.getodk.org/form-logic/#when-expressions-are-evaluated</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>7</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>58</xdr:colOff>
+                <xdr:row>22</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="H1" authorId="0">
       <text>
@@ -140,8 +287,63 @@
           <t xml:space="preserve">Set ‘true’ to indicate that a question’s value cannot be edited.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>8</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>3</xdr:colOff>
+                <xdr:row>4</xdr:row>
+                <xdr:rowOff>14</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Can include a human-friendly note to describe the row. This will be ignored by all ODK tools.</t>
+        </r>
+      </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>9</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>65</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
+    </comment>
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -152,13 +354,34 @@
           <t xml:space="preserve">Can include a human-friendly note to describe the row. This will be ignored by all ODK tools.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>10</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>5</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:v2="http://schemas.openxmlformats.org/spreadsheetml/2006/main/v2" mc:Ignorable="v2">
   <authors>
     <author>Unknown Author</author>
   </authors>
@@ -175,6 +398,27 @@
 https://docs.getodk.org/xlsform/#the-settings-sheet</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>1</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>6</xdr:colOff>
+                <xdr:row>8</xdr:row>
+                <xdr:rowOff>5</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="B1" authorId="0">
       <text>
@@ -188,6 +432,27 @@
 By default, this template uses a formula to create a date-based version that will update automatically.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>2</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>19</xdr:row>
+                <xdr:rowOff>12</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
@@ -200,6 +465,27 @@
           <t xml:space="preserve">Set to ‘pages’ to indicate that groups with the `field-list` appearance represent separate form pages (and all other questions will be shown on their own page). </t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>-109</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>1</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
@@ -212,13 +498,34 @@
           <t xml:space="preserve">Custom namespaces supported in the form.  `cht` must be included here to use the custom `instance::cht` columns on the survey sheet.</t>
         </r>
       </text>
+      <mc:AlternateContent>
+        <mc:Choice Requires="v2">
+          <commentPr autoFill="true" autoScale="false" colHidden="false" locked="false" rowHidden="false" textHAlign="justify" textVAlign="top">
+            <anchor moveWithCells="false" sizeWithCells="false">
+              <xdr:from>
+                <xdr:col>4</xdr:col>
+                <xdr:colOff>23</xdr:colOff>
+                <xdr:row>0</xdr:row>
+                <xdr:rowOff>0</xdr:rowOff>
+              </xdr:from>
+              <xdr:to>
+                <xdr:col>5</xdr:col>
+                <xdr:colOff>47</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>3</xdr:rowOff>
+              </xdr:to>
+            </anchor>
+          </commentPr>
+        </mc:Choice>
+        <mc:Fallback/>
+      </mc:AlternateContent>
     </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="49">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -242,6 +549,9 @@
   </si>
   <si>
     <t xml:space="preserve">read_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instance::type</t>
   </si>
   <si>
     <t xml:space="preserve">note</t>
@@ -274,10 +584,16 @@
     <t xml:space="preserve">android-app-launcher</t>
   </si>
   <si>
-    <t xml:space="preserve">hidden</t>
+    <t xml:space="preserve">text</t>
   </si>
   <si>
     <t xml:space="preserve">action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">App to launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hidden</t>
   </si>
   <si>
     <t xml:space="preserve">android.media.action.IMAGE_CAPTURE</t>
@@ -287,9 +603,6 @@
   </si>
   <si>
     <t xml:space="preserve">android-app-outputs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">text</t>
   </si>
   <si>
     <t xml:space="preserve">data</t>
@@ -302,6 +615,9 @@
   </si>
   <si>
     <t xml:space="preserve">display-base64-image</t>
+  </si>
+  <si>
+    <t xml:space="preserve">binary</t>
   </si>
   <si>
     <t xml:space="preserve">end_group</t>
@@ -735,37 +1051,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -838,7 +1154,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I1020"/>
+  <dimension ref="A1:J1020"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.31"/>
@@ -848,8 +1164,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="9.04"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="26" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.04"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="27" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -880,23 +1197,27 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4"/>
@@ -906,126 +1227,141 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="4"/>
       <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" s="4"/>
       <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
         <v>20</v>
       </c>
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" s="4"/>
       <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F8" s="4"/>
-      <c r="I8" s="4"/>
+      <c r="I8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4"/>
@@ -1035,130 +1371,143 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="4"/>
       <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
       <c r="E14" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F14" s="4"/>
       <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
       <c r="E16" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F16" s="4"/>
       <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4"/>
@@ -1168,6 +1517,7 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4"/>
@@ -1177,6 +1527,7 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4"/>
@@ -1186,6 +1537,7 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4"/>
@@ -1195,6 +1547,7 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4"/>
@@ -1204,6 +1557,7 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4"/>
@@ -1213,6 +1567,7 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4"/>
@@ -1221,6 +1576,7 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4"/>
@@ -1230,6 +1586,7 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4"/>
@@ -1239,6 +1596,7 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4"/>
@@ -1248,6 +1606,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4"/>
@@ -1257,6 +1616,7 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4"/>
@@ -1266,6 +1626,7 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4"/>
@@ -1275,6 +1636,7 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4"/>
@@ -1284,6 +1646,7 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4"/>
@@ -1293,6 +1656,7 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4"/>
@@ -1302,6 +1666,7 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4"/>
@@ -1311,6 +1676,7 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4"/>
@@ -1320,6 +1686,7 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4"/>
@@ -1329,6 +1696,7 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4"/>
@@ -1338,6 +1706,7 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4"/>
@@ -1347,6 +1716,7 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4"/>
@@ -1356,6 +1726,7 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4"/>
@@ -1365,6 +1736,7 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4"/>
@@ -1374,6 +1746,7 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4"/>
@@ -1383,6 +1756,7 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4"/>
@@ -1392,6 +1766,7 @@
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4"/>
@@ -1401,6 +1776,7 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4"/>
@@ -1410,6 +1786,7 @@
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4"/>
@@ -1419,6 +1796,7 @@
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4"/>
@@ -1428,6 +1806,7 @@
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4"/>
@@ -1437,6 +1816,7 @@
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4"/>
@@ -1446,6 +1826,7 @@
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4"/>
@@ -1455,6 +1836,7 @@
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4"/>
@@ -1464,6 +1846,7 @@
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4"/>
@@ -1473,6 +1856,7 @@
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4"/>
@@ -1482,6 +1866,7 @@
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4"/>
@@ -1491,6 +1876,7 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4"/>
@@ -1500,6 +1886,7 @@
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4"/>
@@ -1509,6 +1896,7 @@
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4"/>
@@ -1518,6 +1906,7 @@
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4"/>
@@ -1527,6 +1916,7 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4"/>
@@ -1536,6 +1926,7 @@
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4"/>
@@ -1545,6 +1936,7 @@
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4"/>
@@ -1554,6 +1946,7 @@
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4"/>
@@ -1563,6 +1956,7 @@
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4"/>
@@ -1572,6 +1966,7 @@
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4"/>
@@ -1581,6 +1976,7 @@
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4"/>
@@ -1590,6 +1986,7 @@
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4"/>
@@ -1599,6 +1996,7 @@
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4"/>
@@ -1608,6 +2006,7 @@
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4"/>
@@ -1617,6 +2016,7 @@
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4"/>
@@ -1626,6 +2026,7 @@
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4"/>
@@ -1635,6 +2036,7 @@
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4"/>
@@ -1644,6 +2046,7 @@
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4"/>
@@ -1653,6 +2056,7 @@
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4"/>
@@ -1662,6 +2066,7 @@
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
       <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4"/>
@@ -1671,6 +2076,7 @@
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
     </row>
     <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4"/>
@@ -1680,6 +2086,7 @@
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4"/>
@@ -1689,6 +2096,7 @@
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
       <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4"/>
@@ -1698,6 +2106,7 @@
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
       <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4"/>
@@ -1707,6 +2116,7 @@
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4"/>
@@ -1716,6 +2126,7 @@
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
       <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4"/>
@@ -1725,6 +2136,7 @@
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4"/>
@@ -1734,6 +2146,7 @@
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
       <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4"/>
@@ -1743,6 +2156,7 @@
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4"/>
@@ -1752,6 +2166,7 @@
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
       <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4"/>
@@ -1761,6 +2176,7 @@
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
       <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4"/>
@@ -1770,6 +2186,7 @@
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
       <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4"/>
@@ -1779,6 +2196,7 @@
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4"/>
@@ -1788,6 +2206,7 @@
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
       <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4"/>
@@ -1797,6 +2216,7 @@
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
       <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4"/>
@@ -1806,6 +2226,7 @@
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
       <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4"/>
@@ -1815,6 +2236,7 @@
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4"/>
@@ -1824,6 +2246,7 @@
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
       <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4"/>
@@ -1833,6 +2256,7 @@
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
       <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4"/>
@@ -1842,6 +2266,7 @@
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
       <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4"/>
@@ -1851,6 +2276,7 @@
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4"/>
@@ -1860,6 +2286,7 @@
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
       <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4"/>
@@ -1869,6 +2296,7 @@
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
       <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4"/>
@@ -1878,6 +2306,7 @@
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
       <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4"/>
@@ -1887,6 +2316,7 @@
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4"/>
@@ -1896,6 +2326,7 @@
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
       <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4"/>
@@ -1905,6 +2336,7 @@
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
       <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4"/>
@@ -1914,6 +2346,7 @@
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
       <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="4"/>
@@ -1923,6 +2356,7 @@
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4"/>
@@ -1932,6 +2366,7 @@
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
       <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4"/>
@@ -1941,6 +2376,7 @@
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
       <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4"/>
@@ -1950,6 +2386,7 @@
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
       <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4"/>
@@ -1959,6 +2396,7 @@
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4"/>
@@ -1968,6 +2406,7 @@
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
       <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4"/>
@@ -1977,6 +2416,7 @@
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
       <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4"/>
@@ -1986,6 +2426,7 @@
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
       <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4"/>
@@ -1995,6 +2436,7 @@
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4"/>
@@ -2004,6 +2446,7 @@
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
       <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4"/>
@@ -2013,6 +2456,7 @@
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
       <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4"/>
@@ -2022,6 +2466,7 @@
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
       <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4"/>
@@ -2031,6 +2476,7 @@
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4"/>
@@ -2040,6 +2486,7 @@
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
       <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
     </row>
     <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4"/>
@@ -2049,6 +2496,7 @@
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
       <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
     </row>
     <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4"/>
@@ -2058,6 +2506,7 @@
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
       <c r="I120" s="4"/>
+      <c r="J120" s="4"/>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4"/>
@@ -2067,6 +2516,7 @@
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
       <c r="I121" s="4"/>
+      <c r="J121" s="4"/>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4"/>
@@ -2076,6 +2526,7 @@
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
       <c r="I122" s="4"/>
+      <c r="J122" s="4"/>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4"/>
@@ -2085,6 +2536,7 @@
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
       <c r="I123" s="4"/>
+      <c r="J123" s="4"/>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4"/>
@@ -2094,6 +2546,7 @@
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
       <c r="I124" s="4"/>
+      <c r="J124" s="4"/>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4"/>
@@ -2103,6 +2556,7 @@
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="I125" s="4"/>
+      <c r="J125" s="4"/>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4"/>
@@ -2112,6 +2566,7 @@
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
       <c r="I126" s="4"/>
+      <c r="J126" s="4"/>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="4"/>
@@ -2121,6 +2576,7 @@
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
       <c r="I127" s="4"/>
+      <c r="J127" s="4"/>
     </row>
     <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4"/>
@@ -2130,6 +2586,7 @@
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
       <c r="I128" s="4"/>
+      <c r="J128" s="4"/>
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4"/>
@@ -2139,6 +2596,7 @@
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="I129" s="4"/>
+      <c r="J129" s="4"/>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4"/>
@@ -2148,6 +2606,7 @@
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
       <c r="I130" s="4"/>
+      <c r="J130" s="4"/>
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4"/>
@@ -2157,6 +2616,7 @@
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
       <c r="I131" s="4"/>
+      <c r="J131" s="4"/>
     </row>
     <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="4"/>
@@ -2166,6 +2626,7 @@
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
       <c r="I132" s="4"/>
+      <c r="J132" s="4"/>
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="4"/>
@@ -2175,6 +2636,7 @@
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
       <c r="I133" s="4"/>
+      <c r="J133" s="4"/>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4"/>
@@ -2184,6 +2646,7 @@
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
       <c r="I134" s="4"/>
+      <c r="J134" s="4"/>
     </row>
     <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4"/>
@@ -2193,6 +2656,7 @@
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
       <c r="I135" s="4"/>
+      <c r="J135" s="4"/>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4"/>
@@ -2202,6 +2666,7 @@
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
       <c r="I136" s="4"/>
+      <c r="J136" s="4"/>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4"/>
@@ -2211,6 +2676,7 @@
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
       <c r="I137" s="4"/>
+      <c r="J137" s="4"/>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4"/>
@@ -2220,6 +2686,7 @@
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
       <c r="I138" s="4"/>
+      <c r="J138" s="4"/>
     </row>
     <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4"/>
@@ -2229,6 +2696,7 @@
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
       <c r="I139" s="4"/>
+      <c r="J139" s="4"/>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="4"/>
@@ -2238,6 +2706,7 @@
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
       <c r="I140" s="4"/>
+      <c r="J140" s="4"/>
     </row>
     <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="4"/>
@@ -2247,6 +2716,7 @@
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
       <c r="I141" s="4"/>
+      <c r="J141" s="4"/>
     </row>
     <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="4"/>
@@ -2256,6 +2726,7 @@
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
       <c r="I142" s="4"/>
+      <c r="J142" s="4"/>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4"/>
@@ -2265,6 +2736,7 @@
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
       <c r="I143" s="4"/>
+      <c r="J143" s="4"/>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="4"/>
@@ -2274,6 +2746,7 @@
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
       <c r="I144" s="4"/>
+      <c r="J144" s="4"/>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="4"/>
@@ -2283,6 +2756,7 @@
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
       <c r="I145" s="4"/>
+      <c r="J145" s="4"/>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="4"/>
@@ -2292,6 +2766,7 @@
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
       <c r="I146" s="4"/>
+      <c r="J146" s="4"/>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="4"/>
@@ -2301,6 +2776,7 @@
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
       <c r="I147" s="4"/>
+      <c r="J147" s="4"/>
     </row>
     <row r="148" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="4"/>
@@ -2310,6 +2786,7 @@
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
       <c r="I148" s="4"/>
+      <c r="J148" s="4"/>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="4"/>
@@ -2319,6 +2796,7 @@
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
       <c r="I149" s="4"/>
+      <c r="J149" s="4"/>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="4"/>
@@ -2328,6 +2806,7 @@
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
       <c r="I150" s="4"/>
+      <c r="J150" s="4"/>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4"/>
@@ -2337,6 +2816,7 @@
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
       <c r="I151" s="4"/>
+      <c r="J151" s="4"/>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4"/>
@@ -2346,6 +2826,7 @@
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
       <c r="I152" s="4"/>
+      <c r="J152" s="4"/>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4"/>
@@ -2355,6 +2836,7 @@
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="I153" s="4"/>
+      <c r="J153" s="4"/>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4"/>
@@ -2364,6 +2846,7 @@
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
       <c r="I154" s="4"/>
+      <c r="J154" s="4"/>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4"/>
@@ -2373,6 +2856,7 @@
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
       <c r="I155" s="4"/>
+      <c r="J155" s="4"/>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4"/>
@@ -2382,6 +2866,7 @@
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
       <c r="I156" s="4"/>
+      <c r="J156" s="4"/>
     </row>
     <row r="157" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4"/>
@@ -2391,6 +2876,7 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="I157" s="4"/>
+      <c r="J157" s="4"/>
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4"/>
@@ -2400,6 +2886,7 @@
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
       <c r="I158" s="4"/>
+      <c r="J158" s="4"/>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4"/>
@@ -2409,6 +2896,7 @@
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
       <c r="I159" s="4"/>
+      <c r="J159" s="4"/>
     </row>
     <row r="160" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="4"/>
@@ -2418,6 +2906,7 @@
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
       <c r="I160" s="4"/>
+      <c r="J160" s="4"/>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4"/>
@@ -2427,6 +2916,7 @@
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
     </row>
     <row r="162" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4"/>
@@ -2436,6 +2926,7 @@
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
       <c r="I162" s="4"/>
+      <c r="J162" s="4"/>
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4"/>
@@ -2445,6 +2936,7 @@
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
       <c r="I163" s="4"/>
+      <c r="J163" s="4"/>
     </row>
     <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4"/>
@@ -2454,6 +2946,7 @@
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
       <c r="I164" s="4"/>
+      <c r="J164" s="4"/>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4"/>
@@ -2463,6 +2956,7 @@
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
       <c r="I165" s="4"/>
+      <c r="J165" s="4"/>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4"/>
@@ -2472,6 +2966,7 @@
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
       <c r="I166" s="4"/>
+      <c r="J166" s="4"/>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4"/>
@@ -2481,6 +2976,7 @@
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
       <c r="I167" s="4"/>
+      <c r="J167" s="4"/>
     </row>
     <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4"/>
@@ -2490,6 +2986,7 @@
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
       <c r="I168" s="4"/>
+      <c r="J168" s="4"/>
     </row>
     <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4"/>
@@ -2499,6 +2996,7 @@
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="I169" s="4"/>
+      <c r="J169" s="4"/>
     </row>
     <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4"/>
@@ -2508,6 +3006,7 @@
       <c r="E170" s="4"/>
       <c r="F170" s="4"/>
       <c r="I170" s="4"/>
+      <c r="J170" s="4"/>
     </row>
     <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="4"/>
@@ -2517,6 +3016,7 @@
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
       <c r="I171" s="4"/>
+      <c r="J171" s="4"/>
     </row>
     <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4"/>
@@ -2526,6 +3026,7 @@
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
       <c r="I172" s="4"/>
+      <c r="J172" s="4"/>
     </row>
     <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4"/>
@@ -2535,6 +3036,7 @@
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
       <c r="I173" s="4"/>
+      <c r="J173" s="4"/>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4"/>
@@ -2544,6 +3046,7 @@
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
       <c r="I174" s="4"/>
+      <c r="J174" s="4"/>
     </row>
     <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4"/>
@@ -2553,6 +3056,7 @@
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
       <c r="I175" s="4"/>
+      <c r="J175" s="4"/>
     </row>
     <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4"/>
@@ -2562,6 +3066,7 @@
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
       <c r="I176" s="4"/>
+      <c r="J176" s="4"/>
     </row>
     <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4"/>
@@ -2571,6 +3076,7 @@
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="I177" s="4"/>
+      <c r="J177" s="4"/>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4"/>
@@ -2580,6 +3086,7 @@
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
       <c r="I178" s="4"/>
+      <c r="J178" s="4"/>
     </row>
     <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4"/>
@@ -2589,6 +3096,7 @@
       <c r="E179" s="4"/>
       <c r="F179" s="4"/>
       <c r="I179" s="4"/>
+      <c r="J179" s="4"/>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4"/>
@@ -2598,6 +3106,7 @@
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
       <c r="I180" s="4"/>
+      <c r="J180" s="4"/>
     </row>
     <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4"/>
@@ -2607,6 +3116,7 @@
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
       <c r="I181" s="4"/>
+      <c r="J181" s="4"/>
     </row>
     <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4"/>
@@ -2616,6 +3126,7 @@
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
       <c r="I182" s="4"/>
+      <c r="J182" s="4"/>
     </row>
     <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4"/>
@@ -2625,6 +3136,7 @@
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
       <c r="I183" s="4"/>
+      <c r="J183" s="4"/>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4"/>
@@ -2634,6 +3146,7 @@
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
       <c r="I184" s="4"/>
+      <c r="J184" s="4"/>
     </row>
     <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4"/>
@@ -2643,6 +3156,7 @@
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="I185" s="4"/>
+      <c r="J185" s="4"/>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="4"/>
@@ -2652,6 +3166,7 @@
       <c r="E186" s="4"/>
       <c r="F186" s="4"/>
       <c r="I186" s="4"/>
+      <c r="J186" s="4"/>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4"/>
@@ -2661,6 +3176,7 @@
       <c r="E187" s="4"/>
       <c r="F187" s="4"/>
       <c r="I187" s="4"/>
+      <c r="J187" s="4"/>
     </row>
     <row r="188" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="4"/>
@@ -2670,6 +3186,7 @@
       <c r="E188" s="4"/>
       <c r="F188" s="4"/>
       <c r="I188" s="4"/>
+      <c r="J188" s="4"/>
     </row>
     <row r="189" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="4"/>
@@ -2679,6 +3196,7 @@
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
       <c r="I189" s="4"/>
+      <c r="J189" s="4"/>
     </row>
     <row r="190" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4"/>
@@ -2688,6 +3206,7 @@
       <c r="E190" s="4"/>
       <c r="F190" s="4"/>
       <c r="I190" s="4"/>
+      <c r="J190" s="4"/>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4"/>
@@ -2697,6 +3216,7 @@
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
       <c r="I191" s="4"/>
+      <c r="J191" s="4"/>
     </row>
     <row r="192" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4"/>
@@ -2706,6 +3226,7 @@
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
       <c r="I192" s="4"/>
+      <c r="J192" s="4"/>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4"/>
@@ -2715,6 +3236,7 @@
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
       <c r="I193" s="4"/>
+      <c r="J193" s="4"/>
     </row>
     <row r="194" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="4"/>
@@ -2724,6 +3246,7 @@
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
       <c r="I194" s="4"/>
+      <c r="J194" s="4"/>
     </row>
     <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="4"/>
@@ -2733,6 +3256,7 @@
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
       <c r="I195" s="4"/>
+      <c r="J195" s="4"/>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="4"/>
@@ -2742,6 +3266,7 @@
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
       <c r="I196" s="4"/>
+      <c r="J196" s="4"/>
     </row>
     <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="4"/>
@@ -2751,6 +3276,7 @@
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
       <c r="I197" s="4"/>
+      <c r="J197" s="4"/>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="4"/>
@@ -2760,6 +3286,7 @@
       <c r="E198" s="4"/>
       <c r="F198" s="4"/>
       <c r="I198" s="4"/>
+      <c r="J198" s="4"/>
     </row>
     <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="4"/>
@@ -2769,6 +3296,7 @@
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
       <c r="I199" s="4"/>
+      <c r="J199" s="4"/>
     </row>
     <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="4"/>
@@ -2778,6 +3306,7 @@
       <c r="E200" s="4"/>
       <c r="F200" s="4"/>
       <c r="I200" s="4"/>
+      <c r="J200" s="4"/>
     </row>
     <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="4"/>
@@ -2787,6 +3316,7 @@
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
       <c r="I201" s="4"/>
+      <c r="J201" s="4"/>
     </row>
     <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="4"/>
@@ -2796,6 +3326,7 @@
       <c r="E202" s="4"/>
       <c r="F202" s="4"/>
       <c r="I202" s="4"/>
+      <c r="J202" s="4"/>
     </row>
     <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="4"/>
@@ -2805,6 +3336,7 @@
       <c r="E203" s="4"/>
       <c r="F203" s="4"/>
       <c r="I203" s="4"/>
+      <c r="J203" s="4"/>
     </row>
     <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="4"/>
@@ -2814,6 +3346,7 @@
       <c r="E204" s="4"/>
       <c r="F204" s="4"/>
       <c r="I204" s="4"/>
+      <c r="J204" s="4"/>
     </row>
     <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="4"/>
@@ -2823,6 +3356,7 @@
       <c r="E205" s="4"/>
       <c r="F205" s="4"/>
       <c r="I205" s="4"/>
+      <c r="J205" s="4"/>
     </row>
     <row r="206" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="4"/>
@@ -2832,6 +3366,7 @@
       <c r="E206" s="4"/>
       <c r="F206" s="4"/>
       <c r="I206" s="4"/>
+      <c r="J206" s="4"/>
     </row>
     <row r="207" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="4"/>
@@ -2841,6 +3376,7 @@
       <c r="E207" s="4"/>
       <c r="F207" s="4"/>
       <c r="I207" s="4"/>
+      <c r="J207" s="4"/>
     </row>
     <row r="208" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="4"/>
@@ -2850,6 +3386,7 @@
       <c r="E208" s="4"/>
       <c r="F208" s="4"/>
       <c r="I208" s="4"/>
+      <c r="J208" s="4"/>
     </row>
     <row r="209" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="4"/>
@@ -2859,6 +3396,7 @@
       <c r="E209" s="4"/>
       <c r="F209" s="4"/>
       <c r="I209" s="4"/>
+      <c r="J209" s="4"/>
     </row>
     <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="4"/>
@@ -2868,6 +3406,7 @@
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
       <c r="I210" s="4"/>
+      <c r="J210" s="4"/>
     </row>
     <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="4"/>
@@ -2877,6 +3416,7 @@
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
       <c r="I211" s="4"/>
+      <c r="J211" s="4"/>
     </row>
     <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="4"/>
@@ -2886,6 +3426,7 @@
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
       <c r="I212" s="4"/>
+      <c r="J212" s="4"/>
     </row>
     <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="4"/>
@@ -2895,6 +3436,7 @@
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
       <c r="I213" s="4"/>
+      <c r="J213" s="4"/>
     </row>
     <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="4"/>
@@ -2904,6 +3446,7 @@
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
       <c r="I214" s="4"/>
+      <c r="J214" s="4"/>
     </row>
     <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="4"/>
@@ -2913,6 +3456,7 @@
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
       <c r="I215" s="4"/>
+      <c r="J215" s="4"/>
     </row>
     <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="4"/>
@@ -2922,6 +3466,7 @@
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
       <c r="I216" s="4"/>
+      <c r="J216" s="4"/>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="4"/>
@@ -2931,6 +3476,7 @@
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
       <c r="I217" s="4"/>
+      <c r="J217" s="4"/>
     </row>
     <row r="218" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="4"/>
@@ -2940,6 +3486,7 @@
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
       <c r="I218" s="4"/>
+      <c r="J218" s="4"/>
     </row>
     <row r="219" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="4"/>
@@ -2949,6 +3496,7 @@
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
       <c r="I219" s="4"/>
+      <c r="J219" s="4"/>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="4"/>
@@ -2958,6 +3506,7 @@
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
       <c r="I220" s="4"/>
+      <c r="J220" s="4"/>
     </row>
     <row r="221" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="4"/>
@@ -2967,6 +3516,7 @@
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
       <c r="I221" s="4"/>
+      <c r="J221" s="4"/>
     </row>
     <row r="222" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="4"/>
@@ -2976,6 +3526,7 @@
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
       <c r="I222" s="4"/>
+      <c r="J222" s="4"/>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="4"/>
@@ -2985,6 +3536,7 @@
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
       <c r="I223" s="4"/>
+      <c r="J223" s="4"/>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="4"/>
@@ -2994,6 +3546,7 @@
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
       <c r="I224" s="4"/>
+      <c r="J224" s="4"/>
     </row>
     <row r="225" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="4"/>
@@ -3003,6 +3556,7 @@
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
       <c r="I225" s="4"/>
+      <c r="J225" s="4"/>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="4"/>
@@ -3012,6 +3566,7 @@
       <c r="E226" s="4"/>
       <c r="F226" s="4"/>
       <c r="I226" s="4"/>
+      <c r="J226" s="4"/>
     </row>
     <row r="227" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="4"/>
@@ -3021,6 +3576,7 @@
       <c r="E227" s="4"/>
       <c r="F227" s="4"/>
       <c r="I227" s="4"/>
+      <c r="J227" s="4"/>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="4"/>
@@ -3030,6 +3586,7 @@
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
       <c r="I228" s="4"/>
+      <c r="J228" s="4"/>
     </row>
     <row r="229" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="4"/>
@@ -3039,6 +3596,7 @@
       <c r="E229" s="4"/>
       <c r="F229" s="4"/>
       <c r="I229" s="4"/>
+      <c r="J229" s="4"/>
     </row>
     <row r="230" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="4"/>
@@ -3048,6 +3606,7 @@
       <c r="E230" s="4"/>
       <c r="F230" s="4"/>
       <c r="I230" s="4"/>
+      <c r="J230" s="4"/>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="4"/>
@@ -3057,6 +3616,7 @@
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
       <c r="I231" s="4"/>
+      <c r="J231" s="4"/>
     </row>
     <row r="232" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="4"/>
@@ -3066,6 +3626,7 @@
       <c r="E232" s="4"/>
       <c r="F232" s="4"/>
       <c r="I232" s="4"/>
+      <c r="J232" s="4"/>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="4"/>
@@ -3075,6 +3636,7 @@
       <c r="E233" s="4"/>
       <c r="F233" s="4"/>
       <c r="I233" s="4"/>
+      <c r="J233" s="4"/>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="4"/>
@@ -3084,6 +3646,7 @@
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
       <c r="I234" s="4"/>
+      <c r="J234" s="4"/>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="4"/>
@@ -3093,6 +3656,7 @@
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
       <c r="I235" s="4"/>
+      <c r="J235" s="4"/>
     </row>
     <row r="236" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="4"/>
@@ -3102,6 +3666,7 @@
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
       <c r="I236" s="4"/>
+      <c r="J236" s="4"/>
     </row>
     <row r="237" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="4"/>
@@ -3111,6 +3676,7 @@
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
       <c r="I237" s="4"/>
+      <c r="J237" s="4"/>
     </row>
     <row r="238" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="4"/>
@@ -3120,6 +3686,7 @@
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
       <c r="I238" s="4"/>
+      <c r="J238" s="4"/>
     </row>
     <row r="239" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="4"/>
@@ -3129,6 +3696,7 @@
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
       <c r="I239" s="4"/>
+      <c r="J239" s="4"/>
     </row>
     <row r="240" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="4"/>
@@ -3138,6 +3706,7 @@
       <c r="E240" s="4"/>
       <c r="F240" s="4"/>
       <c r="I240" s="4"/>
+      <c r="J240" s="4"/>
     </row>
     <row r="241" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="4"/>
@@ -3147,6 +3716,7 @@
       <c r="E241" s="4"/>
       <c r="F241" s="4"/>
       <c r="I241" s="4"/>
+      <c r="J241" s="4"/>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="4"/>
@@ -3156,6 +3726,7 @@
       <c r="E242" s="4"/>
       <c r="F242" s="4"/>
       <c r="I242" s="4"/>
+      <c r="J242" s="4"/>
     </row>
     <row r="243" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="4"/>
@@ -3165,6 +3736,7 @@
       <c r="E243" s="4"/>
       <c r="F243" s="4"/>
       <c r="I243" s="4"/>
+      <c r="J243" s="4"/>
     </row>
     <row r="244" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="4"/>
@@ -3174,6 +3746,7 @@
       <c r="E244" s="4"/>
       <c r="F244" s="4"/>
       <c r="I244" s="4"/>
+      <c r="J244" s="4"/>
     </row>
     <row r="245" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="4"/>
@@ -3183,6 +3756,7 @@
       <c r="E245" s="4"/>
       <c r="F245" s="4"/>
       <c r="I245" s="4"/>
+      <c r="J245" s="4"/>
     </row>
     <row r="246" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="4"/>
@@ -3192,6 +3766,7 @@
       <c r="E246" s="4"/>
       <c r="F246" s="4"/>
       <c r="I246" s="4"/>
+      <c r="J246" s="4"/>
     </row>
     <row r="247" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="4"/>
@@ -3201,6 +3776,7 @@
       <c r="E247" s="4"/>
       <c r="F247" s="4"/>
       <c r="I247" s="4"/>
+      <c r="J247" s="4"/>
     </row>
     <row r="248" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="4"/>
@@ -3210,6 +3786,7 @@
       <c r="E248" s="4"/>
       <c r="F248" s="4"/>
       <c r="I248" s="4"/>
+      <c r="J248" s="4"/>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="4"/>
@@ -3219,6 +3796,7 @@
       <c r="E249" s="4"/>
       <c r="F249" s="4"/>
       <c r="I249" s="4"/>
+      <c r="J249" s="4"/>
     </row>
     <row r="250" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="4"/>
@@ -3228,6 +3806,7 @@
       <c r="E250" s="4"/>
       <c r="F250" s="4"/>
       <c r="I250" s="4"/>
+      <c r="J250" s="4"/>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="4"/>
@@ -3237,6 +3816,7 @@
       <c r="E251" s="4"/>
       <c r="F251" s="4"/>
       <c r="I251" s="4"/>
+      <c r="J251" s="4"/>
     </row>
     <row r="252" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="4"/>
@@ -3246,6 +3826,7 @@
       <c r="E252" s="4"/>
       <c r="F252" s="4"/>
       <c r="I252" s="4"/>
+      <c r="J252" s="4"/>
     </row>
     <row r="253" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="4"/>
@@ -3255,6 +3836,7 @@
       <c r="E253" s="4"/>
       <c r="F253" s="4"/>
       <c r="I253" s="4"/>
+      <c r="J253" s="4"/>
     </row>
     <row r="254" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="4"/>
@@ -3264,6 +3846,7 @@
       <c r="E254" s="4"/>
       <c r="F254" s="4"/>
       <c r="I254" s="4"/>
+      <c r="J254" s="4"/>
     </row>
     <row r="255" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="4"/>
@@ -3273,6 +3856,7 @@
       <c r="E255" s="4"/>
       <c r="F255" s="4"/>
       <c r="I255" s="4"/>
+      <c r="J255" s="4"/>
     </row>
     <row r="256" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="4"/>
@@ -3282,6 +3866,7 @@
       <c r="E256" s="4"/>
       <c r="F256" s="4"/>
       <c r="I256" s="4"/>
+      <c r="J256" s="4"/>
     </row>
     <row r="257" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="4"/>
@@ -3291,6 +3876,7 @@
       <c r="E257" s="4"/>
       <c r="F257" s="4"/>
       <c r="I257" s="4"/>
+      <c r="J257" s="4"/>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="4"/>
@@ -3300,6 +3886,7 @@
       <c r="E258" s="4"/>
       <c r="F258" s="4"/>
       <c r="I258" s="4"/>
+      <c r="J258" s="4"/>
     </row>
     <row r="259" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="4"/>
@@ -3309,6 +3896,7 @@
       <c r="E259" s="4"/>
       <c r="F259" s="4"/>
       <c r="I259" s="4"/>
+      <c r="J259" s="4"/>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="4"/>
@@ -3318,6 +3906,7 @@
       <c r="E260" s="4"/>
       <c r="F260" s="4"/>
       <c r="I260" s="4"/>
+      <c r="J260" s="4"/>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="4"/>
@@ -3327,6 +3916,7 @@
       <c r="E261" s="4"/>
       <c r="F261" s="4"/>
       <c r="I261" s="4"/>
+      <c r="J261" s="4"/>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="4"/>
@@ -3336,6 +3926,7 @@
       <c r="E262" s="4"/>
       <c r="F262" s="4"/>
       <c r="I262" s="4"/>
+      <c r="J262" s="4"/>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="4"/>
@@ -3345,6 +3936,7 @@
       <c r="E263" s="4"/>
       <c r="F263" s="4"/>
       <c r="I263" s="4"/>
+      <c r="J263" s="4"/>
     </row>
     <row r="264" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="4"/>
@@ -3354,6 +3946,7 @@
       <c r="E264" s="4"/>
       <c r="F264" s="4"/>
       <c r="I264" s="4"/>
+      <c r="J264" s="4"/>
     </row>
     <row r="265" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="4"/>
@@ -3363,6 +3956,7 @@
       <c r="E265" s="4"/>
       <c r="F265" s="4"/>
       <c r="I265" s="4"/>
+      <c r="J265" s="4"/>
     </row>
     <row r="266" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="4"/>
@@ -3372,6 +3966,7 @@
       <c r="E266" s="4"/>
       <c r="F266" s="4"/>
       <c r="I266" s="4"/>
+      <c r="J266" s="4"/>
     </row>
     <row r="267" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="4"/>
@@ -3381,6 +3976,7 @@
       <c r="E267" s="4"/>
       <c r="F267" s="4"/>
       <c r="I267" s="4"/>
+      <c r="J267" s="4"/>
     </row>
     <row r="268" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="4"/>
@@ -3390,6 +3986,7 @@
       <c r="E268" s="4"/>
       <c r="F268" s="4"/>
       <c r="I268" s="4"/>
+      <c r="J268" s="4"/>
     </row>
     <row r="269" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="4"/>
@@ -3399,6 +3996,7 @@
       <c r="E269" s="4"/>
       <c r="F269" s="4"/>
       <c r="I269" s="4"/>
+      <c r="J269" s="4"/>
     </row>
     <row r="270" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="4"/>
@@ -3408,6 +4006,7 @@
       <c r="E270" s="4"/>
       <c r="F270" s="4"/>
       <c r="I270" s="4"/>
+      <c r="J270" s="4"/>
     </row>
     <row r="271" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="4"/>
@@ -3417,6 +4016,7 @@
       <c r="E271" s="4"/>
       <c r="F271" s="4"/>
       <c r="I271" s="4"/>
+      <c r="J271" s="4"/>
     </row>
     <row r="272" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="4"/>
@@ -3426,6 +4026,7 @@
       <c r="E272" s="4"/>
       <c r="F272" s="4"/>
       <c r="I272" s="4"/>
+      <c r="J272" s="4"/>
     </row>
     <row r="273" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="4"/>
@@ -3435,6 +4036,7 @@
       <c r="E273" s="4"/>
       <c r="F273" s="4"/>
       <c r="I273" s="4"/>
+      <c r="J273" s="4"/>
     </row>
     <row r="274" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="4"/>
@@ -3444,6 +4046,7 @@
       <c r="E274" s="4"/>
       <c r="F274" s="4"/>
       <c r="I274" s="4"/>
+      <c r="J274" s="4"/>
     </row>
     <row r="275" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="4"/>
@@ -3453,6 +4056,7 @@
       <c r="E275" s="4"/>
       <c r="F275" s="4"/>
       <c r="I275" s="4"/>
+      <c r="J275" s="4"/>
     </row>
     <row r="276" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="4"/>
@@ -3462,6 +4066,7 @@
       <c r="E276" s="4"/>
       <c r="F276" s="4"/>
       <c r="I276" s="4"/>
+      <c r="J276" s="4"/>
     </row>
     <row r="277" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="4"/>
@@ -3471,6 +4076,7 @@
       <c r="E277" s="4"/>
       <c r="F277" s="4"/>
       <c r="I277" s="4"/>
+      <c r="J277" s="4"/>
     </row>
     <row r="278" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="4"/>
@@ -3480,6 +4086,7 @@
       <c r="E278" s="4"/>
       <c r="F278" s="4"/>
       <c r="I278" s="4"/>
+      <c r="J278" s="4"/>
     </row>
     <row r="279" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="4"/>
@@ -3489,6 +4096,7 @@
       <c r="E279" s="4"/>
       <c r="F279" s="4"/>
       <c r="I279" s="4"/>
+      <c r="J279" s="4"/>
     </row>
     <row r="280" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="4"/>
@@ -3498,6 +4106,7 @@
       <c r="E280" s="4"/>
       <c r="F280" s="4"/>
       <c r="I280" s="4"/>
+      <c r="J280" s="4"/>
     </row>
     <row r="281" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="4"/>
@@ -3507,6 +4116,7 @@
       <c r="E281" s="4"/>
       <c r="F281" s="4"/>
       <c r="I281" s="4"/>
+      <c r="J281" s="4"/>
     </row>
     <row r="282" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="4"/>
@@ -3516,6 +4126,7 @@
       <c r="E282" s="4"/>
       <c r="F282" s="4"/>
       <c r="I282" s="4"/>
+      <c r="J282" s="4"/>
     </row>
     <row r="283" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="4"/>
@@ -3525,6 +4136,7 @@
       <c r="E283" s="4"/>
       <c r="F283" s="4"/>
       <c r="I283" s="4"/>
+      <c r="J283" s="4"/>
     </row>
     <row r="284" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="4"/>
@@ -3534,6 +4146,7 @@
       <c r="E284" s="4"/>
       <c r="F284" s="4"/>
       <c r="I284" s="4"/>
+      <c r="J284" s="4"/>
     </row>
     <row r="285" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="4"/>
@@ -3543,6 +4156,7 @@
       <c r="E285" s="4"/>
       <c r="F285" s="4"/>
       <c r="I285" s="4"/>
+      <c r="J285" s="4"/>
     </row>
     <row r="286" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="4"/>
@@ -3552,6 +4166,7 @@
       <c r="E286" s="4"/>
       <c r="F286" s="4"/>
       <c r="I286" s="4"/>
+      <c r="J286" s="4"/>
     </row>
     <row r="287" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="4"/>
@@ -3561,6 +4176,7 @@
       <c r="E287" s="4"/>
       <c r="F287" s="4"/>
       <c r="I287" s="4"/>
+      <c r="J287" s="4"/>
     </row>
     <row r="288" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="4"/>
@@ -3570,6 +4186,7 @@
       <c r="E288" s="4"/>
       <c r="F288" s="4"/>
       <c r="I288" s="4"/>
+      <c r="J288" s="4"/>
     </row>
     <row r="289" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="4"/>
@@ -3579,6 +4196,7 @@
       <c r="E289" s="4"/>
       <c r="F289" s="4"/>
       <c r="I289" s="4"/>
+      <c r="J289" s="4"/>
     </row>
     <row r="290" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="4"/>
@@ -3588,6 +4206,7 @@
       <c r="E290" s="4"/>
       <c r="F290" s="4"/>
       <c r="I290" s="4"/>
+      <c r="J290" s="4"/>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="4"/>
@@ -3597,6 +4216,7 @@
       <c r="E291" s="4"/>
       <c r="F291" s="4"/>
       <c r="I291" s="4"/>
+      <c r="J291" s="4"/>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="4"/>
@@ -3606,6 +4226,7 @@
       <c r="E292" s="4"/>
       <c r="F292" s="4"/>
       <c r="I292" s="4"/>
+      <c r="J292" s="4"/>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="4"/>
@@ -3615,6 +4236,7 @@
       <c r="E293" s="4"/>
       <c r="F293" s="4"/>
       <c r="I293" s="4"/>
+      <c r="J293" s="4"/>
     </row>
     <row r="294" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="4"/>
@@ -3624,6 +4246,7 @@
       <c r="E294" s="4"/>
       <c r="F294" s="4"/>
       <c r="I294" s="4"/>
+      <c r="J294" s="4"/>
     </row>
     <row r="295" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="4"/>
@@ -3633,6 +4256,7 @@
       <c r="E295" s="4"/>
       <c r="F295" s="4"/>
       <c r="I295" s="4"/>
+      <c r="J295" s="4"/>
     </row>
     <row r="296" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A296" s="4"/>
@@ -3642,6 +4266,7 @@
       <c r="E296" s="4"/>
       <c r="F296" s="4"/>
       <c r="I296" s="4"/>
+      <c r="J296" s="4"/>
     </row>
     <row r="297" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="4"/>
@@ -3651,6 +4276,7 @@
       <c r="E297" s="4"/>
       <c r="F297" s="4"/>
       <c r="I297" s="4"/>
+      <c r="J297" s="4"/>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="4"/>
@@ -3660,6 +4286,7 @@
       <c r="E298" s="4"/>
       <c r="F298" s="4"/>
       <c r="I298" s="4"/>
+      <c r="J298" s="4"/>
     </row>
     <row r="299" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="4"/>
@@ -3669,6 +4296,7 @@
       <c r="E299" s="4"/>
       <c r="F299" s="4"/>
       <c r="I299" s="4"/>
+      <c r="J299" s="4"/>
     </row>
     <row r="300" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="4"/>
@@ -3678,6 +4306,7 @@
       <c r="E300" s="4"/>
       <c r="F300" s="4"/>
       <c r="I300" s="4"/>
+      <c r="J300" s="4"/>
     </row>
     <row r="301" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="4"/>
@@ -3687,6 +4316,7 @@
       <c r="E301" s="4"/>
       <c r="F301" s="4"/>
       <c r="I301" s="4"/>
+      <c r="J301" s="4"/>
     </row>
     <row r="302" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="4"/>
@@ -3696,6 +4326,7 @@
       <c r="E302" s="4"/>
       <c r="F302" s="4"/>
       <c r="I302" s="4"/>
+      <c r="J302" s="4"/>
     </row>
     <row r="303" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="4"/>
@@ -3705,6 +4336,7 @@
       <c r="E303" s="4"/>
       <c r="F303" s="4"/>
       <c r="I303" s="4"/>
+      <c r="J303" s="4"/>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="4"/>
@@ -3714,6 +4346,7 @@
       <c r="E304" s="4"/>
       <c r="F304" s="4"/>
       <c r="I304" s="4"/>
+      <c r="J304" s="4"/>
     </row>
     <row r="305" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A305" s="4"/>
@@ -3723,6 +4356,7 @@
       <c r="E305" s="4"/>
       <c r="F305" s="4"/>
       <c r="I305" s="4"/>
+      <c r="J305" s="4"/>
     </row>
     <row r="306" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="4"/>
@@ -3732,6 +4366,7 @@
       <c r="E306" s="4"/>
       <c r="F306" s="4"/>
       <c r="I306" s="4"/>
+      <c r="J306" s="4"/>
     </row>
     <row r="307" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A307" s="4"/>
@@ -3741,6 +4376,7 @@
       <c r="E307" s="4"/>
       <c r="F307" s="4"/>
       <c r="I307" s="4"/>
+      <c r="J307" s="4"/>
     </row>
     <row r="308" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="4"/>
@@ -3750,6 +4386,7 @@
       <c r="E308" s="4"/>
       <c r="F308" s="4"/>
       <c r="I308" s="4"/>
+      <c r="J308" s="4"/>
     </row>
     <row r="309" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="4"/>
@@ -3759,6 +4396,7 @@
       <c r="E309" s="4"/>
       <c r="F309" s="4"/>
       <c r="I309" s="4"/>
+      <c r="J309" s="4"/>
     </row>
     <row r="310" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A310" s="4"/>
@@ -3768,6 +4406,7 @@
       <c r="E310" s="4"/>
       <c r="F310" s="4"/>
       <c r="I310" s="4"/>
+      <c r="J310" s="4"/>
     </row>
     <row r="311" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="4"/>
@@ -3777,6 +4416,7 @@
       <c r="E311" s="4"/>
       <c r="F311" s="4"/>
       <c r="I311" s="4"/>
+      <c r="J311" s="4"/>
     </row>
     <row r="312" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="4"/>
@@ -3786,6 +4426,7 @@
       <c r="E312" s="4"/>
       <c r="F312" s="4"/>
       <c r="I312" s="4"/>
+      <c r="J312" s="4"/>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="4"/>
@@ -3795,6 +4436,7 @@
       <c r="E313" s="4"/>
       <c r="F313" s="4"/>
       <c r="I313" s="4"/>
+      <c r="J313" s="4"/>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="4"/>
@@ -3804,6 +4446,7 @@
       <c r="E314" s="4"/>
       <c r="F314" s="4"/>
       <c r="I314" s="4"/>
+      <c r="J314" s="4"/>
     </row>
     <row r="315" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="4"/>
@@ -3813,6 +4456,7 @@
       <c r="E315" s="4"/>
       <c r="F315" s="4"/>
       <c r="I315" s="4"/>
+      <c r="J315" s="4"/>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A316" s="4"/>
@@ -3822,6 +4466,7 @@
       <c r="E316" s="4"/>
       <c r="F316" s="4"/>
       <c r="I316" s="4"/>
+      <c r="J316" s="4"/>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="4"/>
@@ -3831,6 +4476,7 @@
       <c r="E317" s="4"/>
       <c r="F317" s="4"/>
       <c r="I317" s="4"/>
+      <c r="J317" s="4"/>
     </row>
     <row r="318" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="4"/>
@@ -3840,6 +4486,7 @@
       <c r="E318" s="4"/>
       <c r="F318" s="4"/>
       <c r="I318" s="4"/>
+      <c r="J318" s="4"/>
     </row>
     <row r="319" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="4"/>
@@ -3849,6 +4496,7 @@
       <c r="E319" s="4"/>
       <c r="F319" s="4"/>
       <c r="I319" s="4"/>
+      <c r="J319" s="4"/>
     </row>
     <row r="320" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="4"/>
@@ -3858,6 +4506,7 @@
       <c r="E320" s="4"/>
       <c r="F320" s="4"/>
       <c r="I320" s="4"/>
+      <c r="J320" s="4"/>
     </row>
     <row r="321" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="4"/>
@@ -3867,6 +4516,7 @@
       <c r="E321" s="4"/>
       <c r="F321" s="4"/>
       <c r="I321" s="4"/>
+      <c r="J321" s="4"/>
     </row>
     <row r="322" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="4"/>
@@ -3876,6 +4526,7 @@
       <c r="E322" s="4"/>
       <c r="F322" s="4"/>
       <c r="I322" s="4"/>
+      <c r="J322" s="4"/>
     </row>
     <row r="323" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="4"/>
@@ -3885,6 +4536,7 @@
       <c r="E323" s="4"/>
       <c r="F323" s="4"/>
       <c r="I323" s="4"/>
+      <c r="J323" s="4"/>
     </row>
     <row r="324" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A324" s="4"/>
@@ -3894,6 +4546,7 @@
       <c r="E324" s="4"/>
       <c r="F324" s="4"/>
       <c r="I324" s="4"/>
+      <c r="J324" s="4"/>
     </row>
     <row r="325" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A325" s="4"/>
@@ -3903,6 +4556,7 @@
       <c r="E325" s="4"/>
       <c r="F325" s="4"/>
       <c r="I325" s="4"/>
+      <c r="J325" s="4"/>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="4"/>
@@ -3912,6 +4566,7 @@
       <c r="E326" s="4"/>
       <c r="F326" s="4"/>
       <c r="I326" s="4"/>
+      <c r="J326" s="4"/>
     </row>
     <row r="327" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="4"/>
@@ -3921,6 +4576,7 @@
       <c r="E327" s="4"/>
       <c r="F327" s="4"/>
       <c r="I327" s="4"/>
+      <c r="J327" s="4"/>
     </row>
     <row r="328" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A328" s="4"/>
@@ -3930,6 +4586,7 @@
       <c r="E328" s="4"/>
       <c r="F328" s="4"/>
       <c r="I328" s="4"/>
+      <c r="J328" s="4"/>
     </row>
     <row r="329" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="4"/>
@@ -3939,6 +4596,7 @@
       <c r="E329" s="4"/>
       <c r="F329" s="4"/>
       <c r="I329" s="4"/>
+      <c r="J329" s="4"/>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="4"/>
@@ -3948,6 +4606,7 @@
       <c r="E330" s="4"/>
       <c r="F330" s="4"/>
       <c r="I330" s="4"/>
+      <c r="J330" s="4"/>
     </row>
     <row r="331" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="4"/>
@@ -3957,6 +4616,7 @@
       <c r="E331" s="4"/>
       <c r="F331" s="4"/>
       <c r="I331" s="4"/>
+      <c r="J331" s="4"/>
     </row>
     <row r="332" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="4"/>
@@ -3966,6 +4626,7 @@
       <c r="E332" s="4"/>
       <c r="F332" s="4"/>
       <c r="I332" s="4"/>
+      <c r="J332" s="4"/>
     </row>
     <row r="333" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A333" s="4"/>
@@ -3975,6 +4636,7 @@
       <c r="E333" s="4"/>
       <c r="F333" s="4"/>
       <c r="I333" s="4"/>
+      <c r="J333" s="4"/>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="4"/>
@@ -3984,6 +4646,7 @@
       <c r="E334" s="4"/>
       <c r="F334" s="4"/>
       <c r="I334" s="4"/>
+      <c r="J334" s="4"/>
     </row>
     <row r="335" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="4"/>
@@ -3993,6 +4656,7 @@
       <c r="E335" s="4"/>
       <c r="F335" s="4"/>
       <c r="I335" s="4"/>
+      <c r="J335" s="4"/>
     </row>
     <row r="336" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A336" s="4"/>
@@ -4002,6 +4666,7 @@
       <c r="E336" s="4"/>
       <c r="F336" s="4"/>
       <c r="I336" s="4"/>
+      <c r="J336" s="4"/>
     </row>
     <row r="337" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A337" s="4"/>
@@ -4011,6 +4676,7 @@
       <c r="E337" s="4"/>
       <c r="F337" s="4"/>
       <c r="I337" s="4"/>
+      <c r="J337" s="4"/>
     </row>
     <row r="338" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="4"/>
@@ -4020,6 +4686,7 @@
       <c r="E338" s="4"/>
       <c r="F338" s="4"/>
       <c r="I338" s="4"/>
+      <c r="J338" s="4"/>
     </row>
     <row r="339" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="4"/>
@@ -4029,6 +4696,7 @@
       <c r="E339" s="4"/>
       <c r="F339" s="4"/>
       <c r="I339" s="4"/>
+      <c r="J339" s="4"/>
     </row>
     <row r="340" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="4"/>
@@ -4038,6 +4706,7 @@
       <c r="E340" s="4"/>
       <c r="F340" s="4"/>
       <c r="I340" s="4"/>
+      <c r="J340" s="4"/>
     </row>
     <row r="341" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="4"/>
@@ -4047,6 +4716,7 @@
       <c r="E341" s="4"/>
       <c r="F341" s="4"/>
       <c r="I341" s="4"/>
+      <c r="J341" s="4"/>
     </row>
     <row r="342" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="4"/>
@@ -4056,6 +4726,7 @@
       <c r="E342" s="4"/>
       <c r="F342" s="4"/>
       <c r="I342" s="4"/>
+      <c r="J342" s="4"/>
     </row>
     <row r="343" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="4"/>
@@ -4065,6 +4736,7 @@
       <c r="E343" s="4"/>
       <c r="F343" s="4"/>
       <c r="I343" s="4"/>
+      <c r="J343" s="4"/>
     </row>
     <row r="344" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="4"/>
@@ -4074,6 +4746,7 @@
       <c r="E344" s="4"/>
       <c r="F344" s="4"/>
       <c r="I344" s="4"/>
+      <c r="J344" s="4"/>
     </row>
     <row r="345" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A345" s="4"/>
@@ -4083,6 +4756,7 @@
       <c r="E345" s="4"/>
       <c r="F345" s="4"/>
       <c r="I345" s="4"/>
+      <c r="J345" s="4"/>
     </row>
     <row r="346" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A346" s="4"/>
@@ -4092,6 +4766,7 @@
       <c r="E346" s="4"/>
       <c r="F346" s="4"/>
       <c r="I346" s="4"/>
+      <c r="J346" s="4"/>
     </row>
     <row r="347" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A347" s="4"/>
@@ -4101,6 +4776,7 @@
       <c r="E347" s="4"/>
       <c r="F347" s="4"/>
       <c r="I347" s="4"/>
+      <c r="J347" s="4"/>
     </row>
     <row r="348" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="4"/>
@@ -4110,6 +4786,7 @@
       <c r="E348" s="4"/>
       <c r="F348" s="4"/>
       <c r="I348" s="4"/>
+      <c r="J348" s="4"/>
     </row>
     <row r="349" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A349" s="4"/>
@@ -4119,6 +4796,7 @@
       <c r="E349" s="4"/>
       <c r="F349" s="4"/>
       <c r="I349" s="4"/>
+      <c r="J349" s="4"/>
     </row>
     <row r="350" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A350" s="4"/>
@@ -4128,6 +4806,7 @@
       <c r="E350" s="4"/>
       <c r="F350" s="4"/>
       <c r="I350" s="4"/>
+      <c r="J350" s="4"/>
     </row>
     <row r="351" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="4"/>
@@ -4137,6 +4816,7 @@
       <c r="E351" s="4"/>
       <c r="F351" s="4"/>
       <c r="I351" s="4"/>
+      <c r="J351" s="4"/>
     </row>
     <row r="352" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="4"/>
@@ -4146,6 +4826,7 @@
       <c r="E352" s="4"/>
       <c r="F352" s="4"/>
       <c r="I352" s="4"/>
+      <c r="J352" s="4"/>
     </row>
     <row r="353" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A353" s="4"/>
@@ -4155,6 +4836,7 @@
       <c r="E353" s="4"/>
       <c r="F353" s="4"/>
       <c r="I353" s="4"/>
+      <c r="J353" s="4"/>
     </row>
     <row r="354" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A354" s="4"/>
@@ -4164,6 +4846,7 @@
       <c r="E354" s="4"/>
       <c r="F354" s="4"/>
       <c r="I354" s="4"/>
+      <c r="J354" s="4"/>
     </row>
     <row r="355" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A355" s="4"/>
@@ -4173,6 +4856,7 @@
       <c r="E355" s="4"/>
       <c r="F355" s="4"/>
       <c r="I355" s="4"/>
+      <c r="J355" s="4"/>
     </row>
     <row r="356" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A356" s="4"/>
@@ -4182,6 +4866,7 @@
       <c r="E356" s="4"/>
       <c r="F356" s="4"/>
       <c r="I356" s="4"/>
+      <c r="J356" s="4"/>
     </row>
     <row r="357" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A357" s="4"/>
@@ -4191,6 +4876,7 @@
       <c r="E357" s="4"/>
       <c r="F357" s="4"/>
       <c r="I357" s="4"/>
+      <c r="J357" s="4"/>
     </row>
     <row r="358" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A358" s="4"/>
@@ -4200,6 +4886,7 @@
       <c r="E358" s="4"/>
       <c r="F358" s="4"/>
       <c r="I358" s="4"/>
+      <c r="J358" s="4"/>
     </row>
     <row r="359" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A359" s="4"/>
@@ -4209,6 +4896,7 @@
       <c r="E359" s="4"/>
       <c r="F359" s="4"/>
       <c r="I359" s="4"/>
+      <c r="J359" s="4"/>
     </row>
     <row r="360" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A360" s="4"/>
@@ -4218,6 +4906,7 @@
       <c r="E360" s="4"/>
       <c r="F360" s="4"/>
       <c r="I360" s="4"/>
+      <c r="J360" s="4"/>
     </row>
     <row r="361" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A361" s="4"/>
@@ -4227,6 +4916,7 @@
       <c r="E361" s="4"/>
       <c r="F361" s="4"/>
       <c r="I361" s="4"/>
+      <c r="J361" s="4"/>
     </row>
     <row r="362" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A362" s="4"/>
@@ -4236,6 +4926,7 @@
       <c r="E362" s="4"/>
       <c r="F362" s="4"/>
       <c r="I362" s="4"/>
+      <c r="J362" s="4"/>
     </row>
     <row r="363" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A363" s="4"/>
@@ -4245,6 +4936,7 @@
       <c r="E363" s="4"/>
       <c r="F363" s="4"/>
       <c r="I363" s="4"/>
+      <c r="J363" s="4"/>
     </row>
     <row r="364" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A364" s="4"/>
@@ -4254,6 +4946,7 @@
       <c r="E364" s="4"/>
       <c r="F364" s="4"/>
       <c r="I364" s="4"/>
+      <c r="J364" s="4"/>
     </row>
     <row r="365" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A365" s="4"/>
@@ -4263,6 +4956,7 @@
       <c r="E365" s="4"/>
       <c r="F365" s="4"/>
       <c r="I365" s="4"/>
+      <c r="J365" s="4"/>
     </row>
     <row r="366" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A366" s="4"/>
@@ -4272,6 +4966,7 @@
       <c r="E366" s="4"/>
       <c r="F366" s="4"/>
       <c r="I366" s="4"/>
+      <c r="J366" s="4"/>
     </row>
     <row r="367" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A367" s="4"/>
@@ -4281,6 +4976,7 @@
       <c r="E367" s="4"/>
       <c r="F367" s="4"/>
       <c r="I367" s="4"/>
+      <c r="J367" s="4"/>
     </row>
     <row r="368" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="4"/>
@@ -4290,6 +4986,7 @@
       <c r="E368" s="4"/>
       <c r="F368" s="4"/>
       <c r="I368" s="4"/>
+      <c r="J368" s="4"/>
     </row>
     <row r="369" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A369" s="4"/>
@@ -4299,6 +4996,7 @@
       <c r="E369" s="4"/>
       <c r="F369" s="4"/>
       <c r="I369" s="4"/>
+      <c r="J369" s="4"/>
     </row>
     <row r="370" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A370" s="4"/>
@@ -4308,6 +5006,7 @@
       <c r="E370" s="4"/>
       <c r="F370" s="4"/>
       <c r="I370" s="4"/>
+      <c r="J370" s="4"/>
     </row>
     <row r="371" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A371" s="4"/>
@@ -4317,6 +5016,7 @@
       <c r="E371" s="4"/>
       <c r="F371" s="4"/>
       <c r="I371" s="4"/>
+      <c r="J371" s="4"/>
     </row>
     <row r="372" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A372" s="4"/>
@@ -4326,6 +5026,7 @@
       <c r="E372" s="4"/>
       <c r="F372" s="4"/>
       <c r="I372" s="4"/>
+      <c r="J372" s="4"/>
     </row>
     <row r="373" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A373" s="4"/>
@@ -4335,6 +5036,7 @@
       <c r="E373" s="4"/>
       <c r="F373" s="4"/>
       <c r="I373" s="4"/>
+      <c r="J373" s="4"/>
     </row>
     <row r="374" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A374" s="4"/>
@@ -4344,6 +5046,7 @@
       <c r="E374" s="4"/>
       <c r="F374" s="4"/>
       <c r="I374" s="4"/>
+      <c r="J374" s="4"/>
     </row>
     <row r="375" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A375" s="4"/>
@@ -4353,6 +5056,7 @@
       <c r="E375" s="4"/>
       <c r="F375" s="4"/>
       <c r="I375" s="4"/>
+      <c r="J375" s="4"/>
     </row>
     <row r="376" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A376" s="4"/>
@@ -4362,6 +5066,7 @@
       <c r="E376" s="4"/>
       <c r="F376" s="4"/>
       <c r="I376" s="4"/>
+      <c r="J376" s="4"/>
     </row>
     <row r="377" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A377" s="4"/>
@@ -4371,6 +5076,7 @@
       <c r="E377" s="4"/>
       <c r="F377" s="4"/>
       <c r="I377" s="4"/>
+      <c r="J377" s="4"/>
     </row>
     <row r="378" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A378" s="4"/>
@@ -4380,6 +5086,7 @@
       <c r="E378" s="4"/>
       <c r="F378" s="4"/>
       <c r="I378" s="4"/>
+      <c r="J378" s="4"/>
     </row>
     <row r="379" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A379" s="4"/>
@@ -4389,6 +5096,7 @@
       <c r="E379" s="4"/>
       <c r="F379" s="4"/>
       <c r="I379" s="4"/>
+      <c r="J379" s="4"/>
     </row>
     <row r="380" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A380" s="4"/>
@@ -4398,6 +5106,7 @@
       <c r="E380" s="4"/>
       <c r="F380" s="4"/>
       <c r="I380" s="4"/>
+      <c r="J380" s="4"/>
     </row>
     <row r="381" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A381" s="4"/>
@@ -4407,6 +5116,7 @@
       <c r="E381" s="4"/>
       <c r="F381" s="4"/>
       <c r="I381" s="4"/>
+      <c r="J381" s="4"/>
     </row>
     <row r="382" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A382" s="4"/>
@@ -4416,6 +5126,7 @@
       <c r="E382" s="4"/>
       <c r="F382" s="4"/>
       <c r="I382" s="4"/>
+      <c r="J382" s="4"/>
     </row>
     <row r="383" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A383" s="4"/>
@@ -4425,6 +5136,7 @@
       <c r="E383" s="4"/>
       <c r="F383" s="4"/>
       <c r="I383" s="4"/>
+      <c r="J383" s="4"/>
     </row>
     <row r="384" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A384" s="4"/>
@@ -4434,6 +5146,7 @@
       <c r="E384" s="4"/>
       <c r="F384" s="4"/>
       <c r="I384" s="4"/>
+      <c r="J384" s="4"/>
     </row>
     <row r="385" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A385" s="4"/>
@@ -4443,6 +5156,7 @@
       <c r="E385" s="4"/>
       <c r="F385" s="4"/>
       <c r="I385" s="4"/>
+      <c r="J385" s="4"/>
     </row>
     <row r="386" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A386" s="4"/>
@@ -4452,6 +5166,7 @@
       <c r="E386" s="4"/>
       <c r="F386" s="4"/>
       <c r="I386" s="4"/>
+      <c r="J386" s="4"/>
     </row>
     <row r="387" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A387" s="4"/>
@@ -4461,6 +5176,7 @@
       <c r="E387" s="4"/>
       <c r="F387" s="4"/>
       <c r="I387" s="4"/>
+      <c r="J387" s="4"/>
     </row>
     <row r="388" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A388" s="4"/>
@@ -4470,6 +5186,7 @@
       <c r="E388" s="4"/>
       <c r="F388" s="4"/>
       <c r="I388" s="4"/>
+      <c r="J388" s="4"/>
     </row>
     <row r="389" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A389" s="4"/>
@@ -4479,6 +5196,7 @@
       <c r="E389" s="4"/>
       <c r="F389" s="4"/>
       <c r="I389" s="4"/>
+      <c r="J389" s="4"/>
     </row>
     <row r="390" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A390" s="4"/>
@@ -4488,6 +5206,7 @@
       <c r="E390" s="4"/>
       <c r="F390" s="4"/>
       <c r="I390" s="4"/>
+      <c r="J390" s="4"/>
     </row>
     <row r="391" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A391" s="4"/>
@@ -4497,6 +5216,7 @@
       <c r="E391" s="4"/>
       <c r="F391" s="4"/>
       <c r="I391" s="4"/>
+      <c r="J391" s="4"/>
     </row>
     <row r="392" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A392" s="4"/>
@@ -4506,6 +5226,7 @@
       <c r="E392" s="4"/>
       <c r="F392" s="4"/>
       <c r="I392" s="4"/>
+      <c r="J392" s="4"/>
     </row>
     <row r="393" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="4"/>
@@ -4515,6 +5236,7 @@
       <c r="E393" s="4"/>
       <c r="F393" s="4"/>
       <c r="I393" s="4"/>
+      <c r="J393" s="4"/>
     </row>
     <row r="394" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A394" s="4"/>
@@ -4524,6 +5246,7 @@
       <c r="E394" s="4"/>
       <c r="F394" s="4"/>
       <c r="I394" s="4"/>
+      <c r="J394" s="4"/>
     </row>
     <row r="395" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="4"/>
@@ -4533,6 +5256,7 @@
       <c r="E395" s="4"/>
       <c r="F395" s="4"/>
       <c r="I395" s="4"/>
+      <c r="J395" s="4"/>
     </row>
     <row r="396" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A396" s="4"/>
@@ -4542,6 +5266,7 @@
       <c r="E396" s="4"/>
       <c r="F396" s="4"/>
       <c r="I396" s="4"/>
+      <c r="J396" s="4"/>
     </row>
     <row r="397" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A397" s="4"/>
@@ -4551,6 +5276,7 @@
       <c r="E397" s="4"/>
       <c r="F397" s="4"/>
       <c r="I397" s="4"/>
+      <c r="J397" s="4"/>
     </row>
     <row r="398" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A398" s="4"/>
@@ -4560,6 +5286,7 @@
       <c r="E398" s="4"/>
       <c r="F398" s="4"/>
       <c r="I398" s="4"/>
+      <c r="J398" s="4"/>
     </row>
     <row r="399" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A399" s="4"/>
@@ -4569,6 +5296,7 @@
       <c r="E399" s="4"/>
       <c r="F399" s="4"/>
       <c r="I399" s="4"/>
+      <c r="J399" s="4"/>
     </row>
     <row r="400" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A400" s="4"/>
@@ -4578,6 +5306,7 @@
       <c r="E400" s="4"/>
       <c r="F400" s="4"/>
       <c r="I400" s="4"/>
+      <c r="J400" s="4"/>
     </row>
     <row r="401" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A401" s="4"/>
@@ -4587,6 +5316,7 @@
       <c r="E401" s="4"/>
       <c r="F401" s="4"/>
       <c r="I401" s="4"/>
+      <c r="J401" s="4"/>
     </row>
     <row r="402" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A402" s="4"/>
@@ -4596,6 +5326,7 @@
       <c r="E402" s="4"/>
       <c r="F402" s="4"/>
       <c r="I402" s="4"/>
+      <c r="J402" s="4"/>
     </row>
     <row r="403" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A403" s="4"/>
@@ -4605,6 +5336,7 @@
       <c r="E403" s="4"/>
       <c r="F403" s="4"/>
       <c r="I403" s="4"/>
+      <c r="J403" s="4"/>
     </row>
     <row r="404" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="4"/>
@@ -4614,6 +5346,7 @@
       <c r="E404" s="4"/>
       <c r="F404" s="4"/>
       <c r="I404" s="4"/>
+      <c r="J404" s="4"/>
     </row>
     <row r="405" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A405" s="4"/>
@@ -4623,6 +5356,7 @@
       <c r="E405" s="4"/>
       <c r="F405" s="4"/>
       <c r="I405" s="4"/>
+      <c r="J405" s="4"/>
     </row>
     <row r="406" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="4"/>
@@ -4632,6 +5366,7 @@
       <c r="E406" s="4"/>
       <c r="F406" s="4"/>
       <c r="I406" s="4"/>
+      <c r="J406" s="4"/>
     </row>
     <row r="407" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="4"/>
@@ -4641,6 +5376,7 @@
       <c r="E407" s="4"/>
       <c r="F407" s="4"/>
       <c r="I407" s="4"/>
+      <c r="J407" s="4"/>
     </row>
     <row r="408" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A408" s="4"/>
@@ -4650,6 +5386,7 @@
       <c r="E408" s="4"/>
       <c r="F408" s="4"/>
       <c r="I408" s="4"/>
+      <c r="J408" s="4"/>
     </row>
     <row r="409" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A409" s="4"/>
@@ -4659,6 +5396,7 @@
       <c r="E409" s="4"/>
       <c r="F409" s="4"/>
       <c r="I409" s="4"/>
+      <c r="J409" s="4"/>
     </row>
     <row r="410" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A410" s="4"/>
@@ -4668,6 +5406,7 @@
       <c r="E410" s="4"/>
       <c r="F410" s="4"/>
       <c r="I410" s="4"/>
+      <c r="J410" s="4"/>
     </row>
     <row r="411" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A411" s="4"/>
@@ -4677,6 +5416,7 @@
       <c r="E411" s="4"/>
       <c r="F411" s="4"/>
       <c r="I411" s="4"/>
+      <c r="J411" s="4"/>
     </row>
     <row r="412" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A412" s="4"/>
@@ -4686,6 +5426,7 @@
       <c r="E412" s="4"/>
       <c r="F412" s="4"/>
       <c r="I412" s="4"/>
+      <c r="J412" s="4"/>
     </row>
     <row r="413" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A413" s="4"/>
@@ -4695,6 +5436,7 @@
       <c r="E413" s="4"/>
       <c r="F413" s="4"/>
       <c r="I413" s="4"/>
+      <c r="J413" s="4"/>
     </row>
     <row r="414" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A414" s="4"/>
@@ -4704,6 +5446,7 @@
       <c r="E414" s="4"/>
       <c r="F414" s="4"/>
       <c r="I414" s="4"/>
+      <c r="J414" s="4"/>
     </row>
     <row r="415" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A415" s="4"/>
@@ -4713,6 +5456,7 @@
       <c r="E415" s="4"/>
       <c r="F415" s="4"/>
       <c r="I415" s="4"/>
+      <c r="J415" s="4"/>
     </row>
     <row r="416" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A416" s="4"/>
@@ -4722,6 +5466,7 @@
       <c r="E416" s="4"/>
       <c r="F416" s="4"/>
       <c r="I416" s="4"/>
+      <c r="J416" s="4"/>
     </row>
     <row r="417" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A417" s="4"/>
@@ -4731,6 +5476,7 @@
       <c r="E417" s="4"/>
       <c r="F417" s="4"/>
       <c r="I417" s="4"/>
+      <c r="J417" s="4"/>
     </row>
     <row r="418" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A418" s="4"/>
@@ -4740,6 +5486,7 @@
       <c r="E418" s="4"/>
       <c r="F418" s="4"/>
       <c r="I418" s="4"/>
+      <c r="J418" s="4"/>
     </row>
     <row r="419" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="4"/>
@@ -4749,6 +5496,7 @@
       <c r="E419" s="4"/>
       <c r="F419" s="4"/>
       <c r="I419" s="4"/>
+      <c r="J419" s="4"/>
     </row>
     <row r="420" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="4"/>
@@ -4758,6 +5506,7 @@
       <c r="E420" s="4"/>
       <c r="F420" s="4"/>
       <c r="I420" s="4"/>
+      <c r="J420" s="4"/>
     </row>
     <row r="421" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A421" s="4"/>
@@ -4767,6 +5516,7 @@
       <c r="E421" s="4"/>
       <c r="F421" s="4"/>
       <c r="I421" s="4"/>
+      <c r="J421" s="4"/>
     </row>
     <row r="422" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A422" s="4"/>
@@ -4776,6 +5526,7 @@
       <c r="E422" s="4"/>
       <c r="F422" s="4"/>
       <c r="I422" s="4"/>
+      <c r="J422" s="4"/>
     </row>
     <row r="423" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A423" s="4"/>
@@ -4785,6 +5536,7 @@
       <c r="E423" s="4"/>
       <c r="F423" s="4"/>
       <c r="I423" s="4"/>
+      <c r="J423" s="4"/>
     </row>
     <row r="424" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A424" s="4"/>
@@ -4794,6 +5546,7 @@
       <c r="E424" s="4"/>
       <c r="F424" s="4"/>
       <c r="I424" s="4"/>
+      <c r="J424" s="4"/>
     </row>
     <row r="425" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="4"/>
@@ -4803,6 +5556,7 @@
       <c r="E425" s="4"/>
       <c r="F425" s="4"/>
       <c r="I425" s="4"/>
+      <c r="J425" s="4"/>
     </row>
     <row r="426" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="4"/>
@@ -4812,6 +5566,7 @@
       <c r="E426" s="4"/>
       <c r="F426" s="4"/>
       <c r="I426" s="4"/>
+      <c r="J426" s="4"/>
     </row>
     <row r="427" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A427" s="4"/>
@@ -4821,6 +5576,7 @@
       <c r="E427" s="4"/>
       <c r="F427" s="4"/>
       <c r="I427" s="4"/>
+      <c r="J427" s="4"/>
     </row>
     <row r="428" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="4"/>
@@ -4830,6 +5586,7 @@
       <c r="E428" s="4"/>
       <c r="F428" s="4"/>
       <c r="I428" s="4"/>
+      <c r="J428" s="4"/>
     </row>
     <row r="429" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="4"/>
@@ -4839,6 +5596,7 @@
       <c r="E429" s="4"/>
       <c r="F429" s="4"/>
       <c r="I429" s="4"/>
+      <c r="J429" s="4"/>
     </row>
     <row r="430" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="4"/>
@@ -4848,6 +5606,7 @@
       <c r="E430" s="4"/>
       <c r="F430" s="4"/>
       <c r="I430" s="4"/>
+      <c r="J430" s="4"/>
     </row>
     <row r="431" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A431" s="4"/>
@@ -4857,6 +5616,7 @@
       <c r="E431" s="4"/>
       <c r="F431" s="4"/>
       <c r="I431" s="4"/>
+      <c r="J431" s="4"/>
     </row>
     <row r="432" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A432" s="4"/>
@@ -4866,6 +5626,7 @@
       <c r="E432" s="4"/>
       <c r="F432" s="4"/>
       <c r="I432" s="4"/>
+      <c r="J432" s="4"/>
     </row>
     <row r="433" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A433" s="4"/>
@@ -4875,6 +5636,7 @@
       <c r="E433" s="4"/>
       <c r="F433" s="4"/>
       <c r="I433" s="4"/>
+      <c r="J433" s="4"/>
     </row>
     <row r="434" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A434" s="4"/>
@@ -4884,6 +5646,7 @@
       <c r="E434" s="4"/>
       <c r="F434" s="4"/>
       <c r="I434" s="4"/>
+      <c r="J434" s="4"/>
     </row>
     <row r="435" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A435" s="4"/>
@@ -4893,6 +5656,7 @@
       <c r="E435" s="4"/>
       <c r="F435" s="4"/>
       <c r="I435" s="4"/>
+      <c r="J435" s="4"/>
     </row>
     <row r="436" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A436" s="4"/>
@@ -4902,6 +5666,7 @@
       <c r="E436" s="4"/>
       <c r="F436" s="4"/>
       <c r="I436" s="4"/>
+      <c r="J436" s="4"/>
     </row>
     <row r="437" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="4"/>
@@ -4911,6 +5676,7 @@
       <c r="E437" s="4"/>
       <c r="F437" s="4"/>
       <c r="I437" s="4"/>
+      <c r="J437" s="4"/>
     </row>
     <row r="438" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A438" s="4"/>
@@ -4920,6 +5686,7 @@
       <c r="E438" s="4"/>
       <c r="F438" s="4"/>
       <c r="I438" s="4"/>
+      <c r="J438" s="4"/>
     </row>
     <row r="439" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A439" s="4"/>
@@ -4929,6 +5696,7 @@
       <c r="E439" s="4"/>
       <c r="F439" s="4"/>
       <c r="I439" s="4"/>
+      <c r="J439" s="4"/>
     </row>
     <row r="440" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A440" s="4"/>
@@ -4938,6 +5706,7 @@
       <c r="E440" s="4"/>
       <c r="F440" s="4"/>
       <c r="I440" s="4"/>
+      <c r="J440" s="4"/>
     </row>
     <row r="441" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A441" s="4"/>
@@ -4947,6 +5716,7 @@
       <c r="E441" s="4"/>
       <c r="F441" s="4"/>
       <c r="I441" s="4"/>
+      <c r="J441" s="4"/>
     </row>
     <row r="442" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A442" s="4"/>
@@ -4956,6 +5726,7 @@
       <c r="E442" s="4"/>
       <c r="F442" s="4"/>
       <c r="I442" s="4"/>
+      <c r="J442" s="4"/>
     </row>
     <row r="443" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A443" s="4"/>
@@ -4965,6 +5736,7 @@
       <c r="E443" s="4"/>
       <c r="F443" s="4"/>
       <c r="I443" s="4"/>
+      <c r="J443" s="4"/>
     </row>
     <row r="444" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A444" s="4"/>
@@ -4974,6 +5746,7 @@
       <c r="E444" s="4"/>
       <c r="F444" s="4"/>
       <c r="I444" s="4"/>
+      <c r="J444" s="4"/>
     </row>
     <row r="445" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A445" s="4"/>
@@ -4983,6 +5756,7 @@
       <c r="E445" s="4"/>
       <c r="F445" s="4"/>
       <c r="I445" s="4"/>
+      <c r="J445" s="4"/>
     </row>
     <row r="446" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A446" s="4"/>
@@ -4992,6 +5766,7 @@
       <c r="E446" s="4"/>
       <c r="F446" s="4"/>
       <c r="I446" s="4"/>
+      <c r="J446" s="4"/>
     </row>
     <row r="447" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A447" s="4"/>
@@ -5001,6 +5776,7 @@
       <c r="E447" s="4"/>
       <c r="F447" s="4"/>
       <c r="I447" s="4"/>
+      <c r="J447" s="4"/>
     </row>
     <row r="448" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A448" s="4"/>
@@ -5010,6 +5786,7 @@
       <c r="E448" s="4"/>
       <c r="F448" s="4"/>
       <c r="I448" s="4"/>
+      <c r="J448" s="4"/>
     </row>
     <row r="449" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A449" s="4"/>
@@ -5019,6 +5796,7 @@
       <c r="E449" s="4"/>
       <c r="F449" s="4"/>
       <c r="I449" s="4"/>
+      <c r="J449" s="4"/>
     </row>
     <row r="450" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A450" s="4"/>
@@ -5028,6 +5806,7 @@
       <c r="E450" s="4"/>
       <c r="F450" s="4"/>
       <c r="I450" s="4"/>
+      <c r="J450" s="4"/>
     </row>
     <row r="451" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A451" s="4"/>
@@ -5037,6 +5816,7 @@
       <c r="E451" s="4"/>
       <c r="F451" s="4"/>
       <c r="I451" s="4"/>
+      <c r="J451" s="4"/>
     </row>
     <row r="452" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A452" s="4"/>
@@ -5046,6 +5826,7 @@
       <c r="E452" s="4"/>
       <c r="F452" s="4"/>
       <c r="I452" s="4"/>
+      <c r="J452" s="4"/>
     </row>
     <row r="453" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A453" s="4"/>
@@ -5055,6 +5836,7 @@
       <c r="E453" s="4"/>
       <c r="F453" s="4"/>
       <c r="I453" s="4"/>
+      <c r="J453" s="4"/>
     </row>
     <row r="454" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A454" s="4"/>
@@ -5064,6 +5846,7 @@
       <c r="E454" s="4"/>
       <c r="F454" s="4"/>
       <c r="I454" s="4"/>
+      <c r="J454" s="4"/>
     </row>
     <row r="455" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A455" s="4"/>
@@ -5073,6 +5856,7 @@
       <c r="E455" s="4"/>
       <c r="F455" s="4"/>
       <c r="I455" s="4"/>
+      <c r="J455" s="4"/>
     </row>
     <row r="456" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A456" s="4"/>
@@ -5082,6 +5866,7 @@
       <c r="E456" s="4"/>
       <c r="F456" s="4"/>
       <c r="I456" s="4"/>
+      <c r="J456" s="4"/>
     </row>
     <row r="457" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="4"/>
@@ -5091,6 +5876,7 @@
       <c r="E457" s="4"/>
       <c r="F457" s="4"/>
       <c r="I457" s="4"/>
+      <c r="J457" s="4"/>
     </row>
     <row r="458" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A458" s="4"/>
@@ -5100,6 +5886,7 @@
       <c r="E458" s="4"/>
       <c r="F458" s="4"/>
       <c r="I458" s="4"/>
+      <c r="J458" s="4"/>
     </row>
     <row r="459" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A459" s="4"/>
@@ -5109,6 +5896,7 @@
       <c r="E459" s="4"/>
       <c r="F459" s="4"/>
       <c r="I459" s="4"/>
+      <c r="J459" s="4"/>
     </row>
     <row r="460" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A460" s="4"/>
@@ -5118,6 +5906,7 @@
       <c r="E460" s="4"/>
       <c r="F460" s="4"/>
       <c r="I460" s="4"/>
+      <c r="J460" s="4"/>
     </row>
     <row r="461" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A461" s="4"/>
@@ -5127,6 +5916,7 @@
       <c r="E461" s="4"/>
       <c r="F461" s="4"/>
       <c r="I461" s="4"/>
+      <c r="J461" s="4"/>
     </row>
     <row r="462" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A462" s="4"/>
@@ -5136,6 +5926,7 @@
       <c r="E462" s="4"/>
       <c r="F462" s="4"/>
       <c r="I462" s="4"/>
+      <c r="J462" s="4"/>
     </row>
     <row r="463" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A463" s="4"/>
@@ -5145,6 +5936,7 @@
       <c r="E463" s="4"/>
       <c r="F463" s="4"/>
       <c r="I463" s="4"/>
+      <c r="J463" s="4"/>
     </row>
     <row r="464" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A464" s="4"/>
@@ -5154,6 +5946,7 @@
       <c r="E464" s="4"/>
       <c r="F464" s="4"/>
       <c r="I464" s="4"/>
+      <c r="J464" s="4"/>
     </row>
     <row r="465" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A465" s="4"/>
@@ -5163,6 +5956,7 @@
       <c r="E465" s="4"/>
       <c r="F465" s="4"/>
       <c r="I465" s="4"/>
+      <c r="J465" s="4"/>
     </row>
     <row r="466" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A466" s="4"/>
@@ -5172,6 +5966,7 @@
       <c r="E466" s="4"/>
       <c r="F466" s="4"/>
       <c r="I466" s="4"/>
+      <c r="J466" s="4"/>
     </row>
     <row r="467" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A467" s="4"/>
@@ -5181,6 +5976,7 @@
       <c r="E467" s="4"/>
       <c r="F467" s="4"/>
       <c r="I467" s="4"/>
+      <c r="J467" s="4"/>
     </row>
     <row r="468" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A468" s="4"/>
@@ -5190,6 +5986,7 @@
       <c r="E468" s="4"/>
       <c r="F468" s="4"/>
       <c r="I468" s="4"/>
+      <c r="J468" s="4"/>
     </row>
     <row r="469" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A469" s="4"/>
@@ -5199,6 +5996,7 @@
       <c r="E469" s="4"/>
       <c r="F469" s="4"/>
       <c r="I469" s="4"/>
+      <c r="J469" s="4"/>
     </row>
     <row r="470" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="4"/>
@@ -5208,6 +6006,7 @@
       <c r="E470" s="4"/>
       <c r="F470" s="4"/>
       <c r="I470" s="4"/>
+      <c r="J470" s="4"/>
     </row>
     <row r="471" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A471" s="4"/>
@@ -5217,6 +6016,7 @@
       <c r="E471" s="4"/>
       <c r="F471" s="4"/>
       <c r="I471" s="4"/>
+      <c r="J471" s="4"/>
     </row>
     <row r="472" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A472" s="4"/>
@@ -5226,6 +6026,7 @@
       <c r="E472" s="4"/>
       <c r="F472" s="4"/>
       <c r="I472" s="4"/>
+      <c r="J472" s="4"/>
     </row>
     <row r="473" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="4"/>
@@ -5235,6 +6036,7 @@
       <c r="E473" s="4"/>
       <c r="F473" s="4"/>
       <c r="I473" s="4"/>
+      <c r="J473" s="4"/>
     </row>
     <row r="474" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A474" s="4"/>
@@ -5244,6 +6046,7 @@
       <c r="E474" s="4"/>
       <c r="F474" s="4"/>
       <c r="I474" s="4"/>
+      <c r="J474" s="4"/>
     </row>
     <row r="475" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A475" s="4"/>
@@ -5253,6 +6056,7 @@
       <c r="E475" s="4"/>
       <c r="F475" s="4"/>
       <c r="I475" s="4"/>
+      <c r="J475" s="4"/>
     </row>
     <row r="476" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A476" s="4"/>
@@ -5262,6 +6066,7 @@
       <c r="E476" s="4"/>
       <c r="F476" s="4"/>
       <c r="I476" s="4"/>
+      <c r="J476" s="4"/>
     </row>
     <row r="477" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A477" s="4"/>
@@ -5271,6 +6076,7 @@
       <c r="E477" s="4"/>
       <c r="F477" s="4"/>
       <c r="I477" s="4"/>
+      <c r="J477" s="4"/>
     </row>
     <row r="478" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A478" s="4"/>
@@ -5280,6 +6086,7 @@
       <c r="E478" s="4"/>
       <c r="F478" s="4"/>
       <c r="I478" s="4"/>
+      <c r="J478" s="4"/>
     </row>
     <row r="479" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A479" s="4"/>
@@ -5289,6 +6096,7 @@
       <c r="E479" s="4"/>
       <c r="F479" s="4"/>
       <c r="I479" s="4"/>
+      <c r="J479" s="4"/>
     </row>
     <row r="480" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="4"/>
@@ -5298,6 +6106,7 @@
       <c r="E480" s="4"/>
       <c r="F480" s="4"/>
       <c r="I480" s="4"/>
+      <c r="J480" s="4"/>
     </row>
     <row r="481" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="4"/>
@@ -5307,6 +6116,7 @@
       <c r="E481" s="4"/>
       <c r="F481" s="4"/>
       <c r="I481" s="4"/>
+      <c r="J481" s="4"/>
     </row>
     <row r="482" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="4"/>
@@ -5316,6 +6126,7 @@
       <c r="E482" s="4"/>
       <c r="F482" s="4"/>
       <c r="I482" s="4"/>
+      <c r="J482" s="4"/>
     </row>
     <row r="483" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="4"/>
@@ -5325,6 +6136,7 @@
       <c r="E483" s="4"/>
       <c r="F483" s="4"/>
       <c r="I483" s="4"/>
+      <c r="J483" s="4"/>
     </row>
     <row r="484" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="4"/>
@@ -5334,6 +6146,7 @@
       <c r="E484" s="4"/>
       <c r="F484" s="4"/>
       <c r="I484" s="4"/>
+      <c r="J484" s="4"/>
     </row>
     <row r="485" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="4"/>
@@ -5343,6 +6156,7 @@
       <c r="E485" s="4"/>
       <c r="F485" s="4"/>
       <c r="I485" s="4"/>
+      <c r="J485" s="4"/>
     </row>
     <row r="486" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="4"/>
@@ -5352,6 +6166,7 @@
       <c r="E486" s="4"/>
       <c r="F486" s="4"/>
       <c r="I486" s="4"/>
+      <c r="J486" s="4"/>
     </row>
     <row r="487" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="4"/>
@@ -5361,6 +6176,7 @@
       <c r="E487" s="4"/>
       <c r="F487" s="4"/>
       <c r="I487" s="4"/>
+      <c r="J487" s="4"/>
     </row>
     <row r="488" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="4"/>
@@ -5370,6 +6186,7 @@
       <c r="E488" s="4"/>
       <c r="F488" s="4"/>
       <c r="I488" s="4"/>
+      <c r="J488" s="4"/>
     </row>
     <row r="489" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="4"/>
@@ -5379,6 +6196,7 @@
       <c r="E489" s="4"/>
       <c r="F489" s="4"/>
       <c r="I489" s="4"/>
+      <c r="J489" s="4"/>
     </row>
     <row r="490" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="4"/>
@@ -5388,6 +6206,7 @@
       <c r="E490" s="4"/>
       <c r="F490" s="4"/>
       <c r="I490" s="4"/>
+      <c r="J490" s="4"/>
     </row>
     <row r="491" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="4"/>
@@ -5397,6 +6216,7 @@
       <c r="E491" s="4"/>
       <c r="F491" s="4"/>
       <c r="I491" s="4"/>
+      <c r="J491" s="4"/>
     </row>
     <row r="492" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="4"/>
@@ -5406,6 +6226,7 @@
       <c r="E492" s="4"/>
       <c r="F492" s="4"/>
       <c r="I492" s="4"/>
+      <c r="J492" s="4"/>
     </row>
     <row r="493" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="4"/>
@@ -5415,6 +6236,7 @@
       <c r="E493" s="4"/>
       <c r="F493" s="4"/>
       <c r="I493" s="4"/>
+      <c r="J493" s="4"/>
     </row>
     <row r="494" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="4"/>
@@ -5424,6 +6246,7 @@
       <c r="E494" s="4"/>
       <c r="F494" s="4"/>
       <c r="I494" s="4"/>
+      <c r="J494" s="4"/>
     </row>
     <row r="495" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="4"/>
@@ -5433,6 +6256,7 @@
       <c r="E495" s="4"/>
       <c r="F495" s="4"/>
       <c r="I495" s="4"/>
+      <c r="J495" s="4"/>
     </row>
     <row r="496" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="4"/>
@@ -5442,6 +6266,7 @@
       <c r="E496" s="4"/>
       <c r="F496" s="4"/>
       <c r="I496" s="4"/>
+      <c r="J496" s="4"/>
     </row>
     <row r="497" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="4"/>
@@ -5451,6 +6276,7 @@
       <c r="E497" s="4"/>
       <c r="F497" s="4"/>
       <c r="I497" s="4"/>
+      <c r="J497" s="4"/>
     </row>
     <row r="498" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="4"/>
@@ -5460,6 +6286,7 @@
       <c r="E498" s="4"/>
       <c r="F498" s="4"/>
       <c r="I498" s="4"/>
+      <c r="J498" s="4"/>
     </row>
     <row r="499" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="4"/>
@@ -5469,6 +6296,7 @@
       <c r="E499" s="4"/>
       <c r="F499" s="4"/>
       <c r="I499" s="4"/>
+      <c r="J499" s="4"/>
     </row>
     <row r="500" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="4"/>
@@ -5478,6 +6306,7 @@
       <c r="E500" s="4"/>
       <c r="F500" s="4"/>
       <c r="I500" s="4"/>
+      <c r="J500" s="4"/>
     </row>
     <row r="501" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="4"/>
@@ -5487,6 +6316,7 @@
       <c r="E501" s="4"/>
       <c r="F501" s="4"/>
       <c r="I501" s="4"/>
+      <c r="J501" s="4"/>
     </row>
     <row r="502" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="4"/>
@@ -5496,6 +6326,7 @@
       <c r="E502" s="4"/>
       <c r="F502" s="4"/>
       <c r="I502" s="4"/>
+      <c r="J502" s="4"/>
     </row>
     <row r="503" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="4"/>
@@ -5505,6 +6336,7 @@
       <c r="E503" s="4"/>
       <c r="F503" s="4"/>
       <c r="I503" s="4"/>
+      <c r="J503" s="4"/>
     </row>
     <row r="504" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="4"/>
@@ -5514,6 +6346,7 @@
       <c r="E504" s="4"/>
       <c r="F504" s="4"/>
       <c r="I504" s="4"/>
+      <c r="J504" s="4"/>
     </row>
     <row r="505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="4"/>
@@ -5523,6 +6356,7 @@
       <c r="E505" s="4"/>
       <c r="F505" s="4"/>
       <c r="I505" s="4"/>
+      <c r="J505" s="4"/>
     </row>
     <row r="506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="4"/>
@@ -5532,6 +6366,7 @@
       <c r="E506" s="4"/>
       <c r="F506" s="4"/>
       <c r="I506" s="4"/>
+      <c r="J506" s="4"/>
     </row>
     <row r="507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="4"/>
@@ -5541,6 +6376,7 @@
       <c r="E507" s="4"/>
       <c r="F507" s="4"/>
       <c r="I507" s="4"/>
+      <c r="J507" s="4"/>
     </row>
     <row r="508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="4"/>
@@ -5550,6 +6386,7 @@
       <c r="E508" s="4"/>
       <c r="F508" s="4"/>
       <c r="I508" s="4"/>
+      <c r="J508" s="4"/>
     </row>
     <row r="509" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="4"/>
@@ -5559,6 +6396,7 @@
       <c r="E509" s="4"/>
       <c r="F509" s="4"/>
       <c r="I509" s="4"/>
+      <c r="J509" s="4"/>
     </row>
     <row r="510" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="4"/>
@@ -5568,6 +6406,7 @@
       <c r="E510" s="4"/>
       <c r="F510" s="4"/>
       <c r="I510" s="4"/>
+      <c r="J510" s="4"/>
     </row>
     <row r="511" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A511" s="4"/>
@@ -5577,6 +6416,7 @@
       <c r="E511" s="4"/>
       <c r="F511" s="4"/>
       <c r="I511" s="4"/>
+      <c r="J511" s="4"/>
     </row>
     <row r="512" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A512" s="4"/>
@@ -5586,6 +6426,7 @@
       <c r="E512" s="4"/>
       <c r="F512" s="4"/>
       <c r="I512" s="4"/>
+      <c r="J512" s="4"/>
     </row>
     <row r="513" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A513" s="4"/>
@@ -5595,6 +6436,7 @@
       <c r="E513" s="4"/>
       <c r="F513" s="4"/>
       <c r="I513" s="4"/>
+      <c r="J513" s="4"/>
     </row>
     <row r="514" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A514" s="4"/>
@@ -5604,6 +6446,7 @@
       <c r="E514" s="4"/>
       <c r="F514" s="4"/>
       <c r="I514" s="4"/>
+      <c r="J514" s="4"/>
     </row>
     <row r="515" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A515" s="4"/>
@@ -5613,6 +6456,7 @@
       <c r="E515" s="4"/>
       <c r="F515" s="4"/>
       <c r="I515" s="4"/>
+      <c r="J515" s="4"/>
     </row>
     <row r="516" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A516" s="4"/>
@@ -5622,6 +6466,7 @@
       <c r="E516" s="4"/>
       <c r="F516" s="4"/>
       <c r="I516" s="4"/>
+      <c r="J516" s="4"/>
     </row>
     <row r="517" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A517" s="4"/>
@@ -5631,6 +6476,7 @@
       <c r="E517" s="4"/>
       <c r="F517" s="4"/>
       <c r="I517" s="4"/>
+      <c r="J517" s="4"/>
     </row>
     <row r="518" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A518" s="4"/>
@@ -5640,6 +6486,7 @@
       <c r="E518" s="4"/>
       <c r="F518" s="4"/>
       <c r="I518" s="4"/>
+      <c r="J518" s="4"/>
     </row>
     <row r="519" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A519" s="4"/>
@@ -5649,6 +6496,7 @@
       <c r="E519" s="4"/>
       <c r="F519" s="4"/>
       <c r="I519" s="4"/>
+      <c r="J519" s="4"/>
     </row>
     <row r="520" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A520" s="4"/>
@@ -5658,6 +6506,7 @@
       <c r="E520" s="4"/>
       <c r="F520" s="4"/>
       <c r="I520" s="4"/>
+      <c r="J520" s="4"/>
     </row>
     <row r="521" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A521" s="4"/>
@@ -5667,6 +6516,7 @@
       <c r="E521" s="4"/>
       <c r="F521" s="4"/>
       <c r="I521" s="4"/>
+      <c r="J521" s="4"/>
     </row>
     <row r="522" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A522" s="4"/>
@@ -5676,6 +6526,7 @@
       <c r="E522" s="4"/>
       <c r="F522" s="4"/>
       <c r="I522" s="4"/>
+      <c r="J522" s="4"/>
     </row>
     <row r="523" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A523" s="4"/>
@@ -5685,6 +6536,7 @@
       <c r="E523" s="4"/>
       <c r="F523" s="4"/>
       <c r="I523" s="4"/>
+      <c r="J523" s="4"/>
     </row>
     <row r="524" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A524" s="4"/>
@@ -5694,6 +6546,7 @@
       <c r="E524" s="4"/>
       <c r="F524" s="4"/>
       <c r="I524" s="4"/>
+      <c r="J524" s="4"/>
     </row>
     <row r="525" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A525" s="4"/>
@@ -5703,6 +6556,7 @@
       <c r="E525" s="4"/>
       <c r="F525" s="4"/>
       <c r="I525" s="4"/>
+      <c r="J525" s="4"/>
     </row>
     <row r="526" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A526" s="4"/>
@@ -5712,6 +6566,7 @@
       <c r="E526" s="4"/>
       <c r="F526" s="4"/>
       <c r="I526" s="4"/>
+      <c r="J526" s="4"/>
     </row>
     <row r="527" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="4"/>
@@ -5721,6 +6576,7 @@
       <c r="E527" s="4"/>
       <c r="F527" s="4"/>
       <c r="I527" s="4"/>
+      <c r="J527" s="4"/>
     </row>
     <row r="528" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A528" s="4"/>
@@ -5730,6 +6586,7 @@
       <c r="E528" s="4"/>
       <c r="F528" s="4"/>
       <c r="I528" s="4"/>
+      <c r="J528" s="4"/>
     </row>
     <row r="529" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A529" s="4"/>
@@ -5739,6 +6596,7 @@
       <c r="E529" s="4"/>
       <c r="F529" s="4"/>
       <c r="I529" s="4"/>
+      <c r="J529" s="4"/>
     </row>
     <row r="530" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A530" s="4"/>
@@ -5748,6 +6606,7 @@
       <c r="E530" s="4"/>
       <c r="F530" s="4"/>
       <c r="I530" s="4"/>
+      <c r="J530" s="4"/>
     </row>
     <row r="531" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A531" s="4"/>
@@ -5757,6 +6616,7 @@
       <c r="E531" s="4"/>
       <c r="F531" s="4"/>
       <c r="I531" s="4"/>
+      <c r="J531" s="4"/>
     </row>
     <row r="532" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A532" s="4"/>
@@ -5766,6 +6626,7 @@
       <c r="E532" s="4"/>
       <c r="F532" s="4"/>
       <c r="I532" s="4"/>
+      <c r="J532" s="4"/>
     </row>
     <row r="533" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="4"/>
@@ -5775,6 +6636,7 @@
       <c r="E533" s="4"/>
       <c r="F533" s="4"/>
       <c r="I533" s="4"/>
+      <c r="J533" s="4"/>
     </row>
     <row r="534" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A534" s="4"/>
@@ -5784,6 +6646,7 @@
       <c r="E534" s="4"/>
       <c r="F534" s="4"/>
       <c r="I534" s="4"/>
+      <c r="J534" s="4"/>
     </row>
     <row r="535" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A535" s="4"/>
@@ -5793,6 +6656,7 @@
       <c r="E535" s="4"/>
       <c r="F535" s="4"/>
       <c r="I535" s="4"/>
+      <c r="J535" s="4"/>
     </row>
     <row r="536" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A536" s="4"/>
@@ -5802,6 +6666,7 @@
       <c r="E536" s="4"/>
       <c r="F536" s="4"/>
       <c r="I536" s="4"/>
+      <c r="J536" s="4"/>
     </row>
     <row r="537" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A537" s="4"/>
@@ -5811,6 +6676,7 @@
       <c r="E537" s="4"/>
       <c r="F537" s="4"/>
       <c r="I537" s="4"/>
+      <c r="J537" s="4"/>
     </row>
     <row r="538" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A538" s="4"/>
@@ -5820,6 +6686,7 @@
       <c r="E538" s="4"/>
       <c r="F538" s="4"/>
       <c r="I538" s="4"/>
+      <c r="J538" s="4"/>
     </row>
     <row r="539" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A539" s="4"/>
@@ -5829,6 +6696,7 @@
       <c r="E539" s="4"/>
       <c r="F539" s="4"/>
       <c r="I539" s="4"/>
+      <c r="J539" s="4"/>
     </row>
     <row r="540" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A540" s="4"/>
@@ -5838,6 +6706,7 @@
       <c r="E540" s="4"/>
       <c r="F540" s="4"/>
       <c r="I540" s="4"/>
+      <c r="J540" s="4"/>
     </row>
     <row r="541" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A541" s="4"/>
@@ -5847,6 +6716,7 @@
       <c r="E541" s="4"/>
       <c r="F541" s="4"/>
       <c r="I541" s="4"/>
+      <c r="J541" s="4"/>
     </row>
     <row r="542" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A542" s="4"/>
@@ -5856,6 +6726,7 @@
       <c r="E542" s="4"/>
       <c r="F542" s="4"/>
       <c r="I542" s="4"/>
+      <c r="J542" s="4"/>
     </row>
     <row r="543" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A543" s="4"/>
@@ -5865,6 +6736,7 @@
       <c r="E543" s="4"/>
       <c r="F543" s="4"/>
       <c r="I543" s="4"/>
+      <c r="J543" s="4"/>
     </row>
     <row r="544" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A544" s="4"/>
@@ -5874,6 +6746,7 @@
       <c r="E544" s="4"/>
       <c r="F544" s="4"/>
       <c r="I544" s="4"/>
+      <c r="J544" s="4"/>
     </row>
     <row r="545" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A545" s="4"/>
@@ -5883,6 +6756,7 @@
       <c r="E545" s="4"/>
       <c r="F545" s="4"/>
       <c r="I545" s="4"/>
+      <c r="J545" s="4"/>
     </row>
     <row r="546" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="4"/>
@@ -5892,6 +6766,7 @@
       <c r="E546" s="4"/>
       <c r="F546" s="4"/>
       <c r="I546" s="4"/>
+      <c r="J546" s="4"/>
     </row>
     <row r="547" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="4"/>
@@ -5901,6 +6776,7 @@
       <c r="E547" s="4"/>
       <c r="F547" s="4"/>
       <c r="I547" s="4"/>
+      <c r="J547" s="4"/>
     </row>
     <row r="548" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A548" s="4"/>
@@ -5910,6 +6786,7 @@
       <c r="E548" s="4"/>
       <c r="F548" s="4"/>
       <c r="I548" s="4"/>
+      <c r="J548" s="4"/>
     </row>
     <row r="549" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A549" s="4"/>
@@ -5919,6 +6796,7 @@
       <c r="E549" s="4"/>
       <c r="F549" s="4"/>
       <c r="I549" s="4"/>
+      <c r="J549" s="4"/>
     </row>
     <row r="550" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A550" s="4"/>
@@ -5928,6 +6806,7 @@
       <c r="E550" s="4"/>
       <c r="F550" s="4"/>
       <c r="I550" s="4"/>
+      <c r="J550" s="4"/>
     </row>
     <row r="551" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A551" s="4"/>
@@ -5937,6 +6816,7 @@
       <c r="E551" s="4"/>
       <c r="F551" s="4"/>
       <c r="I551" s="4"/>
+      <c r="J551" s="4"/>
     </row>
     <row r="552" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A552" s="4"/>
@@ -5946,6 +6826,7 @@
       <c r="E552" s="4"/>
       <c r="F552" s="4"/>
       <c r="I552" s="4"/>
+      <c r="J552" s="4"/>
     </row>
     <row r="553" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A553" s="4"/>
@@ -5955,6 +6836,7 @@
       <c r="E553" s="4"/>
       <c r="F553" s="4"/>
       <c r="I553" s="4"/>
+      <c r="J553" s="4"/>
     </row>
     <row r="554" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A554" s="4"/>
@@ -5964,6 +6846,7 @@
       <c r="E554" s="4"/>
       <c r="F554" s="4"/>
       <c r="I554" s="4"/>
+      <c r="J554" s="4"/>
     </row>
     <row r="555" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A555" s="4"/>
@@ -5973,6 +6856,7 @@
       <c r="E555" s="4"/>
       <c r="F555" s="4"/>
       <c r="I555" s="4"/>
+      <c r="J555" s="4"/>
     </row>
     <row r="556" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A556" s="4"/>
@@ -5982,6 +6866,7 @@
       <c r="E556" s="4"/>
       <c r="F556" s="4"/>
       <c r="I556" s="4"/>
+      <c r="J556" s="4"/>
     </row>
     <row r="557" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A557" s="4"/>
@@ -5991,6 +6876,7 @@
       <c r="E557" s="4"/>
       <c r="F557" s="4"/>
       <c r="I557" s="4"/>
+      <c r="J557" s="4"/>
     </row>
     <row r="558" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="4"/>
@@ -6000,6 +6886,7 @@
       <c r="E558" s="4"/>
       <c r="F558" s="4"/>
       <c r="I558" s="4"/>
+      <c r="J558" s="4"/>
     </row>
     <row r="559" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="4"/>
@@ -6009,6 +6896,7 @@
       <c r="E559" s="4"/>
       <c r="F559" s="4"/>
       <c r="I559" s="4"/>
+      <c r="J559" s="4"/>
     </row>
     <row r="560" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A560" s="4"/>
@@ -6018,6 +6906,7 @@
       <c r="E560" s="4"/>
       <c r="F560" s="4"/>
       <c r="I560" s="4"/>
+      <c r="J560" s="4"/>
     </row>
     <row r="561" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A561" s="4"/>
@@ -6027,6 +6916,7 @@
       <c r="E561" s="4"/>
       <c r="F561" s="4"/>
       <c r="I561" s="4"/>
+      <c r="J561" s="4"/>
     </row>
     <row r="562" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A562" s="4"/>
@@ -6036,6 +6926,7 @@
       <c r="E562" s="4"/>
       <c r="F562" s="4"/>
       <c r="I562" s="4"/>
+      <c r="J562" s="4"/>
     </row>
     <row r="563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A563" s="4"/>
@@ -6045,6 +6936,7 @@
       <c r="E563" s="4"/>
       <c r="F563" s="4"/>
       <c r="I563" s="4"/>
+      <c r="J563" s="4"/>
     </row>
     <row r="564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A564" s="4"/>
@@ -6054,6 +6946,7 @@
       <c r="E564" s="4"/>
       <c r="F564" s="4"/>
       <c r="I564" s="4"/>
+      <c r="J564" s="4"/>
     </row>
     <row r="565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A565" s="4"/>
@@ -6063,6 +6956,7 @@
       <c r="E565" s="4"/>
       <c r="F565" s="4"/>
       <c r="I565" s="4"/>
+      <c r="J565" s="4"/>
     </row>
     <row r="566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A566" s="4"/>
@@ -6072,6 +6966,7 @@
       <c r="E566" s="4"/>
       <c r="F566" s="4"/>
       <c r="I566" s="4"/>
+      <c r="J566" s="4"/>
     </row>
     <row r="567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A567" s="4"/>
@@ -6081,6 +6976,7 @@
       <c r="E567" s="4"/>
       <c r="F567" s="4"/>
       <c r="I567" s="4"/>
+      <c r="J567" s="4"/>
     </row>
     <row r="568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A568" s="4"/>
@@ -6090,6 +6986,7 @@
       <c r="E568" s="4"/>
       <c r="F568" s="4"/>
       <c r="I568" s="4"/>
+      <c r="J568" s="4"/>
     </row>
     <row r="569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A569" s="4"/>
@@ -6099,6 +6996,7 @@
       <c r="E569" s="4"/>
       <c r="F569" s="4"/>
       <c r="I569" s="4"/>
+      <c r="J569" s="4"/>
     </row>
     <row r="570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A570" s="4"/>
@@ -6108,6 +7006,7 @@
       <c r="E570" s="4"/>
       <c r="F570" s="4"/>
       <c r="I570" s="4"/>
+      <c r="J570" s="4"/>
     </row>
     <row r="571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A571" s="4"/>
@@ -6117,6 +7016,7 @@
       <c r="E571" s="4"/>
       <c r="F571" s="4"/>
       <c r="I571" s="4"/>
+      <c r="J571" s="4"/>
     </row>
     <row r="572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A572" s="4"/>
@@ -6126,6 +7026,7 @@
       <c r="E572" s="4"/>
       <c r="F572" s="4"/>
       <c r="I572" s="4"/>
+      <c r="J572" s="4"/>
     </row>
     <row r="573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A573" s="4"/>
@@ -6135,6 +7036,7 @@
       <c r="E573" s="4"/>
       <c r="F573" s="4"/>
       <c r="I573" s="4"/>
+      <c r="J573" s="4"/>
     </row>
     <row r="574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A574" s="4"/>
@@ -6144,6 +7046,7 @@
       <c r="E574" s="4"/>
       <c r="F574" s="4"/>
       <c r="I574" s="4"/>
+      <c r="J574" s="4"/>
     </row>
     <row r="575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="4"/>
@@ -6153,6 +7056,7 @@
       <c r="E575" s="4"/>
       <c r="F575" s="4"/>
       <c r="I575" s="4"/>
+      <c r="J575" s="4"/>
     </row>
     <row r="576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A576" s="4"/>
@@ -6162,6 +7066,7 @@
       <c r="E576" s="4"/>
       <c r="F576" s="4"/>
       <c r="I576" s="4"/>
+      <c r="J576" s="4"/>
     </row>
     <row r="577" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A577" s="4"/>
@@ -6171,6 +7076,7 @@
       <c r="E577" s="4"/>
       <c r="F577" s="4"/>
       <c r="I577" s="4"/>
+      <c r="J577" s="4"/>
     </row>
     <row r="578" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A578" s="4"/>
@@ -6180,6 +7086,7 @@
       <c r="E578" s="4"/>
       <c r="F578" s="4"/>
       <c r="I578" s="4"/>
+      <c r="J578" s="4"/>
     </row>
     <row r="579" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A579" s="4"/>
@@ -6189,6 +7096,7 @@
       <c r="E579" s="4"/>
       <c r="F579" s="4"/>
       <c r="I579" s="4"/>
+      <c r="J579" s="4"/>
     </row>
     <row r="580" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A580" s="4"/>
@@ -6198,6 +7106,7 @@
       <c r="E580" s="4"/>
       <c r="F580" s="4"/>
       <c r="I580" s="4"/>
+      <c r="J580" s="4"/>
     </row>
     <row r="581" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A581" s="4"/>
@@ -6207,6 +7116,7 @@
       <c r="E581" s="4"/>
       <c r="F581" s="4"/>
       <c r="I581" s="4"/>
+      <c r="J581" s="4"/>
     </row>
     <row r="582" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A582" s="4"/>
@@ -6216,6 +7126,7 @@
       <c r="E582" s="4"/>
       <c r="F582" s="4"/>
       <c r="I582" s="4"/>
+      <c r="J582" s="4"/>
     </row>
     <row r="583" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A583" s="4"/>
@@ -6225,6 +7136,7 @@
       <c r="E583" s="4"/>
       <c r="F583" s="4"/>
       <c r="I583" s="4"/>
+      <c r="J583" s="4"/>
     </row>
     <row r="584" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A584" s="4"/>
@@ -6234,6 +7146,7 @@
       <c r="E584" s="4"/>
       <c r="F584" s="4"/>
       <c r="I584" s="4"/>
+      <c r="J584" s="4"/>
     </row>
     <row r="585" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A585" s="4"/>
@@ -6243,6 +7156,7 @@
       <c r="E585" s="4"/>
       <c r="F585" s="4"/>
       <c r="I585" s="4"/>
+      <c r="J585" s="4"/>
     </row>
     <row r="586" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A586" s="4"/>
@@ -6252,6 +7166,7 @@
       <c r="E586" s="4"/>
       <c r="F586" s="4"/>
       <c r="I586" s="4"/>
+      <c r="J586" s="4"/>
     </row>
     <row r="587" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A587" s="4"/>
@@ -6261,6 +7176,7 @@
       <c r="E587" s="4"/>
       <c r="F587" s="4"/>
       <c r="I587" s="4"/>
+      <c r="J587" s="4"/>
     </row>
     <row r="588" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A588" s="4"/>
@@ -6270,6 +7186,7 @@
       <c r="E588" s="4"/>
       <c r="F588" s="4"/>
       <c r="I588" s="4"/>
+      <c r="J588" s="4"/>
     </row>
     <row r="589" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A589" s="4"/>
@@ -6279,6 +7196,7 @@
       <c r="E589" s="4"/>
       <c r="F589" s="4"/>
       <c r="I589" s="4"/>
+      <c r="J589" s="4"/>
     </row>
     <row r="590" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A590" s="4"/>
@@ -6288,6 +7206,7 @@
       <c r="E590" s="4"/>
       <c r="F590" s="4"/>
       <c r="I590" s="4"/>
+      <c r="J590" s="4"/>
     </row>
     <row r="591" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A591" s="4"/>
@@ -6297,6 +7216,7 @@
       <c r="E591" s="4"/>
       <c r="F591" s="4"/>
       <c r="I591" s="4"/>
+      <c r="J591" s="4"/>
     </row>
     <row r="592" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A592" s="4"/>
@@ -6306,6 +7226,7 @@
       <c r="E592" s="4"/>
       <c r="F592" s="4"/>
       <c r="I592" s="4"/>
+      <c r="J592" s="4"/>
     </row>
     <row r="593" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A593" s="4"/>
@@ -6315,6 +7236,7 @@
       <c r="E593" s="4"/>
       <c r="F593" s="4"/>
       <c r="I593" s="4"/>
+      <c r="J593" s="4"/>
     </row>
     <row r="594" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A594" s="4"/>
@@ -6324,6 +7246,7 @@
       <c r="E594" s="4"/>
       <c r="F594" s="4"/>
       <c r="I594" s="4"/>
+      <c r="J594" s="4"/>
     </row>
     <row r="595" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A595" s="4"/>
@@ -6333,6 +7256,7 @@
       <c r="E595" s="4"/>
       <c r="F595" s="4"/>
       <c r="I595" s="4"/>
+      <c r="J595" s="4"/>
     </row>
     <row r="596" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A596" s="4"/>
@@ -6342,6 +7266,7 @@
       <c r="E596" s="4"/>
       <c r="F596" s="4"/>
       <c r="I596" s="4"/>
+      <c r="J596" s="4"/>
     </row>
     <row r="597" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A597" s="4"/>
@@ -6351,6 +7276,7 @@
       <c r="E597" s="4"/>
       <c r="F597" s="4"/>
       <c r="I597" s="4"/>
+      <c r="J597" s="4"/>
     </row>
     <row r="598" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A598" s="4"/>
@@ -6360,6 +7286,7 @@
       <c r="E598" s="4"/>
       <c r="F598" s="4"/>
       <c r="I598" s="4"/>
+      <c r="J598" s="4"/>
     </row>
     <row r="599" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A599" s="4"/>
@@ -6369,6 +7296,7 @@
       <c r="E599" s="4"/>
       <c r="F599" s="4"/>
       <c r="I599" s="4"/>
+      <c r="J599" s="4"/>
     </row>
     <row r="600" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A600" s="4"/>
@@ -6378,6 +7306,7 @@
       <c r="E600" s="4"/>
       <c r="F600" s="4"/>
       <c r="I600" s="4"/>
+      <c r="J600" s="4"/>
     </row>
     <row r="601" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A601" s="4"/>
@@ -6387,6 +7316,7 @@
       <c r="E601" s="4"/>
       <c r="F601" s="4"/>
       <c r="I601" s="4"/>
+      <c r="J601" s="4"/>
     </row>
     <row r="602" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A602" s="4"/>
@@ -6396,6 +7326,7 @@
       <c r="E602" s="4"/>
       <c r="F602" s="4"/>
       <c r="I602" s="4"/>
+      <c r="J602" s="4"/>
     </row>
     <row r="603" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A603" s="4"/>
@@ -6405,6 +7336,7 @@
       <c r="E603" s="4"/>
       <c r="F603" s="4"/>
       <c r="I603" s="4"/>
+      <c r="J603" s="4"/>
     </row>
     <row r="604" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A604" s="4"/>
@@ -6414,6 +7346,7 @@
       <c r="E604" s="4"/>
       <c r="F604" s="4"/>
       <c r="I604" s="4"/>
+      <c r="J604" s="4"/>
     </row>
     <row r="605" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A605" s="4"/>
@@ -6423,6 +7356,7 @@
       <c r="E605" s="4"/>
       <c r="F605" s="4"/>
       <c r="I605" s="4"/>
+      <c r="J605" s="4"/>
     </row>
     <row r="606" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A606" s="4"/>
@@ -6432,6 +7366,7 @@
       <c r="E606" s="4"/>
       <c r="F606" s="4"/>
       <c r="I606" s="4"/>
+      <c r="J606" s="4"/>
     </row>
     <row r="607" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A607" s="4"/>
@@ -6441,6 +7376,7 @@
       <c r="E607" s="4"/>
       <c r="F607" s="4"/>
       <c r="I607" s="4"/>
+      <c r="J607" s="4"/>
     </row>
     <row r="608" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A608" s="4"/>
@@ -6450,6 +7386,7 @@
       <c r="E608" s="4"/>
       <c r="F608" s="4"/>
       <c r="I608" s="4"/>
+      <c r="J608" s="4"/>
     </row>
     <row r="609" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A609" s="4"/>
@@ -6459,6 +7396,7 @@
       <c r="E609" s="4"/>
       <c r="F609" s="4"/>
       <c r="I609" s="4"/>
+      <c r="J609" s="4"/>
     </row>
     <row r="610" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A610" s="4"/>
@@ -6468,6 +7406,7 @@
       <c r="E610" s="4"/>
       <c r="F610" s="4"/>
       <c r="I610" s="4"/>
+      <c r="J610" s="4"/>
     </row>
     <row r="611" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A611" s="4"/>
@@ -6477,6 +7416,7 @@
       <c r="E611" s="4"/>
       <c r="F611" s="4"/>
       <c r="I611" s="4"/>
+      <c r="J611" s="4"/>
     </row>
     <row r="612" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A612" s="4"/>
@@ -6486,6 +7426,7 @@
       <c r="E612" s="4"/>
       <c r="F612" s="4"/>
       <c r="I612" s="4"/>
+      <c r="J612" s="4"/>
     </row>
     <row r="613" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A613" s="4"/>
@@ -6495,6 +7436,7 @@
       <c r="E613" s="4"/>
       <c r="F613" s="4"/>
       <c r="I613" s="4"/>
+      <c r="J613" s="4"/>
     </row>
     <row r="614" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A614" s="4"/>
@@ -6504,6 +7446,7 @@
       <c r="E614" s="4"/>
       <c r="F614" s="4"/>
       <c r="I614" s="4"/>
+      <c r="J614" s="4"/>
     </row>
     <row r="615" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A615" s="4"/>
@@ -6513,6 +7456,7 @@
       <c r="E615" s="4"/>
       <c r="F615" s="4"/>
       <c r="I615" s="4"/>
+      <c r="J615" s="4"/>
     </row>
     <row r="616" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A616" s="4"/>
@@ -6522,6 +7466,7 @@
       <c r="E616" s="4"/>
       <c r="F616" s="4"/>
       <c r="I616" s="4"/>
+      <c r="J616" s="4"/>
     </row>
     <row r="617" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A617" s="4"/>
@@ -6531,6 +7476,7 @@
       <c r="E617" s="4"/>
       <c r="F617" s="4"/>
       <c r="I617" s="4"/>
+      <c r="J617" s="4"/>
     </row>
     <row r="618" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A618" s="4"/>
@@ -6540,6 +7486,7 @@
       <c r="E618" s="4"/>
       <c r="F618" s="4"/>
       <c r="I618" s="4"/>
+      <c r="J618" s="4"/>
     </row>
     <row r="619" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A619" s="4"/>
@@ -6549,6 +7496,7 @@
       <c r="E619" s="4"/>
       <c r="F619" s="4"/>
       <c r="I619" s="4"/>
+      <c r="J619" s="4"/>
     </row>
     <row r="620" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A620" s="4"/>
@@ -6558,6 +7506,7 @@
       <c r="E620" s="4"/>
       <c r="F620" s="4"/>
       <c r="I620" s="4"/>
+      <c r="J620" s="4"/>
     </row>
     <row r="621" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A621" s="4"/>
@@ -6567,6 +7516,7 @@
       <c r="E621" s="4"/>
       <c r="F621" s="4"/>
       <c r="I621" s="4"/>
+      <c r="J621" s="4"/>
     </row>
     <row r="622" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A622" s="4"/>
@@ -6576,6 +7526,7 @@
       <c r="E622" s="4"/>
       <c r="F622" s="4"/>
       <c r="I622" s="4"/>
+      <c r="J622" s="4"/>
     </row>
     <row r="623" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A623" s="4"/>
@@ -6585,6 +7536,7 @@
       <c r="E623" s="4"/>
       <c r="F623" s="4"/>
       <c r="I623" s="4"/>
+      <c r="J623" s="4"/>
     </row>
     <row r="624" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A624" s="4"/>
@@ -6594,6 +7546,7 @@
       <c r="E624" s="4"/>
       <c r="F624" s="4"/>
       <c r="I624" s="4"/>
+      <c r="J624" s="4"/>
     </row>
     <row r="625" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A625" s="4"/>
@@ -6603,6 +7556,7 @@
       <c r="E625" s="4"/>
       <c r="F625" s="4"/>
       <c r="I625" s="4"/>
+      <c r="J625" s="4"/>
     </row>
     <row r="626" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A626" s="4"/>
@@ -6612,6 +7566,7 @@
       <c r="E626" s="4"/>
       <c r="F626" s="4"/>
       <c r="I626" s="4"/>
+      <c r="J626" s="4"/>
     </row>
     <row r="627" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A627" s="4"/>
@@ -6621,6 +7576,7 @@
       <c r="E627" s="4"/>
       <c r="F627" s="4"/>
       <c r="I627" s="4"/>
+      <c r="J627" s="4"/>
     </row>
     <row r="628" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A628" s="4"/>
@@ -6630,6 +7586,7 @@
       <c r="E628" s="4"/>
       <c r="F628" s="4"/>
       <c r="I628" s="4"/>
+      <c r="J628" s="4"/>
     </row>
     <row r="629" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A629" s="4"/>
@@ -6639,6 +7596,7 @@
       <c r="E629" s="4"/>
       <c r="F629" s="4"/>
       <c r="I629" s="4"/>
+      <c r="J629" s="4"/>
     </row>
     <row r="630" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A630" s="4"/>
@@ -6648,6 +7606,7 @@
       <c r="E630" s="4"/>
       <c r="F630" s="4"/>
       <c r="I630" s="4"/>
+      <c r="J630" s="4"/>
     </row>
     <row r="631" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A631" s="4"/>
@@ -6657,6 +7616,7 @@
       <c r="E631" s="4"/>
       <c r="F631" s="4"/>
       <c r="I631" s="4"/>
+      <c r="J631" s="4"/>
     </row>
     <row r="632" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A632" s="4"/>
@@ -6666,6 +7626,7 @@
       <c r="E632" s="4"/>
       <c r="F632" s="4"/>
       <c r="I632" s="4"/>
+      <c r="J632" s="4"/>
     </row>
     <row r="633" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A633" s="4"/>
@@ -6675,6 +7636,7 @@
       <c r="E633" s="4"/>
       <c r="F633" s="4"/>
       <c r="I633" s="4"/>
+      <c r="J633" s="4"/>
     </row>
     <row r="634" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A634" s="4"/>
@@ -6684,6 +7646,7 @@
       <c r="E634" s="4"/>
       <c r="F634" s="4"/>
       <c r="I634" s="4"/>
+      <c r="J634" s="4"/>
     </row>
     <row r="635" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A635" s="4"/>
@@ -6693,6 +7656,7 @@
       <c r="E635" s="4"/>
       <c r="F635" s="4"/>
       <c r="I635" s="4"/>
+      <c r="J635" s="4"/>
     </row>
     <row r="636" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A636" s="4"/>
@@ -6702,6 +7666,7 @@
       <c r="E636" s="4"/>
       <c r="F636" s="4"/>
       <c r="I636" s="4"/>
+      <c r="J636" s="4"/>
     </row>
     <row r="637" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A637" s="4"/>
@@ -6711,6 +7676,7 @@
       <c r="E637" s="4"/>
       <c r="F637" s="4"/>
       <c r="I637" s="4"/>
+      <c r="J637" s="4"/>
     </row>
     <row r="638" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A638" s="4"/>
@@ -6720,6 +7686,7 @@
       <c r="E638" s="4"/>
       <c r="F638" s="4"/>
       <c r="I638" s="4"/>
+      <c r="J638" s="4"/>
     </row>
     <row r="639" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A639" s="4"/>
@@ -6729,6 +7696,7 @@
       <c r="E639" s="4"/>
       <c r="F639" s="4"/>
       <c r="I639" s="4"/>
+      <c r="J639" s="4"/>
     </row>
     <row r="640" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A640" s="4"/>
@@ -6738,6 +7706,7 @@
       <c r="E640" s="4"/>
       <c r="F640" s="4"/>
       <c r="I640" s="4"/>
+      <c r="J640" s="4"/>
     </row>
     <row r="641" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A641" s="4"/>
@@ -6747,6 +7716,7 @@
       <c r="E641" s="4"/>
       <c r="F641" s="4"/>
       <c r="I641" s="4"/>
+      <c r="J641" s="4"/>
     </row>
     <row r="642" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A642" s="4"/>
@@ -6756,6 +7726,7 @@
       <c r="E642" s="4"/>
       <c r="F642" s="4"/>
       <c r="I642" s="4"/>
+      <c r="J642" s="4"/>
     </row>
     <row r="643" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A643" s="4"/>
@@ -6765,6 +7736,7 @@
       <c r="E643" s="4"/>
       <c r="F643" s="4"/>
       <c r="I643" s="4"/>
+      <c r="J643" s="4"/>
     </row>
     <row r="644" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A644" s="4"/>
@@ -6774,6 +7746,7 @@
       <c r="E644" s="4"/>
       <c r="F644" s="4"/>
       <c r="I644" s="4"/>
+      <c r="J644" s="4"/>
     </row>
     <row r="645" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="4"/>
@@ -6783,6 +7756,7 @@
       <c r="E645" s="4"/>
       <c r="F645" s="4"/>
       <c r="I645" s="4"/>
+      <c r="J645" s="4"/>
     </row>
     <row r="646" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A646" s="4"/>
@@ -6792,6 +7766,7 @@
       <c r="E646" s="4"/>
       <c r="F646" s="4"/>
       <c r="I646" s="4"/>
+      <c r="J646" s="4"/>
     </row>
     <row r="647" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A647" s="4"/>
@@ -6801,6 +7776,7 @@
       <c r="E647" s="4"/>
       <c r="F647" s="4"/>
       <c r="I647" s="4"/>
+      <c r="J647" s="4"/>
     </row>
     <row r="648" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A648" s="4"/>
@@ -6810,6 +7786,7 @@
       <c r="E648" s="4"/>
       <c r="F648" s="4"/>
       <c r="I648" s="4"/>
+      <c r="J648" s="4"/>
     </row>
     <row r="649" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A649" s="4"/>
@@ -6819,6 +7796,7 @@
       <c r="E649" s="4"/>
       <c r="F649" s="4"/>
       <c r="I649" s="4"/>
+      <c r="J649" s="4"/>
     </row>
     <row r="650" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A650" s="4"/>
@@ -6828,6 +7806,7 @@
       <c r="E650" s="4"/>
       <c r="F650" s="4"/>
       <c r="I650" s="4"/>
+      <c r="J650" s="4"/>
     </row>
     <row r="651" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A651" s="4"/>
@@ -6837,6 +7816,7 @@
       <c r="E651" s="4"/>
       <c r="F651" s="4"/>
       <c r="I651" s="4"/>
+      <c r="J651" s="4"/>
     </row>
     <row r="652" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A652" s="4"/>
@@ -6846,6 +7826,7 @@
       <c r="E652" s="4"/>
       <c r="F652" s="4"/>
       <c r="I652" s="4"/>
+      <c r="J652" s="4"/>
     </row>
     <row r="653" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A653" s="4"/>
@@ -6855,6 +7836,7 @@
       <c r="E653" s="4"/>
       <c r="F653" s="4"/>
       <c r="I653" s="4"/>
+      <c r="J653" s="4"/>
     </row>
     <row r="654" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A654" s="4"/>
@@ -6864,6 +7846,7 @@
       <c r="E654" s="4"/>
       <c r="F654" s="4"/>
       <c r="I654" s="4"/>
+      <c r="J654" s="4"/>
     </row>
     <row r="655" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A655" s="4"/>
@@ -6873,6 +7856,7 @@
       <c r="E655" s="4"/>
       <c r="F655" s="4"/>
       <c r="I655" s="4"/>
+      <c r="J655" s="4"/>
     </row>
     <row r="656" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A656" s="4"/>
@@ -6882,6 +7866,7 @@
       <c r="E656" s="4"/>
       <c r="F656" s="4"/>
       <c r="I656" s="4"/>
+      <c r="J656" s="4"/>
     </row>
     <row r="657" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A657" s="4"/>
@@ -6891,6 +7876,7 @@
       <c r="E657" s="4"/>
       <c r="F657" s="4"/>
       <c r="I657" s="4"/>
+      <c r="J657" s="4"/>
     </row>
     <row r="658" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A658" s="4"/>
@@ -6900,6 +7886,7 @@
       <c r="E658" s="4"/>
       <c r="F658" s="4"/>
       <c r="I658" s="4"/>
+      <c r="J658" s="4"/>
     </row>
     <row r="659" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A659" s="4"/>
@@ -6909,6 +7896,7 @@
       <c r="E659" s="4"/>
       <c r="F659" s="4"/>
       <c r="I659" s="4"/>
+      <c r="J659" s="4"/>
     </row>
     <row r="660" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A660" s="4"/>
@@ -6918,6 +7906,7 @@
       <c r="E660" s="4"/>
       <c r="F660" s="4"/>
       <c r="I660" s="4"/>
+      <c r="J660" s="4"/>
     </row>
     <row r="661" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A661" s="4"/>
@@ -6927,6 +7916,7 @@
       <c r="E661" s="4"/>
       <c r="F661" s="4"/>
       <c r="I661" s="4"/>
+      <c r="J661" s="4"/>
     </row>
     <row r="662" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A662" s="4"/>
@@ -6936,6 +7926,7 @@
       <c r="E662" s="4"/>
       <c r="F662" s="4"/>
       <c r="I662" s="4"/>
+      <c r="J662" s="4"/>
     </row>
     <row r="663" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A663" s="4"/>
@@ -6945,6 +7936,7 @@
       <c r="E663" s="4"/>
       <c r="F663" s="4"/>
       <c r="I663" s="4"/>
+      <c r="J663" s="4"/>
     </row>
     <row r="664" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A664" s="4"/>
@@ -6954,6 +7946,7 @@
       <c r="E664" s="4"/>
       <c r="F664" s="4"/>
       <c r="I664" s="4"/>
+      <c r="J664" s="4"/>
     </row>
     <row r="665" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A665" s="4"/>
@@ -6963,6 +7956,7 @@
       <c r="E665" s="4"/>
       <c r="F665" s="4"/>
       <c r="I665" s="4"/>
+      <c r="J665" s="4"/>
     </row>
     <row r="666" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A666" s="4"/>
@@ -6972,6 +7966,7 @@
       <c r="E666" s="4"/>
       <c r="F666" s="4"/>
       <c r="I666" s="4"/>
+      <c r="J666" s="4"/>
     </row>
     <row r="667" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A667" s="4"/>
@@ -6981,6 +7976,7 @@
       <c r="E667" s="4"/>
       <c r="F667" s="4"/>
       <c r="I667" s="4"/>
+      <c r="J667" s="4"/>
     </row>
     <row r="668" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A668" s="4"/>
@@ -6990,6 +7986,7 @@
       <c r="E668" s="4"/>
       <c r="F668" s="4"/>
       <c r="I668" s="4"/>
+      <c r="J668" s="4"/>
     </row>
     <row r="669" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A669" s="4"/>
@@ -6999,6 +7996,7 @@
       <c r="E669" s="4"/>
       <c r="F669" s="4"/>
       <c r="I669" s="4"/>
+      <c r="J669" s="4"/>
     </row>
     <row r="670" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A670" s="4"/>
@@ -7008,6 +8006,7 @@
       <c r="E670" s="4"/>
       <c r="F670" s="4"/>
       <c r="I670" s="4"/>
+      <c r="J670" s="4"/>
     </row>
     <row r="671" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A671" s="4"/>
@@ -7017,6 +8016,7 @@
       <c r="E671" s="4"/>
       <c r="F671" s="4"/>
       <c r="I671" s="4"/>
+      <c r="J671" s="4"/>
     </row>
     <row r="672" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A672" s="4"/>
@@ -7026,6 +8026,7 @@
       <c r="E672" s="4"/>
       <c r="F672" s="4"/>
       <c r="I672" s="4"/>
+      <c r="J672" s="4"/>
     </row>
     <row r="673" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A673" s="4"/>
@@ -7035,6 +8036,7 @@
       <c r="E673" s="4"/>
       <c r="F673" s="4"/>
       <c r="I673" s="4"/>
+      <c r="J673" s="4"/>
     </row>
     <row r="674" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A674" s="4"/>
@@ -7044,6 +8046,7 @@
       <c r="E674" s="4"/>
       <c r="F674" s="4"/>
       <c r="I674" s="4"/>
+      <c r="J674" s="4"/>
     </row>
     <row r="675" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A675" s="4"/>
@@ -7053,6 +8056,7 @@
       <c r="E675" s="4"/>
       <c r="F675" s="4"/>
       <c r="I675" s="4"/>
+      <c r="J675" s="4"/>
     </row>
     <row r="676" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A676" s="4"/>
@@ -7062,6 +8066,7 @@
       <c r="E676" s="4"/>
       <c r="F676" s="4"/>
       <c r="I676" s="4"/>
+      <c r="J676" s="4"/>
     </row>
     <row r="677" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A677" s="4"/>
@@ -7071,6 +8076,7 @@
       <c r="E677" s="4"/>
       <c r="F677" s="4"/>
       <c r="I677" s="4"/>
+      <c r="J677" s="4"/>
     </row>
     <row r="678" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A678" s="4"/>
@@ -7080,6 +8086,7 @@
       <c r="E678" s="4"/>
       <c r="F678" s="4"/>
       <c r="I678" s="4"/>
+      <c r="J678" s="4"/>
     </row>
     <row r="679" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A679" s="4"/>
@@ -7089,6 +8096,7 @@
       <c r="E679" s="4"/>
       <c r="F679" s="4"/>
       <c r="I679" s="4"/>
+      <c r="J679" s="4"/>
     </row>
     <row r="680" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A680" s="4"/>
@@ -7098,6 +8106,7 @@
       <c r="E680" s="4"/>
       <c r="F680" s="4"/>
       <c r="I680" s="4"/>
+      <c r="J680" s="4"/>
     </row>
     <row r="681" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A681" s="4"/>
@@ -7107,6 +8116,7 @@
       <c r="E681" s="4"/>
       <c r="F681" s="4"/>
       <c r="I681" s="4"/>
+      <c r="J681" s="4"/>
     </row>
     <row r="682" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A682" s="4"/>
@@ -7116,6 +8126,7 @@
       <c r="E682" s="4"/>
       <c r="F682" s="4"/>
       <c r="I682" s="4"/>
+      <c r="J682" s="4"/>
     </row>
     <row r="683" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A683" s="4"/>
@@ -7125,6 +8136,7 @@
       <c r="E683" s="4"/>
       <c r="F683" s="4"/>
       <c r="I683" s="4"/>
+      <c r="J683" s="4"/>
     </row>
     <row r="684" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A684" s="4"/>
@@ -7134,6 +8146,7 @@
       <c r="E684" s="4"/>
       <c r="F684" s="4"/>
       <c r="I684" s="4"/>
+      <c r="J684" s="4"/>
     </row>
     <row r="685" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A685" s="4"/>
@@ -7143,6 +8156,7 @@
       <c r="E685" s="4"/>
       <c r="F685" s="4"/>
       <c r="I685" s="4"/>
+      <c r="J685" s="4"/>
     </row>
     <row r="686" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A686" s="4"/>
@@ -7152,6 +8166,7 @@
       <c r="E686" s="4"/>
       <c r="F686" s="4"/>
       <c r="I686" s="4"/>
+      <c r="J686" s="4"/>
     </row>
     <row r="687" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A687" s="4"/>
@@ -7161,6 +8176,7 @@
       <c r="E687" s="4"/>
       <c r="F687" s="4"/>
       <c r="I687" s="4"/>
+      <c r="J687" s="4"/>
     </row>
     <row r="688" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A688" s="4"/>
@@ -7170,6 +8186,7 @@
       <c r="E688" s="4"/>
       <c r="F688" s="4"/>
       <c r="I688" s="4"/>
+      <c r="J688" s="4"/>
     </row>
     <row r="689" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A689" s="4"/>
@@ -7179,6 +8196,7 @@
       <c r="E689" s="4"/>
       <c r="F689" s="4"/>
       <c r="I689" s="4"/>
+      <c r="J689" s="4"/>
     </row>
     <row r="690" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A690" s="4"/>
@@ -7188,6 +8206,7 @@
       <c r="E690" s="4"/>
       <c r="F690" s="4"/>
       <c r="I690" s="4"/>
+      <c r="J690" s="4"/>
     </row>
     <row r="691" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A691" s="4"/>
@@ -7197,6 +8216,7 @@
       <c r="E691" s="4"/>
       <c r="F691" s="4"/>
       <c r="I691" s="4"/>
+      <c r="J691" s="4"/>
     </row>
     <row r="692" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A692" s="4"/>
@@ -7206,6 +8226,7 @@
       <c r="E692" s="4"/>
       <c r="F692" s="4"/>
       <c r="I692" s="4"/>
+      <c r="J692" s="4"/>
     </row>
     <row r="693" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A693" s="4"/>
@@ -7215,6 +8236,7 @@
       <c r="E693" s="4"/>
       <c r="F693" s="4"/>
       <c r="I693" s="4"/>
+      <c r="J693" s="4"/>
     </row>
     <row r="694" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A694" s="4"/>
@@ -7224,6 +8246,7 @@
       <c r="E694" s="4"/>
       <c r="F694" s="4"/>
       <c r="I694" s="4"/>
+      <c r="J694" s="4"/>
     </row>
     <row r="695" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A695" s="4"/>
@@ -7233,6 +8256,7 @@
       <c r="E695" s="4"/>
       <c r="F695" s="4"/>
       <c r="I695" s="4"/>
+      <c r="J695" s="4"/>
     </row>
     <row r="696" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A696" s="4"/>
@@ -7242,6 +8266,7 @@
       <c r="E696" s="4"/>
       <c r="F696" s="4"/>
       <c r="I696" s="4"/>
+      <c r="J696" s="4"/>
     </row>
     <row r="697" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A697" s="4"/>
@@ -7251,6 +8276,7 @@
       <c r="E697" s="4"/>
       <c r="F697" s="4"/>
       <c r="I697" s="4"/>
+      <c r="J697" s="4"/>
     </row>
     <row r="698" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A698" s="4"/>
@@ -7260,6 +8286,7 @@
       <c r="E698" s="4"/>
       <c r="F698" s="4"/>
       <c r="I698" s="4"/>
+      <c r="J698" s="4"/>
     </row>
     <row r="699" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A699" s="4"/>
@@ -7269,6 +8296,7 @@
       <c r="E699" s="4"/>
       <c r="F699" s="4"/>
       <c r="I699" s="4"/>
+      <c r="J699" s="4"/>
     </row>
     <row r="700" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A700" s="4"/>
@@ -7278,6 +8306,7 @@
       <c r="E700" s="4"/>
       <c r="F700" s="4"/>
       <c r="I700" s="4"/>
+      <c r="J700" s="4"/>
     </row>
     <row r="701" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A701" s="4"/>
@@ -7287,6 +8316,7 @@
       <c r="E701" s="4"/>
       <c r="F701" s="4"/>
       <c r="I701" s="4"/>
+      <c r="J701" s="4"/>
     </row>
     <row r="702" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A702" s="4"/>
@@ -7296,6 +8326,7 @@
       <c r="E702" s="4"/>
       <c r="F702" s="4"/>
       <c r="I702" s="4"/>
+      <c r="J702" s="4"/>
     </row>
     <row r="703" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A703" s="4"/>
@@ -7305,6 +8336,7 @@
       <c r="E703" s="4"/>
       <c r="F703" s="4"/>
       <c r="I703" s="4"/>
+      <c r="J703" s="4"/>
     </row>
     <row r="704" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A704" s="4"/>
@@ -7314,6 +8346,7 @@
       <c r="E704" s="4"/>
       <c r="F704" s="4"/>
       <c r="I704" s="4"/>
+      <c r="J704" s="4"/>
     </row>
     <row r="705" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A705" s="4"/>
@@ -7323,6 +8356,7 @@
       <c r="E705" s="4"/>
       <c r="F705" s="4"/>
       <c r="I705" s="4"/>
+      <c r="J705" s="4"/>
     </row>
     <row r="706" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A706" s="4"/>
@@ -7332,6 +8366,7 @@
       <c r="E706" s="4"/>
       <c r="F706" s="4"/>
       <c r="I706" s="4"/>
+      <c r="J706" s="4"/>
     </row>
     <row r="707" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A707" s="4"/>
@@ -7341,6 +8376,7 @@
       <c r="E707" s="4"/>
       <c r="F707" s="4"/>
       <c r="I707" s="4"/>
+      <c r="J707" s="4"/>
     </row>
     <row r="708" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A708" s="4"/>
@@ -7350,6 +8386,7 @@
       <c r="E708" s="4"/>
       <c r="F708" s="4"/>
       <c r="I708" s="4"/>
+      <c r="J708" s="4"/>
     </row>
     <row r="709" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A709" s="4"/>
@@ -7359,6 +8396,7 @@
       <c r="E709" s="4"/>
       <c r="F709" s="4"/>
       <c r="I709" s="4"/>
+      <c r="J709" s="4"/>
     </row>
     <row r="710" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A710" s="4"/>
@@ -7368,6 +8406,7 @@
       <c r="E710" s="4"/>
       <c r="F710" s="4"/>
       <c r="I710" s="4"/>
+      <c r="J710" s="4"/>
     </row>
     <row r="711" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A711" s="4"/>
@@ -7377,6 +8416,7 @@
       <c r="E711" s="4"/>
       <c r="F711" s="4"/>
       <c r="I711" s="4"/>
+      <c r="J711" s="4"/>
     </row>
     <row r="712" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A712" s="4"/>
@@ -7386,6 +8426,7 @@
       <c r="E712" s="4"/>
       <c r="F712" s="4"/>
       <c r="I712" s="4"/>
+      <c r="J712" s="4"/>
     </row>
     <row r="713" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A713" s="4"/>
@@ -7395,6 +8436,7 @@
       <c r="E713" s="4"/>
       <c r="F713" s="4"/>
       <c r="I713" s="4"/>
+      <c r="J713" s="4"/>
     </row>
     <row r="714" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A714" s="4"/>
@@ -7404,6 +8446,7 @@
       <c r="E714" s="4"/>
       <c r="F714" s="4"/>
       <c r="I714" s="4"/>
+      <c r="J714" s="4"/>
     </row>
     <row r="715" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A715" s="4"/>
@@ -7413,6 +8456,7 @@
       <c r="E715" s="4"/>
       <c r="F715" s="4"/>
       <c r="I715" s="4"/>
+      <c r="J715" s="4"/>
     </row>
     <row r="716" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A716" s="4"/>
@@ -7422,6 +8466,7 @@
       <c r="E716" s="4"/>
       <c r="F716" s="4"/>
       <c r="I716" s="4"/>
+      <c r="J716" s="4"/>
     </row>
     <row r="717" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A717" s="4"/>
@@ -7431,6 +8476,7 @@
       <c r="E717" s="4"/>
       <c r="F717" s="4"/>
       <c r="I717" s="4"/>
+      <c r="J717" s="4"/>
     </row>
     <row r="718" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A718" s="4"/>
@@ -7440,6 +8486,7 @@
       <c r="E718" s="4"/>
       <c r="F718" s="4"/>
       <c r="I718" s="4"/>
+      <c r="J718" s="4"/>
     </row>
     <row r="719" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A719" s="4"/>
@@ -7449,6 +8496,7 @@
       <c r="E719" s="4"/>
       <c r="F719" s="4"/>
       <c r="I719" s="4"/>
+      <c r="J719" s="4"/>
     </row>
     <row r="720" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A720" s="4"/>
@@ -7458,6 +8506,7 @@
       <c r="E720" s="4"/>
       <c r="F720" s="4"/>
       <c r="I720" s="4"/>
+      <c r="J720" s="4"/>
     </row>
     <row r="721" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A721" s="4"/>
@@ -7467,6 +8516,7 @@
       <c r="E721" s="4"/>
       <c r="F721" s="4"/>
       <c r="I721" s="4"/>
+      <c r="J721" s="4"/>
     </row>
     <row r="722" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A722" s="4"/>
@@ -7476,6 +8526,7 @@
       <c r="E722" s="4"/>
       <c r="F722" s="4"/>
       <c r="I722" s="4"/>
+      <c r="J722" s="4"/>
     </row>
     <row r="723" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A723" s="4"/>
@@ -7485,6 +8536,7 @@
       <c r="E723" s="4"/>
       <c r="F723" s="4"/>
       <c r="I723" s="4"/>
+      <c r="J723" s="4"/>
     </row>
     <row r="724" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A724" s="4"/>
@@ -7494,6 +8546,7 @@
       <c r="E724" s="4"/>
       <c r="F724" s="4"/>
       <c r="I724" s="4"/>
+      <c r="J724" s="4"/>
     </row>
     <row r="725" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A725" s="4"/>
@@ -7503,6 +8556,7 @@
       <c r="E725" s="4"/>
       <c r="F725" s="4"/>
       <c r="I725" s="4"/>
+      <c r="J725" s="4"/>
     </row>
     <row r="726" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A726" s="4"/>
@@ -7512,6 +8566,7 @@
       <c r="E726" s="4"/>
       <c r="F726" s="4"/>
       <c r="I726" s="4"/>
+      <c r="J726" s="4"/>
     </row>
     <row r="727" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A727" s="4"/>
@@ -7521,6 +8576,7 @@
       <c r="E727" s="4"/>
       <c r="F727" s="4"/>
       <c r="I727" s="4"/>
+      <c r="J727" s="4"/>
     </row>
     <row r="728" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A728" s="4"/>
@@ -7530,6 +8586,7 @@
       <c r="E728" s="4"/>
       <c r="F728" s="4"/>
       <c r="I728" s="4"/>
+      <c r="J728" s="4"/>
     </row>
     <row r="729" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A729" s="4"/>
@@ -7539,6 +8596,7 @@
       <c r="E729" s="4"/>
       <c r="F729" s="4"/>
       <c r="I729" s="4"/>
+      <c r="J729" s="4"/>
     </row>
     <row r="730" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A730" s="4"/>
@@ -7548,6 +8606,7 @@
       <c r="E730" s="4"/>
       <c r="F730" s="4"/>
       <c r="I730" s="4"/>
+      <c r="J730" s="4"/>
     </row>
     <row r="731" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A731" s="4"/>
@@ -7557,6 +8616,7 @@
       <c r="E731" s="4"/>
       <c r="F731" s="4"/>
       <c r="I731" s="4"/>
+      <c r="J731" s="4"/>
     </row>
     <row r="732" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A732" s="4"/>
@@ -7566,6 +8626,7 @@
       <c r="E732" s="4"/>
       <c r="F732" s="4"/>
       <c r="I732" s="4"/>
+      <c r="J732" s="4"/>
     </row>
     <row r="733" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A733" s="4"/>
@@ -7575,6 +8636,7 @@
       <c r="E733" s="4"/>
       <c r="F733" s="4"/>
       <c r="I733" s="4"/>
+      <c r="J733" s="4"/>
     </row>
     <row r="734" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A734" s="4"/>
@@ -7584,6 +8646,7 @@
       <c r="E734" s="4"/>
       <c r="F734" s="4"/>
       <c r="I734" s="4"/>
+      <c r="J734" s="4"/>
     </row>
     <row r="735" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A735" s="4"/>
@@ -7593,6 +8656,7 @@
       <c r="E735" s="4"/>
       <c r="F735" s="4"/>
       <c r="I735" s="4"/>
+      <c r="J735" s="4"/>
     </row>
     <row r="736" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A736" s="4"/>
@@ -7602,6 +8666,7 @@
       <c r="E736" s="4"/>
       <c r="F736" s="4"/>
       <c r="I736" s="4"/>
+      <c r="J736" s="4"/>
     </row>
     <row r="737" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A737" s="4"/>
@@ -7611,6 +8676,7 @@
       <c r="E737" s="4"/>
       <c r="F737" s="4"/>
       <c r="I737" s="4"/>
+      <c r="J737" s="4"/>
     </row>
     <row r="738" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A738" s="4"/>
@@ -7620,6 +8686,7 @@
       <c r="E738" s="4"/>
       <c r="F738" s="4"/>
       <c r="I738" s="4"/>
+      <c r="J738" s="4"/>
     </row>
     <row r="739" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A739" s="4"/>
@@ -7629,6 +8696,7 @@
       <c r="E739" s="4"/>
       <c r="F739" s="4"/>
       <c r="I739" s="4"/>
+      <c r="J739" s="4"/>
     </row>
     <row r="740" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A740" s="4"/>
@@ -7638,6 +8706,7 @@
       <c r="E740" s="4"/>
       <c r="F740" s="4"/>
       <c r="I740" s="4"/>
+      <c r="J740" s="4"/>
     </row>
     <row r="741" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A741" s="4"/>
@@ -7647,6 +8716,7 @@
       <c r="E741" s="4"/>
       <c r="F741" s="4"/>
       <c r="I741" s="4"/>
+      <c r="J741" s="4"/>
     </row>
     <row r="742" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A742" s="4"/>
@@ -7656,6 +8726,7 @@
       <c r="E742" s="4"/>
       <c r="F742" s="4"/>
       <c r="I742" s="4"/>
+      <c r="J742" s="4"/>
     </row>
     <row r="743" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A743" s="4"/>
@@ -7665,6 +8736,7 @@
       <c r="E743" s="4"/>
       <c r="F743" s="4"/>
       <c r="I743" s="4"/>
+      <c r="J743" s="4"/>
     </row>
     <row r="744" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A744" s="4"/>
@@ -7674,6 +8746,7 @@
       <c r="E744" s="4"/>
       <c r="F744" s="4"/>
       <c r="I744" s="4"/>
+      <c r="J744" s="4"/>
     </row>
     <row r="745" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A745" s="4"/>
@@ -7683,6 +8756,7 @@
       <c r="E745" s="4"/>
       <c r="F745" s="4"/>
       <c r="I745" s="4"/>
+      <c r="J745" s="4"/>
     </row>
     <row r="746" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A746" s="4"/>
@@ -7692,6 +8766,7 @@
       <c r="E746" s="4"/>
       <c r="F746" s="4"/>
       <c r="I746" s="4"/>
+      <c r="J746" s="4"/>
     </row>
     <row r="747" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A747" s="4"/>
@@ -7701,6 +8776,7 @@
       <c r="E747" s="4"/>
       <c r="F747" s="4"/>
       <c r="I747" s="4"/>
+      <c r="J747" s="4"/>
     </row>
     <row r="748" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A748" s="4"/>
@@ -7710,6 +8786,7 @@
       <c r="E748" s="4"/>
       <c r="F748" s="4"/>
       <c r="I748" s="4"/>
+      <c r="J748" s="4"/>
     </row>
     <row r="749" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A749" s="4"/>
@@ -7719,6 +8796,7 @@
       <c r="E749" s="4"/>
       <c r="F749" s="4"/>
       <c r="I749" s="4"/>
+      <c r="J749" s="4"/>
     </row>
     <row r="750" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A750" s="4"/>
@@ -7728,6 +8806,7 @@
       <c r="E750" s="4"/>
       <c r="F750" s="4"/>
       <c r="I750" s="4"/>
+      <c r="J750" s="4"/>
     </row>
     <row r="751" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A751" s="4"/>
@@ -7737,6 +8816,7 @@
       <c r="E751" s="4"/>
       <c r="F751" s="4"/>
       <c r="I751" s="4"/>
+      <c r="J751" s="4"/>
     </row>
     <row r="752" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A752" s="4"/>
@@ -7746,6 +8826,7 @@
       <c r="E752" s="4"/>
       <c r="F752" s="4"/>
       <c r="I752" s="4"/>
+      <c r="J752" s="4"/>
     </row>
     <row r="753" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A753" s="4"/>
@@ -7755,6 +8836,7 @@
       <c r="E753" s="4"/>
       <c r="F753" s="4"/>
       <c r="I753" s="4"/>
+      <c r="J753" s="4"/>
     </row>
     <row r="754" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A754" s="4"/>
@@ -7764,6 +8846,7 @@
       <c r="E754" s="4"/>
       <c r="F754" s="4"/>
       <c r="I754" s="4"/>
+      <c r="J754" s="4"/>
     </row>
     <row r="755" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A755" s="4"/>
@@ -7773,6 +8856,7 @@
       <c r="E755" s="4"/>
       <c r="F755" s="4"/>
       <c r="I755" s="4"/>
+      <c r="J755" s="4"/>
     </row>
     <row r="756" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A756" s="4"/>
@@ -7782,6 +8866,7 @@
       <c r="E756" s="4"/>
       <c r="F756" s="4"/>
       <c r="I756" s="4"/>
+      <c r="J756" s="4"/>
     </row>
     <row r="757" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A757" s="4"/>
@@ -7791,6 +8876,7 @@
       <c r="E757" s="4"/>
       <c r="F757" s="4"/>
       <c r="I757" s="4"/>
+      <c r="J757" s="4"/>
     </row>
     <row r="758" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A758" s="4"/>
@@ -7800,6 +8886,7 @@
       <c r="E758" s="4"/>
       <c r="F758" s="4"/>
       <c r="I758" s="4"/>
+      <c r="J758" s="4"/>
     </row>
     <row r="759" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A759" s="4"/>
@@ -7809,6 +8896,7 @@
       <c r="E759" s="4"/>
       <c r="F759" s="4"/>
       <c r="I759" s="4"/>
+      <c r="J759" s="4"/>
     </row>
     <row r="760" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A760" s="4"/>
@@ -7818,6 +8906,7 @@
       <c r="E760" s="4"/>
       <c r="F760" s="4"/>
       <c r="I760" s="4"/>
+      <c r="J760" s="4"/>
     </row>
     <row r="761" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A761" s="4"/>
@@ -7827,6 +8916,7 @@
       <c r="E761" s="4"/>
       <c r="F761" s="4"/>
       <c r="I761" s="4"/>
+      <c r="J761" s="4"/>
     </row>
     <row r="762" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A762" s="4"/>
@@ -7836,6 +8926,7 @@
       <c r="E762" s="4"/>
       <c r="F762" s="4"/>
       <c r="I762" s="4"/>
+      <c r="J762" s="4"/>
     </row>
     <row r="763" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A763" s="4"/>
@@ -7845,6 +8936,7 @@
       <c r="E763" s="4"/>
       <c r="F763" s="4"/>
       <c r="I763" s="4"/>
+      <c r="J763" s="4"/>
     </row>
     <row r="764" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A764" s="4"/>
@@ -7854,6 +8946,7 @@
       <c r="E764" s="4"/>
       <c r="F764" s="4"/>
       <c r="I764" s="4"/>
+      <c r="J764" s="4"/>
     </row>
     <row r="765" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A765" s="4"/>
@@ -7863,6 +8956,7 @@
       <c r="E765" s="4"/>
       <c r="F765" s="4"/>
       <c r="I765" s="4"/>
+      <c r="J765" s="4"/>
     </row>
     <row r="766" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A766" s="4"/>
@@ -7872,6 +8966,7 @@
       <c r="E766" s="4"/>
       <c r="F766" s="4"/>
       <c r="I766" s="4"/>
+      <c r="J766" s="4"/>
     </row>
     <row r="767" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A767" s="4"/>
@@ -7881,6 +8976,7 @@
       <c r="E767" s="4"/>
       <c r="F767" s="4"/>
       <c r="I767" s="4"/>
+      <c r="J767" s="4"/>
     </row>
     <row r="768" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A768" s="4"/>
@@ -7890,6 +8986,7 @@
       <c r="E768" s="4"/>
       <c r="F768" s="4"/>
       <c r="I768" s="4"/>
+      <c r="J768" s="4"/>
     </row>
     <row r="769" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A769" s="4"/>
@@ -7899,6 +8996,7 @@
       <c r="E769" s="4"/>
       <c r="F769" s="4"/>
       <c r="I769" s="4"/>
+      <c r="J769" s="4"/>
     </row>
     <row r="770" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A770" s="4"/>
@@ -7908,6 +9006,7 @@
       <c r="E770" s="4"/>
       <c r="F770" s="4"/>
       <c r="I770" s="4"/>
+      <c r="J770" s="4"/>
     </row>
     <row r="771" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A771" s="4"/>
@@ -7917,6 +9016,7 @@
       <c r="E771" s="4"/>
       <c r="F771" s="4"/>
       <c r="I771" s="4"/>
+      <c r="J771" s="4"/>
     </row>
     <row r="772" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A772" s="4"/>
@@ -7926,6 +9026,7 @@
       <c r="E772" s="4"/>
       <c r="F772" s="4"/>
       <c r="I772" s="4"/>
+      <c r="J772" s="4"/>
     </row>
     <row r="773" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A773" s="4"/>
@@ -7935,6 +9036,7 @@
       <c r="E773" s="4"/>
       <c r="F773" s="4"/>
       <c r="I773" s="4"/>
+      <c r="J773" s="4"/>
     </row>
     <row r="774" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A774" s="4"/>
@@ -7944,6 +9046,7 @@
       <c r="E774" s="4"/>
       <c r="F774" s="4"/>
       <c r="I774" s="4"/>
+      <c r="J774" s="4"/>
     </row>
     <row r="775" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A775" s="4"/>
@@ -7953,6 +9056,7 @@
       <c r="E775" s="4"/>
       <c r="F775" s="4"/>
       <c r="I775" s="4"/>
+      <c r="J775" s="4"/>
     </row>
     <row r="776" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A776" s="4"/>
@@ -7962,6 +9066,7 @@
       <c r="E776" s="4"/>
       <c r="F776" s="4"/>
       <c r="I776" s="4"/>
+      <c r="J776" s="4"/>
     </row>
     <row r="777" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A777" s="4"/>
@@ -7971,6 +9076,7 @@
       <c r="E777" s="4"/>
       <c r="F777" s="4"/>
       <c r="I777" s="4"/>
+      <c r="J777" s="4"/>
     </row>
     <row r="778" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A778" s="4"/>
@@ -7980,6 +9086,7 @@
       <c r="E778" s="4"/>
       <c r="F778" s="4"/>
       <c r="I778" s="4"/>
+      <c r="J778" s="4"/>
     </row>
     <row r="779" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A779" s="4"/>
@@ -7989,6 +9096,7 @@
       <c r="E779" s="4"/>
       <c r="F779" s="4"/>
       <c r="I779" s="4"/>
+      <c r="J779" s="4"/>
     </row>
     <row r="780" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A780" s="4"/>
@@ -7998,6 +9106,7 @@
       <c r="E780" s="4"/>
       <c r="F780" s="4"/>
       <c r="I780" s="4"/>
+      <c r="J780" s="4"/>
     </row>
     <row r="781" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A781" s="4"/>
@@ -8007,6 +9116,7 @@
       <c r="E781" s="4"/>
       <c r="F781" s="4"/>
       <c r="I781" s="4"/>
+      <c r="J781" s="4"/>
     </row>
     <row r="782" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A782" s="4"/>
@@ -8016,6 +9126,7 @@
       <c r="E782" s="4"/>
       <c r="F782" s="4"/>
       <c r="I782" s="4"/>
+      <c r="J782" s="4"/>
     </row>
     <row r="783" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A783" s="4"/>
@@ -8025,6 +9136,7 @@
       <c r="E783" s="4"/>
       <c r="F783" s="4"/>
       <c r="I783" s="4"/>
+      <c r="J783" s="4"/>
     </row>
     <row r="784" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A784" s="4"/>
@@ -8034,6 +9146,7 @@
       <c r="E784" s="4"/>
       <c r="F784" s="4"/>
       <c r="I784" s="4"/>
+      <c r="J784" s="4"/>
     </row>
     <row r="785" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A785" s="4"/>
@@ -8043,6 +9156,7 @@
       <c r="E785" s="4"/>
       <c r="F785" s="4"/>
       <c r="I785" s="4"/>
+      <c r="J785" s="4"/>
     </row>
     <row r="786" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A786" s="4"/>
@@ -8052,6 +9166,7 @@
       <c r="E786" s="4"/>
       <c r="F786" s="4"/>
       <c r="I786" s="4"/>
+      <c r="J786" s="4"/>
     </row>
     <row r="787" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A787" s="4"/>
@@ -8061,6 +9176,7 @@
       <c r="E787" s="4"/>
       <c r="F787" s="4"/>
       <c r="I787" s="4"/>
+      <c r="J787" s="4"/>
     </row>
     <row r="788" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A788" s="4"/>
@@ -8070,6 +9186,7 @@
       <c r="E788" s="4"/>
       <c r="F788" s="4"/>
       <c r="I788" s="4"/>
+      <c r="J788" s="4"/>
     </row>
     <row r="789" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A789" s="4"/>
@@ -8079,6 +9196,7 @@
       <c r="E789" s="4"/>
       <c r="F789" s="4"/>
       <c r="I789" s="4"/>
+      <c r="J789" s="4"/>
     </row>
     <row r="790" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A790" s="4"/>
@@ -8088,6 +9206,7 @@
       <c r="E790" s="4"/>
       <c r="F790" s="4"/>
       <c r="I790" s="4"/>
+      <c r="J790" s="4"/>
     </row>
     <row r="791" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A791" s="4"/>
@@ -8097,6 +9216,7 @@
       <c r="E791" s="4"/>
       <c r="F791" s="4"/>
       <c r="I791" s="4"/>
+      <c r="J791" s="4"/>
     </row>
     <row r="792" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A792" s="4"/>
@@ -8106,6 +9226,7 @@
       <c r="E792" s="4"/>
       <c r="F792" s="4"/>
       <c r="I792" s="4"/>
+      <c r="J792" s="4"/>
     </row>
     <row r="793" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A793" s="4"/>
@@ -8115,6 +9236,7 @@
       <c r="E793" s="4"/>
       <c r="F793" s="4"/>
       <c r="I793" s="4"/>
+      <c r="J793" s="4"/>
     </row>
     <row r="794" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A794" s="4"/>
@@ -8124,6 +9246,7 @@
       <c r="E794" s="4"/>
       <c r="F794" s="4"/>
       <c r="I794" s="4"/>
+      <c r="J794" s="4"/>
     </row>
     <row r="795" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A795" s="4"/>
@@ -8133,6 +9256,7 @@
       <c r="E795" s="4"/>
       <c r="F795" s="4"/>
       <c r="I795" s="4"/>
+      <c r="J795" s="4"/>
     </row>
     <row r="796" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A796" s="4"/>
@@ -8142,6 +9266,7 @@
       <c r="E796" s="4"/>
       <c r="F796" s="4"/>
       <c r="I796" s="4"/>
+      <c r="J796" s="4"/>
     </row>
     <row r="797" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A797" s="4"/>
@@ -8151,6 +9276,7 @@
       <c r="E797" s="4"/>
       <c r="F797" s="4"/>
       <c r="I797" s="4"/>
+      <c r="J797" s="4"/>
     </row>
     <row r="798" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A798" s="4"/>
@@ -8160,6 +9286,7 @@
       <c r="E798" s="4"/>
       <c r="F798" s="4"/>
       <c r="I798" s="4"/>
+      <c r="J798" s="4"/>
     </row>
     <row r="799" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A799" s="4"/>
@@ -8169,6 +9296,7 @@
       <c r="E799" s="4"/>
       <c r="F799" s="4"/>
       <c r="I799" s="4"/>
+      <c r="J799" s="4"/>
     </row>
     <row r="800" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A800" s="4"/>
@@ -8178,6 +9306,7 @@
       <c r="E800" s="4"/>
       <c r="F800" s="4"/>
       <c r="I800" s="4"/>
+      <c r="J800" s="4"/>
     </row>
     <row r="801" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A801" s="4"/>
@@ -8187,6 +9316,7 @@
       <c r="E801" s="4"/>
       <c r="F801" s="4"/>
       <c r="I801" s="4"/>
+      <c r="J801" s="4"/>
     </row>
     <row r="802" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A802" s="4"/>
@@ -8196,6 +9326,7 @@
       <c r="E802" s="4"/>
       <c r="F802" s="4"/>
       <c r="I802" s="4"/>
+      <c r="J802" s="4"/>
     </row>
     <row r="803" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A803" s="4"/>
@@ -8205,6 +9336,7 @@
       <c r="E803" s="4"/>
       <c r="F803" s="4"/>
       <c r="I803" s="4"/>
+      <c r="J803" s="4"/>
     </row>
     <row r="804" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A804" s="4"/>
@@ -8214,6 +9346,7 @@
       <c r="E804" s="4"/>
       <c r="F804" s="4"/>
       <c r="I804" s="4"/>
+      <c r="J804" s="4"/>
     </row>
     <row r="805" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A805" s="4"/>
@@ -8223,6 +9356,7 @@
       <c r="E805" s="4"/>
       <c r="F805" s="4"/>
       <c r="I805" s="4"/>
+      <c r="J805" s="4"/>
     </row>
     <row r="806" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A806" s="4"/>
@@ -8232,6 +9366,7 @@
       <c r="E806" s="4"/>
       <c r="F806" s="4"/>
       <c r="I806" s="4"/>
+      <c r="J806" s="4"/>
     </row>
     <row r="807" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A807" s="4"/>
@@ -8241,6 +9376,7 @@
       <c r="E807" s="4"/>
       <c r="F807" s="4"/>
       <c r="I807" s="4"/>
+      <c r="J807" s="4"/>
     </row>
     <row r="808" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A808" s="4"/>
@@ -8250,6 +9386,7 @@
       <c r="E808" s="4"/>
       <c r="F808" s="4"/>
       <c r="I808" s="4"/>
+      <c r="J808" s="4"/>
     </row>
     <row r="809" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A809" s="4"/>
@@ -8259,6 +9396,7 @@
       <c r="E809" s="4"/>
       <c r="F809" s="4"/>
       <c r="I809" s="4"/>
+      <c r="J809" s="4"/>
     </row>
     <row r="810" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A810" s="4"/>
@@ -8268,6 +9406,7 @@
       <c r="E810" s="4"/>
       <c r="F810" s="4"/>
       <c r="I810" s="4"/>
+      <c r="J810" s="4"/>
     </row>
     <row r="811" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A811" s="4"/>
@@ -8277,6 +9416,7 @@
       <c r="E811" s="4"/>
       <c r="F811" s="4"/>
       <c r="I811" s="4"/>
+      <c r="J811" s="4"/>
     </row>
     <row r="812" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A812" s="4"/>
@@ -8286,6 +9426,7 @@
       <c r="E812" s="4"/>
       <c r="F812" s="4"/>
       <c r="I812" s="4"/>
+      <c r="J812" s="4"/>
     </row>
     <row r="813" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A813" s="4"/>
@@ -8295,6 +9436,7 @@
       <c r="E813" s="4"/>
       <c r="F813" s="4"/>
       <c r="I813" s="4"/>
+      <c r="J813" s="4"/>
     </row>
     <row r="814" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A814" s="4"/>
@@ -8304,6 +9446,7 @@
       <c r="E814" s="4"/>
       <c r="F814" s="4"/>
       <c r="I814" s="4"/>
+      <c r="J814" s="4"/>
     </row>
     <row r="815" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A815" s="4"/>
@@ -8313,6 +9456,7 @@
       <c r="E815" s="4"/>
       <c r="F815" s="4"/>
       <c r="I815" s="4"/>
+      <c r="J815" s="4"/>
     </row>
     <row r="816" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A816" s="4"/>
@@ -8322,6 +9466,7 @@
       <c r="E816" s="4"/>
       <c r="F816" s="4"/>
       <c r="I816" s="4"/>
+      <c r="J816" s="4"/>
     </row>
     <row r="817" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A817" s="4"/>
@@ -8331,6 +9476,7 @@
       <c r="E817" s="4"/>
       <c r="F817" s="4"/>
       <c r="I817" s="4"/>
+      <c r="J817" s="4"/>
     </row>
     <row r="818" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A818" s="4"/>
@@ -8340,6 +9486,7 @@
       <c r="E818" s="4"/>
       <c r="F818" s="4"/>
       <c r="I818" s="4"/>
+      <c r="J818" s="4"/>
     </row>
     <row r="819" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A819" s="4"/>
@@ -8349,6 +9496,7 @@
       <c r="E819" s="4"/>
       <c r="F819" s="4"/>
       <c r="I819" s="4"/>
+      <c r="J819" s="4"/>
     </row>
     <row r="820" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A820" s="4"/>
@@ -8358,6 +9506,7 @@
       <c r="E820" s="4"/>
       <c r="F820" s="4"/>
       <c r="I820" s="4"/>
+      <c r="J820" s="4"/>
     </row>
     <row r="821" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A821" s="4"/>
@@ -8367,6 +9516,7 @@
       <c r="E821" s="4"/>
       <c r="F821" s="4"/>
       <c r="I821" s="4"/>
+      <c r="J821" s="4"/>
     </row>
     <row r="822" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A822" s="4"/>
@@ -8376,6 +9526,7 @@
       <c r="E822" s="4"/>
       <c r="F822" s="4"/>
       <c r="I822" s="4"/>
+      <c r="J822" s="4"/>
     </row>
     <row r="823" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A823" s="4"/>
@@ -8385,6 +9536,7 @@
       <c r="E823" s="4"/>
       <c r="F823" s="4"/>
       <c r="I823" s="4"/>
+      <c r="J823" s="4"/>
     </row>
     <row r="824" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A824" s="4"/>
@@ -8394,6 +9546,7 @@
       <c r="E824" s="4"/>
       <c r="F824" s="4"/>
       <c r="I824" s="4"/>
+      <c r="J824" s="4"/>
     </row>
     <row r="825" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A825" s="4"/>
@@ -8403,6 +9556,7 @@
       <c r="E825" s="4"/>
       <c r="F825" s="4"/>
       <c r="I825" s="4"/>
+      <c r="J825" s="4"/>
     </row>
     <row r="826" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A826" s="4"/>
@@ -8412,6 +9566,7 @@
       <c r="E826" s="4"/>
       <c r="F826" s="4"/>
       <c r="I826" s="4"/>
+      <c r="J826" s="4"/>
     </row>
     <row r="827" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A827" s="4"/>
@@ -8421,6 +9576,7 @@
       <c r="E827" s="4"/>
       <c r="F827" s="4"/>
       <c r="I827" s="4"/>
+      <c r="J827" s="4"/>
     </row>
     <row r="828" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A828" s="4"/>
@@ -8430,6 +9586,7 @@
       <c r="E828" s="4"/>
       <c r="F828" s="4"/>
       <c r="I828" s="4"/>
+      <c r="J828" s="4"/>
     </row>
     <row r="829" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A829" s="4"/>
@@ -8439,6 +9596,7 @@
       <c r="E829" s="4"/>
       <c r="F829" s="4"/>
       <c r="I829" s="4"/>
+      <c r="J829" s="4"/>
     </row>
     <row r="830" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A830" s="4"/>
@@ -8448,6 +9606,7 @@
       <c r="E830" s="4"/>
       <c r="F830" s="4"/>
       <c r="I830" s="4"/>
+      <c r="J830" s="4"/>
     </row>
     <row r="831" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A831" s="4"/>
@@ -8457,6 +9616,7 @@
       <c r="E831" s="4"/>
       <c r="F831" s="4"/>
       <c r="I831" s="4"/>
+      <c r="J831" s="4"/>
     </row>
     <row r="832" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A832" s="4"/>
@@ -8466,6 +9626,7 @@
       <c r="E832" s="4"/>
       <c r="F832" s="4"/>
       <c r="I832" s="4"/>
+      <c r="J832" s="4"/>
     </row>
     <row r="833" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A833" s="4"/>
@@ -8475,6 +9636,7 @@
       <c r="E833" s="4"/>
       <c r="F833" s="4"/>
       <c r="I833" s="4"/>
+      <c r="J833" s="4"/>
     </row>
     <row r="834" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A834" s="4"/>
@@ -8484,6 +9646,7 @@
       <c r="E834" s="4"/>
       <c r="F834" s="4"/>
       <c r="I834" s="4"/>
+      <c r="J834" s="4"/>
     </row>
     <row r="835" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A835" s="4"/>
@@ -8493,6 +9656,7 @@
       <c r="E835" s="4"/>
       <c r="F835" s="4"/>
       <c r="I835" s="4"/>
+      <c r="J835" s="4"/>
     </row>
     <row r="836" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A836" s="4"/>
@@ -8502,6 +9666,7 @@
       <c r="E836" s="4"/>
       <c r="F836" s="4"/>
       <c r="I836" s="4"/>
+      <c r="J836" s="4"/>
     </row>
     <row r="837" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A837" s="4"/>
@@ -8511,6 +9676,7 @@
       <c r="E837" s="4"/>
       <c r="F837" s="4"/>
       <c r="I837" s="4"/>
+      <c r="J837" s="4"/>
     </row>
     <row r="838" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A838" s="4"/>
@@ -8520,6 +9686,7 @@
       <c r="E838" s="4"/>
       <c r="F838" s="4"/>
       <c r="I838" s="4"/>
+      <c r="J838" s="4"/>
     </row>
     <row r="839" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A839" s="4"/>
@@ -8529,6 +9696,7 @@
       <c r="E839" s="4"/>
       <c r="F839" s="4"/>
       <c r="I839" s="4"/>
+      <c r="J839" s="4"/>
     </row>
     <row r="840" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A840" s="4"/>
@@ -8538,6 +9706,7 @@
       <c r="E840" s="4"/>
       <c r="F840" s="4"/>
       <c r="I840" s="4"/>
+      <c r="J840" s="4"/>
     </row>
     <row r="841" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A841" s="4"/>
@@ -8547,6 +9716,7 @@
       <c r="E841" s="4"/>
       <c r="F841" s="4"/>
       <c r="I841" s="4"/>
+      <c r="J841" s="4"/>
     </row>
     <row r="842" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A842" s="4"/>
@@ -8556,6 +9726,7 @@
       <c r="E842" s="4"/>
       <c r="F842" s="4"/>
       <c r="I842" s="4"/>
+      <c r="J842" s="4"/>
     </row>
     <row r="843" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A843" s="4"/>
@@ -8565,6 +9736,7 @@
       <c r="E843" s="4"/>
       <c r="F843" s="4"/>
       <c r="I843" s="4"/>
+      <c r="J843" s="4"/>
     </row>
     <row r="844" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A844" s="4"/>
@@ -8574,6 +9746,7 @@
       <c r="E844" s="4"/>
       <c r="F844" s="4"/>
       <c r="I844" s="4"/>
+      <c r="J844" s="4"/>
     </row>
     <row r="845" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A845" s="4"/>
@@ -8583,6 +9756,7 @@
       <c r="E845" s="4"/>
       <c r="F845" s="4"/>
       <c r="I845" s="4"/>
+      <c r="J845" s="4"/>
     </row>
     <row r="846" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A846" s="4"/>
@@ -8592,6 +9766,7 @@
       <c r="E846" s="4"/>
       <c r="F846" s="4"/>
       <c r="I846" s="4"/>
+      <c r="J846" s="4"/>
     </row>
     <row r="847" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A847" s="4"/>
@@ -8601,6 +9776,7 @@
       <c r="E847" s="4"/>
       <c r="F847" s="4"/>
       <c r="I847" s="4"/>
+      <c r="J847" s="4"/>
     </row>
     <row r="848" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A848" s="4"/>
@@ -8610,6 +9786,7 @@
       <c r="E848" s="4"/>
       <c r="F848" s="4"/>
       <c r="I848" s="4"/>
+      <c r="J848" s="4"/>
     </row>
     <row r="849" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A849" s="4"/>
@@ -8619,6 +9796,7 @@
       <c r="E849" s="4"/>
       <c r="F849" s="4"/>
       <c r="I849" s="4"/>
+      <c r="J849" s="4"/>
     </row>
     <row r="850" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A850" s="4"/>
@@ -8628,6 +9806,7 @@
       <c r="E850" s="4"/>
       <c r="F850" s="4"/>
       <c r="I850" s="4"/>
+      <c r="J850" s="4"/>
     </row>
     <row r="851" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A851" s="4"/>
@@ -8637,6 +9816,7 @@
       <c r="E851" s="4"/>
       <c r="F851" s="4"/>
       <c r="I851" s="4"/>
+      <c r="J851" s="4"/>
     </row>
     <row r="852" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A852" s="4"/>
@@ -8646,6 +9826,7 @@
       <c r="E852" s="4"/>
       <c r="F852" s="4"/>
       <c r="I852" s="4"/>
+      <c r="J852" s="4"/>
     </row>
     <row r="853" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A853" s="4"/>
@@ -8655,6 +9836,7 @@
       <c r="E853" s="4"/>
       <c r="F853" s="4"/>
       <c r="I853" s="4"/>
+      <c r="J853" s="4"/>
     </row>
     <row r="854" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A854" s="4"/>
@@ -8664,6 +9846,7 @@
       <c r="E854" s="4"/>
       <c r="F854" s="4"/>
       <c r="I854" s="4"/>
+      <c r="J854" s="4"/>
     </row>
     <row r="855" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A855" s="4"/>
@@ -8673,6 +9856,7 @@
       <c r="E855" s="4"/>
       <c r="F855" s="4"/>
       <c r="I855" s="4"/>
+      <c r="J855" s="4"/>
     </row>
     <row r="856" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A856" s="4"/>
@@ -8682,6 +9866,7 @@
       <c r="E856" s="4"/>
       <c r="F856" s="4"/>
       <c r="I856" s="4"/>
+      <c r="J856" s="4"/>
     </row>
     <row r="857" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A857" s="4"/>
@@ -8691,6 +9876,7 @@
       <c r="E857" s="4"/>
       <c r="F857" s="4"/>
       <c r="I857" s="4"/>
+      <c r="J857" s="4"/>
     </row>
     <row r="858" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A858" s="4"/>
@@ -8700,6 +9886,7 @@
       <c r="E858" s="4"/>
       <c r="F858" s="4"/>
       <c r="I858" s="4"/>
+      <c r="J858" s="4"/>
     </row>
     <row r="859" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A859" s="4"/>
@@ -8709,6 +9896,7 @@
       <c r="E859" s="4"/>
       <c r="F859" s="4"/>
       <c r="I859" s="4"/>
+      <c r="J859" s="4"/>
     </row>
     <row r="860" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A860" s="4"/>
@@ -8718,6 +9906,7 @@
       <c r="E860" s="4"/>
       <c r="F860" s="4"/>
       <c r="I860" s="4"/>
+      <c r="J860" s="4"/>
     </row>
     <row r="861" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A861" s="4"/>
@@ -8727,6 +9916,7 @@
       <c r="E861" s="4"/>
       <c r="F861" s="4"/>
       <c r="I861" s="4"/>
+      <c r="J861" s="4"/>
     </row>
     <row r="862" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A862" s="4"/>
@@ -8736,6 +9926,7 @@
       <c r="E862" s="4"/>
       <c r="F862" s="4"/>
       <c r="I862" s="4"/>
+      <c r="J862" s="4"/>
     </row>
     <row r="863" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A863" s="4"/>
@@ -8745,6 +9936,7 @@
       <c r="E863" s="4"/>
       <c r="F863" s="4"/>
       <c r="I863" s="4"/>
+      <c r="J863" s="4"/>
     </row>
     <row r="864" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A864" s="4"/>
@@ -8754,6 +9946,7 @@
       <c r="E864" s="4"/>
       <c r="F864" s="4"/>
       <c r="I864" s="4"/>
+      <c r="J864" s="4"/>
     </row>
     <row r="865" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A865" s="4"/>
@@ -8763,6 +9956,7 @@
       <c r="E865" s="4"/>
       <c r="F865" s="4"/>
       <c r="I865" s="4"/>
+      <c r="J865" s="4"/>
     </row>
     <row r="866" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A866" s="4"/>
@@ -8772,6 +9966,7 @@
       <c r="E866" s="4"/>
       <c r="F866" s="4"/>
       <c r="I866" s="4"/>
+      <c r="J866" s="4"/>
     </row>
     <row r="867" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A867" s="4"/>
@@ -8781,6 +9976,7 @@
       <c r="E867" s="4"/>
       <c r="F867" s="4"/>
       <c r="I867" s="4"/>
+      <c r="J867" s="4"/>
     </row>
     <row r="868" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A868" s="4"/>
@@ -8790,6 +9986,7 @@
       <c r="E868" s="4"/>
       <c r="F868" s="4"/>
       <c r="I868" s="4"/>
+      <c r="J868" s="4"/>
     </row>
     <row r="869" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A869" s="4"/>
@@ -8799,6 +9996,7 @@
       <c r="E869" s="4"/>
       <c r="F869" s="4"/>
       <c r="I869" s="4"/>
+      <c r="J869" s="4"/>
     </row>
     <row r="870" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A870" s="4"/>
@@ -8808,6 +10006,7 @@
       <c r="E870" s="4"/>
       <c r="F870" s="4"/>
       <c r="I870" s="4"/>
+      <c r="J870" s="4"/>
     </row>
     <row r="871" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A871" s="4"/>
@@ -8817,6 +10016,7 @@
       <c r="E871" s="4"/>
       <c r="F871" s="4"/>
       <c r="I871" s="4"/>
+      <c r="J871" s="4"/>
     </row>
     <row r="872" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A872" s="4"/>
@@ -8826,6 +10026,7 @@
       <c r="E872" s="4"/>
       <c r="F872" s="4"/>
       <c r="I872" s="4"/>
+      <c r="J872" s="4"/>
     </row>
     <row r="873" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A873" s="4"/>
@@ -8835,6 +10036,7 @@
       <c r="E873" s="4"/>
       <c r="F873" s="4"/>
       <c r="I873" s="4"/>
+      <c r="J873" s="4"/>
     </row>
     <row r="874" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A874" s="4"/>
@@ -8844,6 +10046,7 @@
       <c r="E874" s="4"/>
       <c r="F874" s="4"/>
       <c r="I874" s="4"/>
+      <c r="J874" s="4"/>
     </row>
     <row r="875" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A875" s="4"/>
@@ -8853,6 +10056,7 @@
       <c r="E875" s="4"/>
       <c r="F875" s="4"/>
       <c r="I875" s="4"/>
+      <c r="J875" s="4"/>
     </row>
     <row r="876" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A876" s="4"/>
@@ -8862,6 +10066,7 @@
       <c r="E876" s="4"/>
       <c r="F876" s="4"/>
       <c r="I876" s="4"/>
+      <c r="J876" s="4"/>
     </row>
     <row r="877" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A877" s="4"/>
@@ -8871,6 +10076,7 @@
       <c r="E877" s="4"/>
       <c r="F877" s="4"/>
       <c r="I877" s="4"/>
+      <c r="J877" s="4"/>
     </row>
     <row r="878" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A878" s="4"/>
@@ -8880,6 +10086,7 @@
       <c r="E878" s="4"/>
       <c r="F878" s="4"/>
       <c r="I878" s="4"/>
+      <c r="J878" s="4"/>
     </row>
     <row r="879" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A879" s="4"/>
@@ -8889,6 +10096,7 @@
       <c r="E879" s="4"/>
       <c r="F879" s="4"/>
       <c r="I879" s="4"/>
+      <c r="J879" s="4"/>
     </row>
     <row r="880" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A880" s="4"/>
@@ -8898,6 +10106,7 @@
       <c r="E880" s="4"/>
       <c r="F880" s="4"/>
       <c r="I880" s="4"/>
+      <c r="J880" s="4"/>
     </row>
     <row r="881" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A881" s="4"/>
@@ -8907,6 +10116,7 @@
       <c r="E881" s="4"/>
       <c r="F881" s="4"/>
       <c r="I881" s="4"/>
+      <c r="J881" s="4"/>
     </row>
     <row r="882" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A882" s="4"/>
@@ -8916,6 +10126,7 @@
       <c r="E882" s="4"/>
       <c r="F882" s="4"/>
       <c r="I882" s="4"/>
+      <c r="J882" s="4"/>
     </row>
     <row r="883" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A883" s="4"/>
@@ -8925,6 +10136,7 @@
       <c r="E883" s="4"/>
       <c r="F883" s="4"/>
       <c r="I883" s="4"/>
+      <c r="J883" s="4"/>
     </row>
     <row r="884" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A884" s="4"/>
@@ -8934,6 +10146,7 @@
       <c r="E884" s="4"/>
       <c r="F884" s="4"/>
       <c r="I884" s="4"/>
+      <c r="J884" s="4"/>
     </row>
     <row r="885" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A885" s="4"/>
@@ -8943,6 +10156,7 @@
       <c r="E885" s="4"/>
       <c r="F885" s="4"/>
       <c r="I885" s="4"/>
+      <c r="J885" s="4"/>
     </row>
     <row r="886" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A886" s="4"/>
@@ -8952,6 +10166,7 @@
       <c r="E886" s="4"/>
       <c r="F886" s="4"/>
       <c r="I886" s="4"/>
+      <c r="J886" s="4"/>
     </row>
     <row r="887" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A887" s="4"/>
@@ -8961,6 +10176,7 @@
       <c r="E887" s="4"/>
       <c r="F887" s="4"/>
       <c r="I887" s="4"/>
+      <c r="J887" s="4"/>
     </row>
     <row r="888" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A888" s="4"/>
@@ -8970,6 +10186,7 @@
       <c r="E888" s="4"/>
       <c r="F888" s="4"/>
       <c r="I888" s="4"/>
+      <c r="J888" s="4"/>
     </row>
     <row r="889" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A889" s="4"/>
@@ -8979,6 +10196,7 @@
       <c r="E889" s="4"/>
       <c r="F889" s="4"/>
       <c r="I889" s="4"/>
+      <c r="J889" s="4"/>
     </row>
     <row r="890" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A890" s="4"/>
@@ -8988,6 +10206,7 @@
       <c r="E890" s="4"/>
       <c r="F890" s="4"/>
       <c r="I890" s="4"/>
+      <c r="J890" s="4"/>
     </row>
     <row r="891" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A891" s="4"/>
@@ -8997,6 +10216,7 @@
       <c r="E891" s="4"/>
       <c r="F891" s="4"/>
       <c r="I891" s="4"/>
+      <c r="J891" s="4"/>
     </row>
     <row r="892" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A892" s="4"/>
@@ -9006,6 +10226,7 @@
       <c r="E892" s="4"/>
       <c r="F892" s="4"/>
       <c r="I892" s="4"/>
+      <c r="J892" s="4"/>
     </row>
     <row r="893" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A893" s="4"/>
@@ -9015,6 +10236,7 @@
       <c r="E893" s="4"/>
       <c r="F893" s="4"/>
       <c r="I893" s="4"/>
+      <c r="J893" s="4"/>
     </row>
     <row r="894" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A894" s="4"/>
@@ -9024,6 +10246,7 @@
       <c r="E894" s="4"/>
       <c r="F894" s="4"/>
       <c r="I894" s="4"/>
+      <c r="J894" s="4"/>
     </row>
     <row r="895" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A895" s="4"/>
@@ -9033,6 +10256,7 @@
       <c r="E895" s="4"/>
       <c r="F895" s="4"/>
       <c r="I895" s="4"/>
+      <c r="J895" s="4"/>
     </row>
     <row r="896" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A896" s="4"/>
@@ -9042,6 +10266,7 @@
       <c r="E896" s="4"/>
       <c r="F896" s="4"/>
       <c r="I896" s="4"/>
+      <c r="J896" s="4"/>
     </row>
     <row r="897" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A897" s="4"/>
@@ -9051,6 +10276,7 @@
       <c r="E897" s="4"/>
       <c r="F897" s="4"/>
       <c r="I897" s="4"/>
+      <c r="J897" s="4"/>
     </row>
     <row r="898" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A898" s="4"/>
@@ -9060,6 +10286,7 @@
       <c r="E898" s="4"/>
       <c r="F898" s="4"/>
       <c r="I898" s="4"/>
+      <c r="J898" s="4"/>
     </row>
     <row r="899" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A899" s="4"/>
@@ -9069,6 +10296,7 @@
       <c r="E899" s="4"/>
       <c r="F899" s="4"/>
       <c r="I899" s="4"/>
+      <c r="J899" s="4"/>
     </row>
     <row r="900" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A900" s="4"/>
@@ -9078,6 +10306,7 @@
       <c r="E900" s="4"/>
       <c r="F900" s="4"/>
       <c r="I900" s="4"/>
+      <c r="J900" s="4"/>
     </row>
     <row r="901" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A901" s="4"/>
@@ -9087,6 +10316,7 @@
       <c r="E901" s="4"/>
       <c r="F901" s="4"/>
       <c r="I901" s="4"/>
+      <c r="J901" s="4"/>
     </row>
     <row r="902" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A902" s="4"/>
@@ -9096,6 +10326,7 @@
       <c r="E902" s="4"/>
       <c r="F902" s="4"/>
       <c r="I902" s="4"/>
+      <c r="J902" s="4"/>
     </row>
     <row r="903" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A903" s="4"/>
@@ -9105,6 +10336,7 @@
       <c r="E903" s="4"/>
       <c r="F903" s="4"/>
       <c r="I903" s="4"/>
+      <c r="J903" s="4"/>
     </row>
     <row r="904" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A904" s="4"/>
@@ -9114,6 +10346,7 @@
       <c r="E904" s="4"/>
       <c r="F904" s="4"/>
       <c r="I904" s="4"/>
+      <c r="J904" s="4"/>
     </row>
     <row r="905" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A905" s="4"/>
@@ -9123,6 +10356,7 @@
       <c r="E905" s="4"/>
       <c r="F905" s="4"/>
       <c r="I905" s="4"/>
+      <c r="J905" s="4"/>
     </row>
     <row r="906" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A906" s="4"/>
@@ -9132,6 +10366,7 @@
       <c r="E906" s="4"/>
       <c r="F906" s="4"/>
       <c r="I906" s="4"/>
+      <c r="J906" s="4"/>
     </row>
     <row r="907" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A907" s="4"/>
@@ -9141,6 +10376,7 @@
       <c r="E907" s="4"/>
       <c r="F907" s="4"/>
       <c r="I907" s="4"/>
+      <c r="J907" s="4"/>
     </row>
     <row r="908" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A908" s="4"/>
@@ -9150,6 +10386,7 @@
       <c r="E908" s="4"/>
       <c r="F908" s="4"/>
       <c r="I908" s="4"/>
+      <c r="J908" s="4"/>
     </row>
     <row r="909" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A909" s="4"/>
@@ -9159,6 +10396,7 @@
       <c r="E909" s="4"/>
       <c r="F909" s="4"/>
       <c r="I909" s="4"/>
+      <c r="J909" s="4"/>
     </row>
     <row r="910" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A910" s="4"/>
@@ -9168,6 +10406,7 @@
       <c r="E910" s="4"/>
       <c r="F910" s="4"/>
       <c r="I910" s="4"/>
+      <c r="J910" s="4"/>
     </row>
     <row r="911" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A911" s="4"/>
@@ -9177,6 +10416,7 @@
       <c r="E911" s="4"/>
       <c r="F911" s="4"/>
       <c r="I911" s="4"/>
+      <c r="J911" s="4"/>
     </row>
     <row r="912" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A912" s="4"/>
@@ -9186,6 +10426,7 @@
       <c r="E912" s="4"/>
       <c r="F912" s="4"/>
       <c r="I912" s="4"/>
+      <c r="J912" s="4"/>
     </row>
     <row r="913" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A913" s="4"/>
@@ -9195,6 +10436,7 @@
       <c r="E913" s="4"/>
       <c r="F913" s="4"/>
       <c r="I913" s="4"/>
+      <c r="J913" s="4"/>
     </row>
     <row r="914" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A914" s="4"/>
@@ -9204,6 +10446,7 @@
       <c r="E914" s="4"/>
       <c r="F914" s="4"/>
       <c r="I914" s="4"/>
+      <c r="J914" s="4"/>
     </row>
     <row r="915" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A915" s="4"/>
@@ -9213,6 +10456,7 @@
       <c r="E915" s="4"/>
       <c r="F915" s="4"/>
       <c r="I915" s="4"/>
+      <c r="J915" s="4"/>
     </row>
     <row r="916" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A916" s="4"/>
@@ -9222,6 +10466,7 @@
       <c r="E916" s="4"/>
       <c r="F916" s="4"/>
       <c r="I916" s="4"/>
+      <c r="J916" s="4"/>
     </row>
     <row r="917" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A917" s="4"/>
@@ -9231,6 +10476,7 @@
       <c r="E917" s="4"/>
       <c r="F917" s="4"/>
       <c r="I917" s="4"/>
+      <c r="J917" s="4"/>
     </row>
     <row r="918" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A918" s="4"/>
@@ -9240,6 +10486,7 @@
       <c r="E918" s="4"/>
       <c r="F918" s="4"/>
       <c r="I918" s="4"/>
+      <c r="J918" s="4"/>
     </row>
     <row r="919" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A919" s="4"/>
@@ -9249,6 +10496,7 @@
       <c r="E919" s="4"/>
       <c r="F919" s="4"/>
       <c r="I919" s="4"/>
+      <c r="J919" s="4"/>
     </row>
     <row r="920" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A920" s="4"/>
@@ -9258,6 +10506,7 @@
       <c r="E920" s="4"/>
       <c r="F920" s="4"/>
       <c r="I920" s="4"/>
+      <c r="J920" s="4"/>
     </row>
     <row r="921" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A921" s="4"/>
@@ -9267,6 +10516,7 @@
       <c r="E921" s="4"/>
       <c r="F921" s="4"/>
       <c r="I921" s="4"/>
+      <c r="J921" s="4"/>
     </row>
     <row r="922" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A922" s="4"/>
@@ -9276,6 +10526,7 @@
       <c r="E922" s="4"/>
       <c r="F922" s="4"/>
       <c r="I922" s="4"/>
+      <c r="J922" s="4"/>
     </row>
     <row r="923" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A923" s="4"/>
@@ -9285,6 +10536,7 @@
       <c r="E923" s="4"/>
       <c r="F923" s="4"/>
       <c r="I923" s="4"/>
+      <c r="J923" s="4"/>
     </row>
     <row r="924" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A924" s="4"/>
@@ -9294,6 +10546,7 @@
       <c r="E924" s="4"/>
       <c r="F924" s="4"/>
       <c r="I924" s="4"/>
+      <c r="J924" s="4"/>
     </row>
     <row r="925" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A925" s="4"/>
@@ -9303,6 +10556,7 @@
       <c r="E925" s="4"/>
       <c r="F925" s="4"/>
       <c r="I925" s="4"/>
+      <c r="J925" s="4"/>
     </row>
     <row r="926" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A926" s="4"/>
@@ -9312,6 +10566,7 @@
       <c r="E926" s="4"/>
       <c r="F926" s="4"/>
       <c r="I926" s="4"/>
+      <c r="J926" s="4"/>
     </row>
     <row r="927" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A927" s="4"/>
@@ -9321,6 +10576,7 @@
       <c r="E927" s="4"/>
       <c r="F927" s="4"/>
       <c r="I927" s="4"/>
+      <c r="J927" s="4"/>
     </row>
     <row r="928" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A928" s="4"/>
@@ -9330,6 +10586,7 @@
       <c r="E928" s="4"/>
       <c r="F928" s="4"/>
       <c r="I928" s="4"/>
+      <c r="J928" s="4"/>
     </row>
     <row r="929" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A929" s="4"/>
@@ -9339,6 +10596,7 @@
       <c r="E929" s="4"/>
       <c r="F929" s="4"/>
       <c r="I929" s="4"/>
+      <c r="J929" s="4"/>
     </row>
     <row r="930" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A930" s="4"/>
@@ -9348,6 +10606,7 @@
       <c r="E930" s="4"/>
       <c r="F930" s="4"/>
       <c r="I930" s="4"/>
+      <c r="J930" s="4"/>
     </row>
     <row r="931" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A931" s="4"/>
@@ -9357,6 +10616,7 @@
       <c r="E931" s="4"/>
       <c r="F931" s="4"/>
       <c r="I931" s="4"/>
+      <c r="J931" s="4"/>
     </row>
     <row r="932" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A932" s="4"/>
@@ -9366,6 +10626,7 @@
       <c r="E932" s="4"/>
       <c r="F932" s="4"/>
       <c r="I932" s="4"/>
+      <c r="J932" s="4"/>
     </row>
     <row r="933" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A933" s="4"/>
@@ -9375,6 +10636,7 @@
       <c r="E933" s="4"/>
       <c r="F933" s="4"/>
       <c r="I933" s="4"/>
+      <c r="J933" s="4"/>
     </row>
     <row r="934" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A934" s="4"/>
@@ -9384,6 +10646,7 @@
       <c r="E934" s="4"/>
       <c r="F934" s="4"/>
       <c r="I934" s="4"/>
+      <c r="J934" s="4"/>
     </row>
     <row r="935" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A935" s="4"/>
@@ -9393,6 +10656,7 @@
       <c r="E935" s="4"/>
       <c r="F935" s="4"/>
       <c r="I935" s="4"/>
+      <c r="J935" s="4"/>
     </row>
     <row r="936" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A936" s="4"/>
@@ -9402,6 +10666,7 @@
       <c r="E936" s="4"/>
       <c r="F936" s="4"/>
       <c r="I936" s="4"/>
+      <c r="J936" s="4"/>
     </row>
     <row r="937" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A937" s="4"/>
@@ -9411,6 +10676,7 @@
       <c r="E937" s="4"/>
       <c r="F937" s="4"/>
       <c r="I937" s="4"/>
+      <c r="J937" s="4"/>
     </row>
     <row r="938" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A938" s="4"/>
@@ -9420,6 +10686,7 @@
       <c r="E938" s="4"/>
       <c r="F938" s="4"/>
       <c r="I938" s="4"/>
+      <c r="J938" s="4"/>
     </row>
     <row r="939" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A939" s="4"/>
@@ -9429,6 +10696,7 @@
       <c r="E939" s="4"/>
       <c r="F939" s="4"/>
       <c r="I939" s="4"/>
+      <c r="J939" s="4"/>
     </row>
     <row r="940" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A940" s="4"/>
@@ -9438,6 +10706,7 @@
       <c r="E940" s="4"/>
       <c r="F940" s="4"/>
       <c r="I940" s="4"/>
+      <c r="J940" s="4"/>
     </row>
     <row r="941" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A941" s="4"/>
@@ -9447,6 +10716,7 @@
       <c r="E941" s="4"/>
       <c r="F941" s="4"/>
       <c r="I941" s="4"/>
+      <c r="J941" s="4"/>
     </row>
     <row r="942" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A942" s="4"/>
@@ -9456,6 +10726,7 @@
       <c r="E942" s="4"/>
       <c r="F942" s="4"/>
       <c r="I942" s="4"/>
+      <c r="J942" s="4"/>
     </row>
     <row r="943" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A943" s="4"/>
@@ -9465,6 +10736,7 @@
       <c r="E943" s="4"/>
       <c r="F943" s="4"/>
       <c r="I943" s="4"/>
+      <c r="J943" s="4"/>
     </row>
     <row r="944" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A944" s="4"/>
@@ -9474,6 +10746,7 @@
       <c r="E944" s="4"/>
       <c r="F944" s="4"/>
       <c r="I944" s="4"/>
+      <c r="J944" s="4"/>
     </row>
     <row r="945" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A945" s="4"/>
@@ -9483,6 +10756,7 @@
       <c r="E945" s="4"/>
       <c r="F945" s="4"/>
       <c r="I945" s="4"/>
+      <c r="J945" s="4"/>
     </row>
     <row r="946" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A946" s="4"/>
@@ -9492,6 +10766,7 @@
       <c r="E946" s="4"/>
       <c r="F946" s="4"/>
       <c r="I946" s="4"/>
+      <c r="J946" s="4"/>
     </row>
     <row r="947" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A947" s="4"/>
@@ -9501,6 +10776,7 @@
       <c r="E947" s="4"/>
       <c r="F947" s="4"/>
       <c r="I947" s="4"/>
+      <c r="J947" s="4"/>
     </row>
     <row r="948" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A948" s="4"/>
@@ -9510,6 +10786,7 @@
       <c r="E948" s="4"/>
       <c r="F948" s="4"/>
       <c r="I948" s="4"/>
+      <c r="J948" s="4"/>
     </row>
     <row r="949" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A949" s="4"/>
@@ -9519,6 +10796,7 @@
       <c r="E949" s="4"/>
       <c r="F949" s="4"/>
       <c r="I949" s="4"/>
+      <c r="J949" s="4"/>
     </row>
     <row r="950" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A950" s="4"/>
@@ -9528,6 +10806,7 @@
       <c r="E950" s="4"/>
       <c r="F950" s="4"/>
       <c r="I950" s="4"/>
+      <c r="J950" s="4"/>
     </row>
     <row r="951" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A951" s="4"/>
@@ -9537,6 +10816,7 @@
       <c r="E951" s="4"/>
       <c r="F951" s="4"/>
       <c r="I951" s="4"/>
+      <c r="J951" s="4"/>
     </row>
     <row r="952" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A952" s="4"/>
@@ -9546,6 +10826,7 @@
       <c r="E952" s="4"/>
       <c r="F952" s="4"/>
       <c r="I952" s="4"/>
+      <c r="J952" s="4"/>
     </row>
     <row r="953" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A953" s="4"/>
@@ -9555,6 +10836,7 @@
       <c r="E953" s="4"/>
       <c r="F953" s="4"/>
       <c r="I953" s="4"/>
+      <c r="J953" s="4"/>
     </row>
     <row r="954" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A954" s="4"/>
@@ -9564,6 +10846,7 @@
       <c r="E954" s="4"/>
       <c r="F954" s="4"/>
       <c r="I954" s="4"/>
+      <c r="J954" s="4"/>
     </row>
     <row r="955" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A955" s="4"/>
@@ -9573,6 +10856,7 @@
       <c r="E955" s="4"/>
       <c r="F955" s="4"/>
       <c r="I955" s="4"/>
+      <c r="J955" s="4"/>
     </row>
     <row r="956" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A956" s="4"/>
@@ -9582,6 +10866,7 @@
       <c r="E956" s="4"/>
       <c r="F956" s="4"/>
       <c r="I956" s="4"/>
+      <c r="J956" s="4"/>
     </row>
     <row r="957" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A957" s="4"/>
@@ -9591,6 +10876,7 @@
       <c r="E957" s="4"/>
       <c r="F957" s="4"/>
       <c r="I957" s="4"/>
+      <c r="J957" s="4"/>
     </row>
     <row r="958" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A958" s="4"/>
@@ -9600,6 +10886,7 @@
       <c r="E958" s="4"/>
       <c r="F958" s="4"/>
       <c r="I958" s="4"/>
+      <c r="J958" s="4"/>
     </row>
     <row r="959" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A959" s="4"/>
@@ -9609,6 +10896,7 @@
       <c r="E959" s="4"/>
       <c r="F959" s="4"/>
       <c r="I959" s="4"/>
+      <c r="J959" s="4"/>
     </row>
     <row r="960" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A960" s="4"/>
@@ -9618,6 +10906,7 @@
       <c r="E960" s="4"/>
       <c r="F960" s="4"/>
       <c r="I960" s="4"/>
+      <c r="J960" s="4"/>
     </row>
     <row r="961" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A961" s="4"/>
@@ -9627,6 +10916,7 @@
       <c r="E961" s="4"/>
       <c r="F961" s="4"/>
       <c r="I961" s="4"/>
+      <c r="J961" s="4"/>
     </row>
     <row r="962" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A962" s="4"/>
@@ -9636,6 +10926,7 @@
       <c r="E962" s="4"/>
       <c r="F962" s="4"/>
       <c r="I962" s="4"/>
+      <c r="J962" s="4"/>
     </row>
     <row r="963" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A963" s="4"/>
@@ -9645,6 +10936,7 @@
       <c r="E963" s="4"/>
       <c r="F963" s="4"/>
       <c r="I963" s="4"/>
+      <c r="J963" s="4"/>
     </row>
     <row r="964" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A964" s="4"/>
@@ -9654,6 +10946,7 @@
       <c r="E964" s="4"/>
       <c r="F964" s="4"/>
       <c r="I964" s="4"/>
+      <c r="J964" s="4"/>
     </row>
     <row r="965" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A965" s="4"/>
@@ -9663,6 +10956,7 @@
       <c r="E965" s="4"/>
       <c r="F965" s="4"/>
       <c r="I965" s="4"/>
+      <c r="J965" s="4"/>
     </row>
     <row r="966" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A966" s="4"/>
@@ -9672,6 +10966,7 @@
       <c r="E966" s="4"/>
       <c r="F966" s="4"/>
       <c r="I966" s="4"/>
+      <c r="J966" s="4"/>
     </row>
     <row r="967" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A967" s="4"/>
@@ -9681,6 +10976,7 @@
       <c r="E967" s="4"/>
       <c r="F967" s="4"/>
       <c r="I967" s="4"/>
+      <c r="J967" s="4"/>
     </row>
     <row r="968" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A968" s="4"/>
@@ -9690,6 +10986,7 @@
       <c r="E968" s="4"/>
       <c r="F968" s="4"/>
       <c r="I968" s="4"/>
+      <c r="J968" s="4"/>
     </row>
     <row r="969" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A969" s="4"/>
@@ -9699,6 +10996,7 @@
       <c r="E969" s="4"/>
       <c r="F969" s="4"/>
       <c r="I969" s="4"/>
+      <c r="J969" s="4"/>
     </row>
     <row r="970" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A970" s="4"/>
@@ -9708,6 +11006,7 @@
       <c r="E970" s="4"/>
       <c r="F970" s="4"/>
       <c r="I970" s="4"/>
+      <c r="J970" s="4"/>
     </row>
     <row r="971" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A971" s="4"/>
@@ -9717,6 +11016,7 @@
       <c r="E971" s="4"/>
       <c r="F971" s="4"/>
       <c r="I971" s="4"/>
+      <c r="J971" s="4"/>
     </row>
     <row r="972" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A972" s="4"/>
@@ -9726,6 +11026,7 @@
       <c r="E972" s="4"/>
       <c r="F972" s="4"/>
       <c r="I972" s="4"/>
+      <c r="J972" s="4"/>
     </row>
     <row r="973" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A973" s="4"/>
@@ -9735,6 +11036,7 @@
       <c r="E973" s="4"/>
       <c r="F973" s="4"/>
       <c r="I973" s="4"/>
+      <c r="J973" s="4"/>
     </row>
     <row r="974" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A974" s="4"/>
@@ -9744,6 +11046,7 @@
       <c r="E974" s="4"/>
       <c r="F974" s="4"/>
       <c r="I974" s="4"/>
+      <c r="J974" s="4"/>
     </row>
     <row r="975" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A975" s="4"/>
@@ -9753,6 +11056,7 @@
       <c r="E975" s="4"/>
       <c r="F975" s="4"/>
       <c r="I975" s="4"/>
+      <c r="J975" s="4"/>
     </row>
     <row r="976" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A976" s="4"/>
@@ -9762,6 +11066,7 @@
       <c r="E976" s="4"/>
       <c r="F976" s="4"/>
       <c r="I976" s="4"/>
+      <c r="J976" s="4"/>
     </row>
     <row r="977" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A977" s="4"/>
@@ -9771,6 +11076,7 @@
       <c r="E977" s="4"/>
       <c r="F977" s="4"/>
       <c r="I977" s="4"/>
+      <c r="J977" s="4"/>
     </row>
     <row r="978" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A978" s="4"/>
@@ -9780,6 +11086,7 @@
       <c r="E978" s="4"/>
       <c r="F978" s="4"/>
       <c r="I978" s="4"/>
+      <c r="J978" s="4"/>
     </row>
     <row r="979" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A979" s="4"/>
@@ -9789,6 +11096,7 @@
       <c r="E979" s="4"/>
       <c r="F979" s="4"/>
       <c r="I979" s="4"/>
+      <c r="J979" s="4"/>
     </row>
     <row r="980" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A980" s="4"/>
@@ -9798,6 +11106,7 @@
       <c r="E980" s="4"/>
       <c r="F980" s="4"/>
       <c r="I980" s="4"/>
+      <c r="J980" s="4"/>
     </row>
     <row r="981" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A981" s="4"/>
@@ -9807,6 +11116,7 @@
       <c r="E981" s="4"/>
       <c r="F981" s="4"/>
       <c r="I981" s="4"/>
+      <c r="J981" s="4"/>
     </row>
     <row r="982" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A982" s="4"/>
@@ -9816,6 +11126,7 @@
       <c r="E982" s="4"/>
       <c r="F982" s="4"/>
       <c r="I982" s="4"/>
+      <c r="J982" s="4"/>
     </row>
     <row r="983" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A983" s="4"/>
@@ -9825,6 +11136,7 @@
       <c r="E983" s="4"/>
       <c r="F983" s="4"/>
       <c r="I983" s="4"/>
+      <c r="J983" s="4"/>
     </row>
     <row r="984" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A984" s="4"/>
@@ -9834,6 +11146,7 @@
       <c r="E984" s="4"/>
       <c r="F984" s="4"/>
       <c r="I984" s="4"/>
+      <c r="J984" s="4"/>
     </row>
     <row r="985" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A985" s="4"/>
@@ -9843,6 +11156,7 @@
       <c r="E985" s="4"/>
       <c r="F985" s="4"/>
       <c r="I985" s="4"/>
+      <c r="J985" s="4"/>
     </row>
     <row r="986" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A986" s="4"/>
@@ -9852,6 +11166,7 @@
       <c r="E986" s="4"/>
       <c r="F986" s="4"/>
       <c r="I986" s="4"/>
+      <c r="J986" s="4"/>
     </row>
     <row r="987" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A987" s="4"/>
@@ -9861,6 +11176,7 @@
       <c r="E987" s="4"/>
       <c r="F987" s="4"/>
       <c r="I987" s="4"/>
+      <c r="J987" s="4"/>
     </row>
     <row r="988" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A988" s="4"/>
@@ -9870,6 +11186,7 @@
       <c r="E988" s="4"/>
       <c r="F988" s="4"/>
       <c r="I988" s="4"/>
+      <c r="J988" s="4"/>
     </row>
     <row r="989" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A989" s="4"/>
@@ -9879,6 +11196,7 @@
       <c r="E989" s="4"/>
       <c r="F989" s="4"/>
       <c r="I989" s="4"/>
+      <c r="J989" s="4"/>
     </row>
     <row r="990" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A990" s="4"/>
@@ -9888,6 +11206,7 @@
       <c r="E990" s="4"/>
       <c r="F990" s="4"/>
       <c r="I990" s="4"/>
+      <c r="J990" s="4"/>
     </row>
     <row r="991" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A991" s="4"/>
@@ -9897,6 +11216,7 @@
       <c r="E991" s="4"/>
       <c r="F991" s="4"/>
       <c r="I991" s="4"/>
+      <c r="J991" s="4"/>
     </row>
     <row r="992" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A992" s="4"/>
@@ -9906,6 +11226,7 @@
       <c r="E992" s="4"/>
       <c r="F992" s="4"/>
       <c r="I992" s="4"/>
+      <c r="J992" s="4"/>
     </row>
     <row r="993" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A993" s="4"/>
@@ -9915,6 +11236,7 @@
       <c r="E993" s="4"/>
       <c r="F993" s="4"/>
       <c r="I993" s="4"/>
+      <c r="J993" s="4"/>
     </row>
     <row r="994" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A994" s="4"/>
@@ -9924,6 +11246,7 @@
       <c r="E994" s="4"/>
       <c r="F994" s="4"/>
       <c r="I994" s="4"/>
+      <c r="J994" s="4"/>
     </row>
     <row r="995" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A995" s="4"/>
@@ -9933,6 +11256,7 @@
       <c r="E995" s="4"/>
       <c r="F995" s="4"/>
       <c r="I995" s="4"/>
+      <c r="J995" s="4"/>
     </row>
     <row r="996" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A996" s="4"/>
@@ -9942,6 +11266,7 @@
       <c r="E996" s="4"/>
       <c r="F996" s="4"/>
       <c r="I996" s="4"/>
+      <c r="J996" s="4"/>
     </row>
     <row r="997" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A997" s="4"/>
@@ -9951,6 +11276,7 @@
       <c r="E997" s="4"/>
       <c r="F997" s="4"/>
       <c r="I997" s="4"/>
+      <c r="J997" s="4"/>
     </row>
     <row r="998" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A998" s="4"/>
@@ -9960,6 +11286,7 @@
       <c r="E998" s="4"/>
       <c r="F998" s="4"/>
       <c r="I998" s="4"/>
+      <c r="J998" s="4"/>
     </row>
     <row r="999" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A999" s="4"/>
@@ -9969,6 +11296,7 @@
       <c r="E999" s="4"/>
       <c r="F999" s="4"/>
       <c r="I999" s="4"/>
+      <c r="J999" s="4"/>
     </row>
     <row r="1000" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1000" s="4"/>
@@ -9978,6 +11306,7 @@
       <c r="E1000" s="4"/>
       <c r="F1000" s="4"/>
       <c r="I1000" s="4"/>
+      <c r="J1000" s="4"/>
     </row>
     <row r="1001" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1001" s="4"/>
@@ -9987,6 +11316,7 @@
       <c r="E1001" s="4"/>
       <c r="F1001" s="4"/>
       <c r="I1001" s="4"/>
+      <c r="J1001" s="4"/>
     </row>
     <row r="1002" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1002" s="4"/>
@@ -9996,6 +11326,7 @@
       <c r="E1002" s="4"/>
       <c r="F1002" s="4"/>
       <c r="I1002" s="4"/>
+      <c r="J1002" s="4"/>
     </row>
     <row r="1003" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1003" s="4"/>
@@ -10005,6 +11336,7 @@
       <c r="E1003" s="4"/>
       <c r="F1003" s="4"/>
       <c r="I1003" s="4"/>
+      <c r="J1003" s="4"/>
     </row>
     <row r="1004" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1004" s="4"/>
@@ -10014,6 +11346,7 @@
       <c r="E1004" s="4"/>
       <c r="F1004" s="4"/>
       <c r="I1004" s="4"/>
+      <c r="J1004" s="4"/>
     </row>
     <row r="1005" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1005" s="4"/>
@@ -10023,6 +11356,7 @@
       <c r="E1005" s="4"/>
       <c r="F1005" s="4"/>
       <c r="I1005" s="4"/>
+      <c r="J1005" s="4"/>
     </row>
     <row r="1006" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1006" s="4"/>
@@ -10032,6 +11366,7 @@
       <c r="E1006" s="4"/>
       <c r="F1006" s="4"/>
       <c r="I1006" s="4"/>
+      <c r="J1006" s="4"/>
     </row>
     <row r="1007" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1007" s="4"/>
@@ -10041,6 +11376,7 @@
       <c r="E1007" s="4"/>
       <c r="F1007" s="4"/>
       <c r="I1007" s="4"/>
+      <c r="J1007" s="4"/>
     </row>
     <row r="1008" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1008" s="4"/>
@@ -10050,6 +11386,7 @@
       <c r="E1008" s="4"/>
       <c r="F1008" s="4"/>
       <c r="I1008" s="4"/>
+      <c r="J1008" s="4"/>
     </row>
     <row r="1009" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1009" s="4"/>
@@ -10059,6 +11396,7 @@
       <c r="E1009" s="4"/>
       <c r="F1009" s="4"/>
       <c r="I1009" s="4"/>
+      <c r="J1009" s="4"/>
     </row>
     <row r="1010" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1010" s="4"/>
@@ -10068,6 +11406,7 @@
       <c r="E1010" s="4"/>
       <c r="F1010" s="4"/>
       <c r="I1010" s="4"/>
+      <c r="J1010" s="4"/>
     </row>
     <row r="1011" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1011" s="4"/>
@@ -10077,6 +11416,7 @@
       <c r="E1011" s="4"/>
       <c r="F1011" s="4"/>
       <c r="I1011" s="4"/>
+      <c r="J1011" s="4"/>
     </row>
     <row r="1012" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1012" s="4"/>
@@ -10086,6 +11426,7 @@
       <c r="E1012" s="4"/>
       <c r="F1012" s="4"/>
       <c r="I1012" s="4"/>
+      <c r="J1012" s="4"/>
     </row>
     <row r="1013" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1013" s="4"/>
@@ -10095,6 +11436,7 @@
       <c r="E1013" s="4"/>
       <c r="F1013" s="4"/>
       <c r="I1013" s="4"/>
+      <c r="J1013" s="4"/>
     </row>
     <row r="1014" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1014" s="4"/>
@@ -10104,6 +11446,7 @@
       <c r="E1014" s="4"/>
       <c r="F1014" s="4"/>
       <c r="I1014" s="4"/>
+      <c r="J1014" s="4"/>
     </row>
     <row r="1015" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1015" s="4"/>
@@ -10113,6 +11456,7 @@
       <c r="E1015" s="4"/>
       <c r="F1015" s="4"/>
       <c r="I1015" s="4"/>
+      <c r="J1015" s="4"/>
     </row>
     <row r="1016" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1016" s="4"/>
@@ -10123,6 +11467,7 @@
       <c r="F1016" s="4"/>
       <c r="H1016" s="4"/>
       <c r="I1016" s="4"/>
+      <c r="J1016" s="4"/>
     </row>
     <row r="1017" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1017" s="4"/>
@@ -10133,6 +11478,7 @@
       <c r="F1017" s="4"/>
       <c r="H1017" s="4"/>
       <c r="I1017" s="4"/>
+      <c r="J1017" s="4"/>
     </row>
     <row r="1018" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1018" s="4"/>
@@ -10143,6 +11489,7 @@
       <c r="F1018" s="4"/>
       <c r="H1018" s="4"/>
       <c r="I1018" s="4"/>
+      <c r="J1018" s="4"/>
     </row>
     <row r="1019" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1019" s="4"/>
@@ -10153,6 +11500,7 @@
       <c r="F1019" s="4"/>
       <c r="H1019" s="4"/>
       <c r="I1019" s="4"/>
+      <c r="J1019" s="4"/>
     </row>
     <row r="1020" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1020" s="4"/>
@@ -10163,9 +11511,10 @@
       <c r="F1020" s="4"/>
       <c r="H1020" s="4"/>
       <c r="I1020" s="4"/>
+      <c r="J1020" s="4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:I10000">
+  <conditionalFormatting sqref="J21:J10000 A2:I10000 J2:J20">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A2="begin_group"</formula>
     </cfRule>
@@ -10237,31 +11586,31 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B2" s="7" t="str">
         <f aca="true">TEXT(NOW(), "yyyymmddhhmmss")</f>
-        <v>20260114091903</v>
+        <v>20260416171218</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
